--- a/BOM/Heli_Collective_Final_BOM.xlsx
+++ b/BOM/Heli_Collective_Final_BOM.xlsx
@@ -633,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P76"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>SEARCH CONT hat (4) and starter trigger (1). IN8, IN15, IN16 are spare</t>
+          <t>SEARCH CONT hat (4, new rocker hat) and starter trigger (1). IN8, IN15, IN16 are spare</t>
         </is>
       </c>
       <c r="P35" s="11" t="inlineStr">
@@ -2718,11 +2718,11 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>Panels</t>
+          <t>Search hat bezel</t>
         </is>
       </c>
       <c r="C43" s="21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D43" s="21" t="n">
         <v>1</v>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="H43" s="22" t="inlineStr">
         <is>
-          <t>M3 x 12 countersunk screw (DIN 7991)</t>
+          <t>M2 x 8 countersunk screw</t>
         </is>
       </c>
       <c r="I43" s="22" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="O43" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. 4 per panel, into M3 threads tapped in the box's corner columns (the pilots run 50 mm deep, so the x 12 has room)</t>
+          <t>In the screw kit. Through the hat's bezel into M2 threads tapped in the carrier (1.6 mm pilots)</t>
         </is>
       </c>
       <c r="P43" s="22" t="inlineStr">
@@ -2783,11 +2783,11 @@
       </c>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>HeliSR board</t>
+          <t>Search hat pivot</t>
         </is>
       </c>
       <c r="C44" s="21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D44" s="21" t="n">
         <v>1</v>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H44" s="22" t="inlineStr">
         <is>
-          <t>M3 x 12 countersunk screw (DIN 7991) + M3 hex nut</t>
+          <t>M3 x 4 set screw</t>
         </is>
       </c>
       <c r="I44" s="22" t="inlineStr">
         <is>
-          <t>AvrestYPT</t>
+          <t>HIQTRADEBYJJ</t>
         </is>
       </c>
       <c r="J44" s="22" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="L44" s="24" t="inlineStr">
         <is>
-          <t>B0FMD5TMSH</t>
+          <t>B0DG33R714</t>
         </is>
       </c>
       <c r="M44" s="25" t="n">
@@ -2833,443 +2833,443 @@
       </c>
       <c r="O44" s="22" t="inlineStr">
         <is>
+          <t>In the set screw kit. Into the rocker plate's centre (tap M3), from behind; its tip is the pivot and sets the preload. Turn it with a 1.5 mm hex key through the carrier floor</t>
+        </is>
+      </c>
+      <c r="P44" s="22" t="inlineStr">
+        <is>
+          <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>Panels</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="21">
+        <f>ROUNDUP(C45*$C$3/D45,0)</f>
+        <v/>
+      </c>
+      <c r="F45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="21">
+        <f>MAX(0,E45-F45)</f>
+        <v/>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>M3 x 12 countersunk screw (DIN 7991)</t>
+        </is>
+      </c>
+      <c r="I45" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT</t>
+        </is>
+      </c>
+      <c r="J45" s="22" t="inlineStr"/>
+      <c r="K45" s="22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L45" s="24" t="inlineStr">
+        <is>
+          <t>B0FMD5TMSH</t>
+        </is>
+      </c>
+      <c r="M45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="25">
+        <f>IF(M45="","",G45*M45)</f>
+        <v/>
+      </c>
+      <c r="O45" s="22" t="inlineStr">
+        <is>
+          <t>In the screw kit. 4 per panel, into M3 threads tapped in the box's corner columns (the pilots run 50 mm deep, so the x 12 has room)</t>
+        </is>
+      </c>
+      <c r="P45" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>HeliSR board</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="21">
+        <f>ROUNDUP(C46*$C$3/D46,0)</f>
+        <v/>
+      </c>
+      <c r="F46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="21">
+        <f>MAX(0,E46-F46)</f>
+        <v/>
+      </c>
+      <c r="H46" s="22" t="inlineStr">
+        <is>
+          <t>M3 x 12 countersunk screw (DIN 7991) + M3 hex nut</t>
+        </is>
+      </c>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT</t>
+        </is>
+      </c>
+      <c r="J46" s="22" t="inlineStr"/>
+      <c r="K46" s="22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L46" s="24" t="inlineStr">
+        <is>
+          <t>B0FMD5TMSH</t>
+        </is>
+      </c>
+      <c r="M46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="25">
+        <f>IF(M46="","",G46*M46)</f>
+        <v/>
+      </c>
+      <c r="O46" s="22" t="inlineStr">
+        <is>
           <t>In the screw kit. From outside the rear wall through a spacer and the board</t>
         </is>
       </c>
-      <c r="P44" s="22" t="inlineStr">
+      <c r="P46" s="22" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>HeliSR board</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n">
+      <c r="C47" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D45" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="10">
-        <f>ROUNDUP(C45*$C$3/D45,0)</f>
-        <v/>
-      </c>
-      <c r="F45" s="12" t="n">
+      <c r="D47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="10">
+        <f>ROUNDUP(C47*$C$3/D47,0)</f>
+        <v/>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G45" s="10">
-        <f>MAX(0,E45-F45)</f>
-        <v/>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="G47" s="10">
+        <f>MAX(0,E47-F47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>Round spacer, unthreaded, for M3, 4 mm long, 6.4 mm OD, PVC, self-retaining</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I47" s="11" t="inlineStr">
         <is>
           <t>Bivar</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J47" s="11" t="inlineStr">
         <is>
           <t>SRS-4-4MM</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
+      <c r="K47" s="11" t="inlineStr">
         <is>
           <t>Digi-Key</t>
         </is>
       </c>
-      <c r="L45" s="13" t="inlineStr">
+      <c r="L47" s="13" t="inlineStr">
         <is>
           <t>SRS-4-4MM-ND</t>
         </is>
       </c>
-      <c r="M45" s="14" t="n">
+      <c r="M47" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="N45" s="14">
-        <f>IF(M45="","",G45*M45)</f>
-        <v/>
-      </c>
-      <c r="O45" s="11" t="inlineStr">
+      <c r="N47" s="14">
+        <f>IF(M47="","",G47*M47)</f>
+        <v/>
+      </c>
+      <c r="O47" s="11" t="inlineStr">
         <is>
           <t>Between the rear wall and the board</t>
         </is>
       </c>
-      <c r="P45" s="11" t="inlineStr">
+      <c r="P47" s="11" t="inlineStr">
         <is>
           <t>Head/Rev4/README.md and Head/Rev3/README.md, Bought</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="B46" s="27" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="C46" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="26" t="n">
+      <c r="C48" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="E46" s="26">
-        <f>ROUNDUP(C46*$C$3/D46,0)</f>
-        <v/>
-      </c>
-      <c r="F46" s="28" t="n">
+      <c r="E48" s="26">
+        <f>ROUNDUP(C48*$C$3/D48,0)</f>
+        <v/>
+      </c>
+      <c r="F48" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="26">
-        <f>MAX(0,E46-F46)</f>
-        <v/>
-      </c>
-      <c r="H46" s="27" t="inlineStr">
+      <c r="G48" s="26">
+        <f>MAX(0,E48-F48)</f>
+        <v/>
+      </c>
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>Pen spring, 4 mm OD x 50 mm, 0.4 mm wire, pack of 10</t>
         </is>
       </c>
-      <c r="I46" s="27" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>uxcell</t>
         </is>
       </c>
-      <c r="J46" s="27" t="inlineStr"/>
-      <c r="K46" s="27" t="inlineStr">
+      <c r="J48" s="27" t="inlineStr"/>
+      <c r="K48" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L46" s="29" t="inlineStr">
+      <c r="L48" s="29" t="inlineStr">
         <is>
           <t>B0GCZGNBYH</t>
         </is>
       </c>
-      <c r="M46" s="30" t="n">
+      <c r="M48" s="30" t="n">
         <v>6.99</v>
       </c>
-      <c r="N46" s="30">
-        <f>IF(M46="","",G46*M46)</f>
-        <v/>
-      </c>
-      <c r="O46" s="27" t="inlineStr">
+      <c r="N48" s="30">
+        <f>IF(M48="","",G48*M48)</f>
+        <v/>
+      </c>
+      <c r="O48" s="27" t="inlineStr">
         <is>
           <t>Trigger return: cut to about 13 mm</t>
         </is>
       </c>
-      <c r="P46" s="27" t="inlineStr">
+      <c r="P48" s="27" t="inlineStr">
         <is>
           <t>Head/Rev4/README.md and Head/Rev3/README.md, Bought; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="B47" s="27" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>Head box</t>
         </is>
       </c>
-      <c r="C47" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="26">
-        <f>ROUNDUP(C47*$C$3/D47,0)</f>
-        <v/>
-      </c>
-      <c r="F47" s="28" t="n">
+      <c r="C49" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="26">
+        <f>ROUNDUP(C49*$C$3/D49,0)</f>
+        <v/>
+      </c>
+      <c r="F49" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="26">
-        <f>MAX(0,E47-F47)</f>
-        <v/>
-      </c>
-      <c r="H47" s="27" t="inlineStr">
+      <c r="G49" s="26">
+        <f>MAX(0,E49-F49)</f>
+        <v/>
+      </c>
+      <c r="H49" s="27" t="inlineStr">
         <is>
           <t>Ballast: lead split shot fishing weights, assorted, 120 pcs</t>
         </is>
       </c>
-      <c r="I47" s="27" t="inlineStr">
+      <c r="I49" s="27" t="inlineStr">
         <is>
           <t>SANWEAL</t>
         </is>
       </c>
-      <c r="J47" s="27" t="inlineStr"/>
-      <c r="K47" s="27" t="inlineStr">
+      <c r="J49" s="27" t="inlineStr"/>
+      <c r="K49" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L47" s="29" t="inlineStr">
+      <c r="L49" s="29" t="inlineStr">
         <is>
           <t>B0H6J3X6GL</t>
         </is>
       </c>
-      <c r="M47" s="30" t="n">
+      <c r="M49" s="30" t="n">
         <v>5.99</v>
       </c>
-      <c r="N47" s="30">
-        <f>IF(M47="","",G47*M47)</f>
-        <v/>
-      </c>
-      <c r="O47" s="27" t="inlineStr">
+      <c r="N49" s="30">
+        <f>IF(M49="","",G49*M49)</f>
+        <v/>
+      </c>
+      <c r="O49" s="27" t="inlineStr">
         <is>
           <t>Only if the gas strut lifts too much: about 48 g for a 45 N strut. Close to the middle of the box. Weigh out what you need</t>
         </is>
       </c>
-      <c r="P47" s="27" t="inlineStr">
+      <c r="P49" s="27" t="inlineStr">
         <is>
           <t>Base/README.md, Bought parts; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="M48" s="3" t="inlineStr">
+    <row r="50">
+      <c r="M50" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N48" s="15">
-        <f>SUM(N38:N47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="N50" s="15">
+        <f>SUM(N38:N49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>MkIII base Rev 3 (concept, not yet printed)</t>
         </is>
       </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="8" t="n"/>
-      <c r="L49" s="8" t="n"/>
-      <c r="M49" s="8" t="n"/>
-      <c r="N49" s="8" t="n"/>
-      <c r="O49" s="8" t="n"/>
-      <c r="P49" s="9" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
+      <c r="N51" s="8" t="n"/>
+      <c r="O51" s="8" t="n"/>
+      <c r="P51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>Pivot</t>
         </is>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C52" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D52" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E50" s="10">
-        <f>ROUNDUP(C50*$C$3/D50,0)</f>
-        <v/>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="10">
-        <f>MAX(0,E50-F50)</f>
-        <v/>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="E52" s="10">
+        <f>ROUNDUP(C52*$C$3/D52,0)</f>
+        <v/>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="10">
+        <f>MAX(0,E52-F52)</f>
+        <v/>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>Deep-groove ball bearing 6006-2RS, 30 x 55 x 13 mm</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr">
+      <c r="I52" s="11" t="inlineStr">
         <is>
           <t>BlueStars</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr">
+      <c r="J52" s="11" t="inlineStr">
         <is>
           <t>6006-2RS</t>
         </is>
       </c>
-      <c r="K50" s="11" t="inlineStr">
+      <c r="K52" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L50" s="13" t="inlineStr">
+      <c r="L52" s="13" t="inlineStr">
         <is>
           <t>B09XTV8XYK</t>
         </is>
       </c>
-      <c r="M50" s="14" t="n">
+      <c r="M52" s="14" t="n">
         <v>8.99</v>
       </c>
-      <c r="N50" s="14">
-        <f>IF(M50="","",G50*M50)</f>
-        <v/>
-      </c>
-      <c r="O50" s="11" t="inlineStr">
+      <c r="N52" s="14">
+        <f>IF(M52="","",G52*M52)</f>
+        <v/>
+      </c>
+      <c r="O52" s="11" t="inlineStr">
         <is>
           <t>Sold in pairs</t>
         </is>
       </c>
-      <c r="P50" s="11" t="inlineStr">
+      <c r="P52" s="11" t="inlineStr">
         <is>
           <t>Amazon listing on 2026-10-22 (link you sent); Base/mk3_pivot.py (the Rev 1 parts Rev 3 keeps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>Tube</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E51" s="10">
-        <f>ROUNDUP(C51*$C$3/D51,0)</f>
-        <v/>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="10">
-        <f>MAX(0,E51-F51)</f>
-        <v/>
-      </c>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>Carbon fibre tube, 25 mm OD x 23 mm ID, 500 mm, 3K plain weave, wrapped</t>
-        </is>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>MECCANIXITY</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="inlineStr"/>
-      <c r="K51" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L51" s="13" t="inlineStr">
-        <is>
-          <t>B0CFFT1B31</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="n">
-        <v>27.49</v>
-      </c>
-      <c r="N51" s="14">
-        <f>IF(M51="","",G51*M51)</f>
-        <v/>
-      </c>
-      <c r="O51" s="11" t="inlineStr">
-        <is>
-          <t>Sold in pairs. Wrapped, as the base needs (not pultruded). Cut to 483 mm (470 + the head's extra 12.7 mm of bore). Drill the M4 lock-screw hole 30.5 mm from the bottom end and the head's 5.2 mm cross hole 10 mm below the top end. Check the socket and head fits with it (coupons)</t>
-        </is>
-      </c>
-      <c r="P51" s="11" t="inlineStr">
-        <is>
-          <t>Amazon listing on 2026-10-22 (link you sent); Base/README.md, Bought parts</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="21" t="n">
-        <v>34</v>
-      </c>
-      <c r="B52" s="22" t="inlineStr">
-        <is>
-          <t>Lever halves</t>
-        </is>
-      </c>
-      <c r="C52" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D52" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="21">
-        <f>ROUNDUP(C52*$C$3/D52,0)</f>
-        <v/>
-      </c>
-      <c r="F52" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="21">
-        <f>MAX(0,E52-F52)</f>
-        <v/>
-      </c>
-      <c r="H52" s="22" t="inlineStr">
-        <is>
-          <t>M4 x 20 countersunk screw + M4 hex nut</t>
-        </is>
-      </c>
-      <c r="I52" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J52" s="22" t="inlineStr"/>
-      <c r="K52" s="22" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L52" s="24" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M52" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="25">
-        <f>IF(M52="","",G52*M52)</f>
-        <v/>
-      </c>
-      <c r="O52" s="22" t="inlineStr">
-        <is>
-          <t>In the screw kit. From the top, the heads 16 mm down their counterbores (a long 2.5 mm hex key helps); the nuts go in the lower half's pockets first</t>
-        </is>
-      </c>
-      <c r="P52" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Strut</t>
+          <t>Tube</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Gas strut, 6 in (152.4 mm eye to eye), 45 N (sold as 9-12 lb), flat eyelet tabs</t>
+          <t>Carbon fibre tube, 25 mm OD x 23 mm ID, 500 mm, 3K plain weave, wrapped</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>X AUTOHAUX</t>
+          <t>MECCANIXITY</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr"/>
@@ -3317,11 +3317,11 @@
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>B0CY267GFY</t>
+          <t>B0CFFT1B31</t>
         </is>
       </c>
       <c r="M53" s="14" t="n">
-        <v>13.69</v>
+        <v>27.49</v>
       </c>
       <c r="N53" s="14">
         <f>IF(M53="","",G53*M53)</f>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>Sold in pairs: the spare is the other half</t>
+          <t>Sold in pairs. Wrapped, as the base needs (not pultruded). Cut to 491 mm (470 + the head's extra 12.7 mm of bore + 8 mm for the base's deeper socket). Drill the M4 lock-screw hole 38.5 mm from the bottom end and the head's 5.2 mm cross hole 10 mm below the top end. Check the socket and head fits with it (coupons)</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
         <is>
-          <t>Base/README.md, Bought parts</t>
+          <t>Amazon listing on 2026-10-22 (link you sent); Base/README.md, Bought parts</t>
         </is>
       </c>
     </row>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>Strut eyes</t>
+          <t>Lever halves</t>
         </is>
       </c>
       <c r="C54" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D54" s="21" t="n">
         <v>1</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="H54" s="22" t="inlineStr">
         <is>
-          <t>M4 x 16 countersunk screw + M4 hex nut</t>
+          <t>M4 x 20 countersunk screw + M4 hex nut</t>
         </is>
       </c>
       <c r="I54" s="22" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O54" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. One per eye: head on +y, nut in the -y cheek's pocket. The listing gives the strut's eye holes as 4 mm. Snug, then thread-lock: the eye must still turn</t>
+          <t>In the screw kit. From the top, the heads 16 mm down their counterbores (a long 2.5 mm hex key helps); the nuts go in the lower half's pockets first</t>
         </is>
       </c>
       <c r="P54" s="22" t="inlineStr">
@@ -3404,67 +3404,67 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="21" t="n">
+      <c r="A55" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>Strut collar</t>
-        </is>
-      </c>
-      <c r="C55" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="21">
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Strut</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="10">
         <f>ROUNDUP(C55*$C$3/D55,0)</f>
         <v/>
       </c>
-      <c r="F55" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="21">
+      <c r="F55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="10">
         <f>MAX(0,E55-F55)</f>
         <v/>
       </c>
-      <c r="H55" s="22" t="inlineStr">
-        <is>
-          <t>M4 x 12 countersunk screw + M4 hex nut</t>
-        </is>
-      </c>
-      <c r="I55" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J55" s="22" t="inlineStr"/>
-      <c r="K55" s="22" t="inlineStr">
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Gas strut, 6 in (152.4 mm eye to eye), 45 N (sold as 9-12 lb), flat eyelet tabs</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>X AUTOHAUX</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr"/>
+      <c r="K55" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L55" s="24" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M55" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="25">
+      <c r="L55" s="13" t="inlineStr">
+        <is>
+          <t>B0CY267GFY</t>
+        </is>
+      </c>
+      <c r="M55" s="14" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="N55" s="14">
         <f>IF(M55="","",G55*M55)</f>
         <v/>
       </c>
-      <c r="O55" s="22" t="inlineStr">
-        <is>
-          <t>In the screw kit. Collar clamp: the head sits 2 mm into the -y ear, the nut in the +y ear's pocket</t>
-        </is>
-      </c>
-      <c r="P55" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+      <c r="O55" s="11" t="inlineStr">
+        <is>
+          <t>Sold in pairs: the spare is the other half</t>
+        </is>
+      </c>
+      <c r="P55" s="11" t="inlineStr">
+        <is>
+          <t>Base/README.md, Bought parts</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>Down-stops</t>
+          <t>Strut eyes</t>
         </is>
       </c>
       <c r="C56" s="21" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H56" s="22" t="inlineStr">
         <is>
-          <t>M4 x 16 countersunk screw + 2 M4 hex nuts</t>
+          <t>M4 x 16 countersunk screw + M4 hex nut</t>
         </is>
       </c>
       <c r="I56" s="22" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="O56" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. Head up: its flat top is the stop. One nut pressed into the post's top pocket, the second on top of it locks the height that levels the tube</t>
+          <t>In the screw kit. One per eye: head on +y, nut in the -y cheek's pocket. The listing gives the strut's eye holes as 4 mm. Snug, then thread-lock: the eye must still turn</t>
         </is>
       </c>
       <c r="P56" s="22" t="inlineStr">
@@ -3539,11 +3539,11 @@
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>Pillow-block caps</t>
+          <t>Strut collar</t>
         </is>
       </c>
       <c r="C57" s="21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D57" s="21" t="n">
         <v>1</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H57" s="22" t="inlineStr">
         <is>
-          <t>M4 x 20 countersunk screw + M4 hex nut</t>
+          <t>M4 x 12 countersunk screw + M4 hex nut</t>
         </is>
       </c>
       <c r="I57" s="22" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="O57" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. Two per cap, from the top; each nut slides into a slot in the block's front or back face. Length from the CAD</t>
+          <t>In the screw kit. Collar clamp: the head sits 2 mm into the -y ear, the nut in the +y ear's pocket</t>
         </is>
       </c>
       <c r="P57" s="22" t="inlineStr">
@@ -3604,11 +3604,11 @@
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>Side covers</t>
+          <t>Down-stops</t>
         </is>
       </c>
       <c r="C58" s="21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D58" s="21" t="n">
         <v>1</v>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H58" s="22" t="inlineStr">
         <is>
-          <t>M3 x 20 countersunk screw</t>
+          <t>M4 x 16 countersunk screw + 2 M4 hex nuts</t>
         </is>
       </c>
       <c r="I58" s="22" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="O58" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. Four per cover, from its outer face into M3 threads tapped 7 mm deep in the block and cap. Length from the CAD</t>
+          <t>In the screw kit. Head up: its flat top is the stop. One nut pressed into the post's top pocket, the second on top of it locks the height that levels the tube</t>
         </is>
       </c>
       <c r="P58" s="22" t="inlineStr">
@@ -3669,11 +3669,11 @@
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>Cable plug</t>
+          <t>Pillow-block caps</t>
         </is>
       </c>
       <c r="C59" s="21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D59" s="21" t="n">
         <v>1</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="H59" s="22" t="inlineStr">
         <is>
-          <t>M2 x 12 countersunk screw</t>
+          <t>M4 x 20 countersunk screw + M4 hex nut</t>
         </is>
       </c>
       <c r="I59" s="22" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O59" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. Up from under the cable cover's rim, through a clearance hole, into an M2 thread tapped in the plug (1.6 mm pilot): pulls the plug that closes the cable's slot down onto the cover's shoulders. Length from the CAD</t>
+          <t>In the screw kit. Two per cap, from the top; each nut slides into a slot in the block's front or back face. Length from the CAD</t>
         </is>
       </c>
       <c r="P59" s="22" t="inlineStr">
@@ -3729,67 +3729,69 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="21" t="n">
+      <c r="A60" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="B60" s="22" t="inlineStr">
-        <is>
-          <t>Tube lock</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="21">
-        <f>ROUNDUP(C60*$C$3/D60,0)</f>
-        <v/>
-      </c>
-      <c r="F60" s="23" t="n">
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Side covers</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="E60" s="10">
+        <f>IF($C$3&gt;0,C60,0)</f>
+        <v/>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="10">
+        <f>MAX(0,E60-F60)</f>
+        <v/>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>M3 x 25 countersunk screw (from the M3 x 20-40 set, ASIN B0BYXS4BTF)</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr"/>
+      <c r="K60" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L60" s="13" t="inlineStr">
+        <is>
+          <t>B0BYXS4BTF</t>
+        </is>
+      </c>
+      <c r="M60" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="21">
-        <f>MAX(0,E60-F60)</f>
-        <v/>
-      </c>
-      <c r="H60" s="22" t="inlineStr">
-        <is>
-          <t>M4 x 6 set screw</t>
-        </is>
-      </c>
-      <c r="I60" s="22" t="inlineStr">
-        <is>
-          <t>HIQTRADEBYJJ</t>
-        </is>
-      </c>
-      <c r="J60" s="22" t="inlineStr"/>
-      <c r="K60" s="22" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L60" s="24" t="inlineStr">
-        <is>
-          <t>B0DG33R714</t>
-        </is>
-      </c>
-      <c r="M60" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="25">
+      <c r="N60" s="14">
         <f>IF(M60="","",G60*M60)</f>
         <v/>
       </c>
-      <c r="O60" s="22" t="inlineStr">
-        <is>
-          <t>In the set screw kit. Tap the socket boss's 3.3 mm pilot M4; the tip goes into the tube's 4 mm lock hole, 30.5 mm from its bottom end</t>
-        </is>
-      </c>
-      <c r="P60" s="22" t="inlineStr">
-        <is>
-          <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+      <c r="O60" s="11" t="inlineStr">
+        <is>
+          <t>From the same 100-piece set as the trigger pivot (20 of each length). Four per cover, from its outer face into M3 threads tapped 11 mm deep in the block and cap: 10 mm of thread, three times the 20 mm screw's. The kit's M3 x 20 would only reach 5</t>
+        </is>
+      </c>
+      <c r="P60" s="11" t="inlineStr">
+        <is>
+          <t>Base/README.md, Bought parts; user's M3 set 2026-10-24; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3801,7 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>Friction knob</t>
+          <t>Cable plug</t>
         </is>
       </c>
       <c r="C61" s="21" t="n">
@@ -3821,7 +3823,7 @@
       </c>
       <c r="H61" s="22" t="inlineStr">
         <is>
-          <t>M5 x 20 countersunk screw + M5 hex nut</t>
+          <t>M2 x 12 countersunk screw</t>
         </is>
       </c>
       <c r="I61" s="22" t="inlineStr">
@@ -3849,7 +3851,7 @@
       </c>
       <c r="O61" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. Glue the head into the printed knob (Base/stl/friction_knob.stl); the screw goes through the spring and the shoe into the nut, slid into the knob tower's slot from the front. Length from the CAD</t>
+          <t>In the screw kit. Up from under the cable cover's rim, through a clearance hole, into an M2 thread tapped in the plug (1.6 mm pilot): pulls the plug that closes the cable's slot down onto the cover's shoulders. Length from the CAD</t>
         </is>
       </c>
       <c r="P61" s="22" t="inlineStr">
@@ -3864,7 +3866,7 @@
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>Shoe hinge</t>
+          <t>Tube lock</t>
         </is>
       </c>
       <c r="C62" s="21" t="n">
@@ -3886,12 +3888,12 @@
       </c>
       <c r="H62" s="22" t="inlineStr">
         <is>
-          <t>M4 x 20 countersunk screw + M4 hex nut</t>
+          <t>M4 x 6 set screw</t>
         </is>
       </c>
       <c r="I62" s="22" t="inlineStr">
         <is>
-          <t>AvrestYPT</t>
+          <t>HIQTRADEBYJJ</t>
         </is>
       </c>
       <c r="J62" s="22" t="inlineStr"/>
@@ -3902,7 +3904,7 @@
       </c>
       <c r="L62" s="24" t="inlineStr">
         <is>
-          <t>B0FMD5TMSH</t>
+          <t>B0DG33R714</t>
         </is>
       </c>
       <c r="M62" s="25" t="n">
@@ -3914,181 +3916,177 @@
       </c>
       <c r="O62" s="22" t="inlineStr">
         <is>
+          <t>In the set screw kit. Tap the socket boss's 3.3 mm pilot M4; the tip goes into the tube's 4 mm lock hole, 38.5 mm from its bottom end</t>
+        </is>
+      </c>
+      <c r="P62" s="22" t="inlineStr">
+        <is>
+          <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>Friction knob</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="21">
+        <f>ROUNDUP(C63*$C$3/D63,0)</f>
+        <v/>
+      </c>
+      <c r="F63" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="21">
+        <f>MAX(0,E63-F63)</f>
+        <v/>
+      </c>
+      <c r="H63" s="22" t="inlineStr">
+        <is>
+          <t>M5 x 20 countersunk screw + M5 hex nut</t>
+        </is>
+      </c>
+      <c r="I63" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT</t>
+        </is>
+      </c>
+      <c r="J63" s="22" t="inlineStr"/>
+      <c r="K63" s="22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L63" s="24" t="inlineStr">
+        <is>
+          <t>B0FMD5TMSH</t>
+        </is>
+      </c>
+      <c r="M63" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="25">
+        <f>IF(M63="","",G63*M63)</f>
+        <v/>
+      </c>
+      <c r="O63" s="22" t="inlineStr">
+        <is>
+          <t>In the screw kit. Glue the head into the printed knob (Base/stl/friction_knob.stl); the screw goes through the spring and the shoe into the nut, slid into the knob tower's slot from the front. Length from the CAD</t>
+        </is>
+      </c>
+      <c r="P63" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>Shoe hinge</t>
+        </is>
+      </c>
+      <c r="C64" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="21">
+        <f>ROUNDUP(C64*$C$3/D64,0)</f>
+        <v/>
+      </c>
+      <c r="F64" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="21">
+        <f>MAX(0,E64-F64)</f>
+        <v/>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t>M4 x 20 countersunk screw + M4 hex nut</t>
+        </is>
+      </c>
+      <c r="I64" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT</t>
+        </is>
+      </c>
+      <c r="J64" s="22" t="inlineStr"/>
+      <c r="K64" s="22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L64" s="24" t="inlineStr">
+        <is>
+          <t>B0FMD5TMSH</t>
+        </is>
+      </c>
+      <c r="M64" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="25">
+        <f>IF(M64="","",G64*M64)</f>
+        <v/>
+      </c>
+      <c r="O64" s="22" t="inlineStr">
+        <is>
           <t>In the screw kit. Hinge pin through both frame lugs and the shoe's eye: head in the -y lug, nut in the +y lug's pocket (the lugs are 20 mm apart outside). Snug, then thread-lock: the shoe must still swing</t>
         </is>
       </c>
-      <c r="P62" s="22" t="inlineStr">
+      <c r="P64" s="22" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="M63" s="3" t="inlineStr">
+    <row r="65">
+      <c r="M65" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N63" s="15">
-        <f>SUM(N50:N62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="N65" s="15">
+        <f>SUM(N52:N64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>Kits, consumables and tools</t>
         </is>
       </c>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
-      <c r="L64" s="8" t="n"/>
-      <c r="M64" s="8" t="n"/>
-      <c r="N64" s="8" t="n"/>
-      <c r="O64" s="8" t="n"/>
-      <c r="P64" s="9" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>once</t>
-        </is>
-      </c>
-      <c r="E65" s="10">
-        <f>IF($C$3&gt;0,C65,0)</f>
-        <v/>
-      </c>
-      <c r="F65" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="10">
-        <f>MAX(0,E65-F65)</f>
-        <v/>
-      </c>
-      <c r="H65" s="11" t="inlineStr">
-        <is>
-          <t>Screw kit, 1715 pieces: countersunk hex-socket screws M2-M4 x 8, 12, 16, 20 and M5 x 10, 12, 16, 20, with hex nuts and washers, hex keys</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J65" s="11" t="inlineStr"/>
-      <c r="K65" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L65" s="13" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M65" s="14" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="N65" s="14">
-        <f>IF(M65="","",G65*M65)</f>
-        <v/>
-      </c>
-      <c r="O65" s="11" t="inlineStr">
-        <is>
-          <t>Every countersunk screw and nut in the head and base (the green lines). Used: M3 x 12 (12), M3 x 20 (8), M4 x 12 (2), M4 x 16 (4), M4 x 20 (9), M5 x 20 (1); nuts M3 (4), M4 (17), M5 (1). Your order (link 2026-10-23)</t>
-        </is>
-      </c>
-      <c r="P65" s="11" t="inlineStr">
-        <is>
-          <t>Amazon listing 2026-10-23 (your order)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>once</t>
-        </is>
-      </c>
-      <c r="E66" s="10">
-        <f>IF($C$3&gt;0,C66,0)</f>
-        <v/>
-      </c>
-      <c r="F66" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="10">
-        <f>MAX(0,E66-F66)</f>
-        <v/>
-      </c>
-      <c r="H66" s="11" t="inlineStr">
-        <is>
-          <t>Set screw kit, 500 pieces, 304 stainless: M3 x 3, 4, 5, 6; M4 x 4, 5, 6; M5 x 5, 8; M6 x 6, 10; M8 x 8; hex keys</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>HIQTRADEBYJJ</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr"/>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L66" s="13" t="inlineStr">
-        <is>
-          <t>B0DG33R714</t>
-        </is>
-      </c>
-      <c r="M66" s="14" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="N66" s="14">
-        <f>IF(M66="","",G66*M66)</f>
-        <v/>
-      </c>
-      <c r="O66" s="11" t="inlineStr">
-        <is>
-          <t>The set screws: M5 x 8 (tube, head), M3 x 4 (trigger pull stop), M4 x 6 (tube lock, base). Your order (link 2026-10-23)</t>
-        </is>
-      </c>
-      <c r="P66" s="11" t="inlineStr">
-        <is>
-          <t>Amazon listing 2026-10-23 (your order)</t>
-        </is>
-      </c>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="8" t="n"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="8" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
+      <c r="L66" s="8" t="n"/>
+      <c r="M66" s="8" t="n"/>
+      <c r="N66" s="8" t="n"/>
+      <c r="O66" s="8" t="n"/>
+      <c r="P66" s="9" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="n">
@@ -4096,7 +4094,7 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
@@ -4120,12 +4118,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>White lithium grease, 1.5 oz tube</t>
+          <t>Screw kit, 1715 pieces: countersunk hex-socket screws M2-M4 x 8, 12, 16, 20 and M5 x 10, 12, 16, 20, with hex nuts and washers, hex keys</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>Permatex</t>
+          <t>AvrestYPT</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr"/>
@@ -4136,11 +4134,11 @@
       </c>
       <c r="L67" s="13" t="inlineStr">
         <is>
-          <t>B000HBNV58</t>
+          <t>B0FMD5TMSH</t>
         </is>
       </c>
       <c r="M67" s="14" t="n">
-        <v>3.99</v>
+        <v>17.99</v>
       </c>
       <c r="N67" s="14">
         <f>IF(M67="","",G67*M67)</f>
@@ -4148,12 +4146,12 @@
       </c>
       <c r="O67" s="11" t="inlineStr">
         <is>
-          <t>Bearing grease (not silicone paste)</t>
+          <t>Every countersunk screw and nut in the head and base (the green lines). Used: M3 x 12 (12), M3 x 20 (8), M4 x 12 (2), M4 x 16 (4), M4 x 20 (9), M5 x 20 (1); nuts M3 (4), M4 (17), M5 (1). Your order (link 2026-10-23)</t>
         </is>
       </c>
       <c r="P67" s="11" t="inlineStr">
         <is>
-          <t>Head/Rev4/README.md; Base/README.md; Amazon listing 2026-10-23</t>
+          <t>Amazon listing 2026-10-23 (your order)</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4161,7 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
@@ -4187,12 +4185,12 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>Silicone faucet grease, waterproof, 0.5 oz</t>
+          <t>Set screw kit, 500 pieces, 304 stainless: M3 x 3, 4, 5, 6; M4 x 4, 5, 6; M5 x 5, 8; M6 x 6, 10; M8 x 8; hex keys</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>Danco</t>
+          <t>HIQTRADEBYJJ</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr"/>
@@ -4203,11 +4201,11 @@
       </c>
       <c r="L68" s="13" t="inlineStr">
         <is>
-          <t>B000DZFUPC</t>
+          <t>B0DG33R714</t>
         </is>
       </c>
       <c r="M68" s="14" t="n">
-        <v>5.68</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N68" s="14">
         <f>IF(M68="","",G68*M68)</f>
@@ -4215,12 +4213,12 @@
       </c>
       <c r="O68" s="11" t="inlineStr">
         <is>
-          <t>For the head's four throttle O-rings (grease them lightly before fitting)</t>
+          <t>The set screws: M5 x 8 (tube, head), M3 x 4 (trigger pull stop), M4 x 6 (tube lock, base). Your order (link 2026-10-23)</t>
         </is>
       </c>
       <c r="P68" s="11" t="inlineStr">
         <is>
-          <t>Head/Rev4/README.md; Amazon listing 2026-10-23</t>
+          <t>Amazon listing 2026-10-23 (your order)</t>
         </is>
       </c>
     </row>
@@ -4254,31 +4252,27 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Solder paste, low-temperature (Sn42/Bi58, 138 C), syringe</t>
+          <t>White lithium grease, 1.5 oz tube</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>Chip Quik</t>
-        </is>
-      </c>
-      <c r="J69" s="11" t="inlineStr">
-        <is>
-          <t>NC191LT10</t>
-        </is>
-      </c>
+          <t>Permatex</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr"/>
       <c r="K69" s="11" t="inlineStr">
         <is>
-          <t>Digi-Key</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="L69" s="13" t="inlineStr">
         <is>
-          <t>315-NC191LT10-ND</t>
+          <t>B000HBNV58</t>
         </is>
       </c>
       <c r="M69" s="14" t="n">
-        <v>7.95</v>
+        <v>3.99</v>
       </c>
       <c r="N69" s="14">
         <f>IF(M69="","",G69*M69)</f>
@@ -4286,12 +4280,12 @@
       </c>
       <c r="O69" s="11" t="inlineStr">
         <is>
-          <t>For the SMD parts on the board (U1, U2, the 1206 caps, the JST headers, SW1-SW3). Needs a hot plate or hot air tool and flux. Optional: hand-soldering works too</t>
+          <t>Bearing grease (not silicone paste)</t>
         </is>
       </c>
       <c r="P69" s="11" t="inlineStr">
         <is>
-          <t>Digi-Key cart 2026-10-23</t>
+          <t>Head/Rev4/README.md; Base/README.md; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -4325,31 +4319,27 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>Tweezers, 1 mm tip (Olimex CHN-TWZ1MM), for placing the SMD parts</t>
+          <t>Silicone faucet grease, waterproof, 0.5 oz</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>Olimex</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr">
-        <is>
-          <t>CHN-TWZ1MM</t>
-        </is>
-      </c>
+          <t>Danco</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr"/>
       <c r="K70" s="11" t="inlineStr">
         <is>
-          <t>Digi-Key</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="L70" s="13" t="inlineStr">
         <is>
-          <t>1188-CHN-TWZ1MM-ND</t>
+          <t>B000DZFUPC</t>
         </is>
       </c>
       <c r="M70" s="14" t="n">
-        <v>0.82</v>
+        <v>5.68</v>
       </c>
       <c r="N70" s="14">
         <f>IF(M70="","",G70*M70)</f>
@@ -4357,61 +4347,203 @@
       </c>
       <c r="O70" s="11" t="inlineStr">
         <is>
+          <t>For the head's four throttle O-rings (grease them lightly before fitting)</t>
+        </is>
+      </c>
+      <c r="P70" s="11" t="inlineStr">
+        <is>
+          <t>Head/Rev4/README.md; Amazon listing 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="E71" s="10">
+        <f>IF($C$3&gt;0,C71,0)</f>
+        <v/>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="10">
+        <f>MAX(0,E71-F71)</f>
+        <v/>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>Solder paste, low-temperature (Sn42/Bi58, 138 C), syringe</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Chip Quik</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>NC191LT10</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L71" s="13" t="inlineStr">
+        <is>
+          <t>315-NC191LT10-ND</t>
+        </is>
+      </c>
+      <c r="M71" s="14" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="N71" s="14">
+        <f>IF(M71="","",G71*M71)</f>
+        <v/>
+      </c>
+      <c r="O71" s="11" t="inlineStr">
+        <is>
+          <t>For the SMD parts on the board (U1, U2, the 1206 caps, the JST headers, SW1-SW3). Needs a hot plate or hot air tool and flux. Optional: hand-soldering works too</t>
+        </is>
+      </c>
+      <c r="P71" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key cart 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="E72" s="10">
+        <f>IF($C$3&gt;0,C72,0)</f>
+        <v/>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="10">
+        <f>MAX(0,E72-F72)</f>
+        <v/>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>Tweezers, 1 mm tip (Olimex CHN-TWZ1MM), for placing the SMD parts</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Olimex</t>
+        </is>
+      </c>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>CHN-TWZ1MM</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L72" s="13" t="inlineStr">
+        <is>
+          <t>1188-CHN-TWZ1MM-ND</t>
+        </is>
+      </c>
+      <c r="M72" s="14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N72" s="14">
+        <f>IF(M72="","",G72*M72)</f>
+        <v/>
+      </c>
+      <c r="O72" s="11" t="inlineStr">
+        <is>
           <t>Description from Olimex's sibling CHN-TWZ2MM listing: check the tip</t>
         </is>
       </c>
-      <c r="P70" s="11" t="inlineStr">
+      <c r="P72" s="11" t="inlineStr">
         <is>
           <t>Digi-Key order 102438510</t>
         </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="N71" s="15">
-        <f>SUM(N65:N70)</f>
-        <v/>
       </c>
     </row>
     <row r="73">
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>Still to buy</t>
+          <t>Subtotal</t>
         </is>
       </c>
       <c r="N73" s="15">
-        <f>N16+N20+N26+N29+N36+N48+N63+N71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>Whole build</t>
-        </is>
-      </c>
-      <c r="N74" s="15">
-        <f>SUMPRODUCT(E6:E71,M6:M71)</f>
+        <f>SUM(N67:N72)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="M75" s="3" t="inlineStr">
         <is>
+          <t>Still to buy</t>
+        </is>
+      </c>
+      <c r="N75" s="15">
+        <f>N16+N20+N26+N29+N36+N50+N65+N73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Whole build</t>
+        </is>
+      </c>
+      <c r="N76" s="15">
+        <f>SUMPRODUCT(E6:E73,M6:M73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="M77" s="3" t="inlineStr">
+        <is>
           <t>Unpriced lines</t>
         </is>
       </c>
-      <c r="N75" s="3">
-        <f>COUNTIFS(A6:A71,"&gt;0",M6:M71,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="N77" s="3">
+        <f>COUNTIFS(A6:A73,"&gt;0",M6:M73,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>Still to buy counts the packs to order; whole build counts every pack needed, bought or not. Both leave out the unpriced lines: generic hardware and wire.</t>
         </is>
@@ -4419,16 +4551,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A49:P49"/>
-    <mergeCell ref="A76:P76"/>
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="A66:P66"/>
     <mergeCell ref="A17:P17"/>
     <mergeCell ref="A37:P37"/>
     <mergeCell ref="A27:P27"/>
     <mergeCell ref="A6:P6"/>
     <mergeCell ref="D3:P3"/>
     <mergeCell ref="A30:P30"/>
+    <mergeCell ref="A78:P78"/>
     <mergeCell ref="A21:P21"/>
-    <mergeCell ref="A64:P64"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
@@ -4464,8 +4596,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId36"/>
@@ -4477,12 +4609,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5322,7 +5456,7 @@
       </c>
       <c r="I22" s="27" t="inlineStr">
         <is>
-          <t>SEARCH CONT hat (4) and starter trigger (1). IN8, IN15, IN16 are spare</t>
+          <t>SEARCH CONT hat (4, new rocker hat) and starter trigger (1). IN8, IN15, IN16 are spare</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5470,7 @@
         </is>
       </c>
       <c r="C23" s="26">
-        <f>'Final BOM'!G45</f>
+        <f>'Final BOM'!G47</f>
         <v/>
       </c>
       <c r="D23" s="27" t="inlineStr">
@@ -5355,11 +5489,11 @@
         </is>
       </c>
       <c r="G23" s="30">
-        <f>'Final BOM'!M45</f>
+        <f>'Final BOM'!M47</f>
         <v/>
       </c>
       <c r="H23" s="30">
-        <f>IF('Final BOM'!M45="","",C23*G23)</f>
+        <f>IF('Final BOM'!M47="","",C23*G23)</f>
         <v/>
       </c>
       <c r="I23" s="27" t="inlineStr">
@@ -5378,7 +5512,7 @@
         </is>
       </c>
       <c r="C24" s="26">
-        <f>'Final BOM'!G69</f>
+        <f>'Final BOM'!G71</f>
         <v/>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -5397,11 +5531,11 @@
         </is>
       </c>
       <c r="G24" s="30">
-        <f>'Final BOM'!M69</f>
+        <f>'Final BOM'!M71</f>
         <v/>
       </c>
       <c r="H24" s="30">
-        <f>IF('Final BOM'!M69="","",C24*G24)</f>
+        <f>IF('Final BOM'!M71="","",C24*G24)</f>
         <v/>
       </c>
       <c r="I24" s="27" t="inlineStr">
@@ -5420,7 +5554,7 @@
         </is>
       </c>
       <c r="C25" s="26">
-        <f>'Final BOM'!G70</f>
+        <f>'Final BOM'!G72</f>
         <v/>
       </c>
       <c r="D25" s="27" t="inlineStr">
@@ -5439,11 +5573,11 @@
         </is>
       </c>
       <c r="G25" s="30">
-        <f>'Final BOM'!M70</f>
+        <f>'Final BOM'!M72</f>
         <v/>
       </c>
       <c r="H25" s="30">
-        <f>IF('Final BOM'!M70="","",C25*G25)</f>
+        <f>IF('Final BOM'!M72="","",C25*G25)</f>
         <v/>
       </c>
       <c r="I25" s="27" t="inlineStr">
@@ -5509,7 +5643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5732,7 +5866,7 @@
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-SearchHat.stl</t>
+          <t>Head/Rev4/stl/HueyHeadR4-Hat-Cap.stl</t>
         </is>
       </c>
       <c r="D12" s="26" t="n">
@@ -5740,7 +5874,7 @@
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>On its flat bottom ring</t>
+          <t>Base down. Glue it onto the rocker plate's four legs, last</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5889,7 @@
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>MkII original: 4way_Cover.stl, Bezel.stl, StickRetainer.stl, one ThumbStick-*.stl</t>
+          <t>Head/Rev4/stl/HueyHeadR4-Hat-RockerPlate.stl</t>
         </is>
       </c>
       <c r="D13" s="26" t="n">
@@ -5763,7 +5897,7 @@
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>The 4-way hat's parts, from the Thingiverse 5226353 head files (not in this folder). The ThumbStick comes in 4.5 to 5.8 mm, set by the switch's height: the TE 1825910-6 is 5.0 mm to the top of its button (datasheet), so print the 4.8 and the 5.3 and keep the one that clicks cleanly with no preload</t>
+          <t>Legs down on the bed, boss up; the legs are part of it</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5912,7 @@
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-ThrottleGrip.stl</t>
+          <t>Head/Rev4/stl/HueyHeadR4-Hat-Bezel.stl</t>
         </is>
       </c>
       <c r="D14" s="26" t="n">
@@ -5786,7 +5920,7 @@
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>Upright, bottom end down; no supports</t>
+          <t>Front face down</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5935,7 @@
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-FrictionCollar.stl</t>
+          <t>Head/Rev4/stl/HueyHeadR4-ThrottleGrip.stl</t>
         </is>
       </c>
       <c r="D15" s="26" t="n">
@@ -5809,7 +5943,7 @@
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>Bottom face down, O-ring groove up</t>
+          <t>Upright, bottom end down; no supports</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5958,7 @@
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-Pinion.stl</t>
+          <t>Head/Rev4/stl/HueyHeadR4-FrictionCollar.stl</t>
         </is>
       </c>
       <c r="D16" s="26" t="n">
@@ -5832,7 +5966,7 @@
       </c>
       <c r="E16" s="27" t="inlineStr">
         <is>
-          <t>Flat; the magnet shaft presses into its hex</t>
+          <t>Bottom face down, O-ring groove up</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5981,7 @@
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-MagnetShaft.stl</t>
+          <t>Head/Rev4/stl/HueyHeadR4-Pinion.stl</t>
         </is>
       </c>
       <c r="D17" s="26" t="n">
@@ -5855,7 +5989,7 @@
       </c>
       <c r="E17" s="27" t="inlineStr">
         <is>
-          <t>Cap face down, pin up</t>
+          <t>Flat; the magnet shaft presses into its hex</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5999,12 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Head</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>Base/stl/coupons/coupon_trunnion.stl, coupon_bearing_seat.stl, coupon_tube_socket.stl</t>
+          <t>Head/Rev4/stl/HueyHeadR4-MagnetShaft.stl</t>
         </is>
       </c>
       <c r="D18" s="26" t="n">
@@ -5878,7 +6012,7 @@
       </c>
       <c r="E18" s="27" t="inlineStr">
         <is>
-          <t>Fit-test coupons: print first and tune mk3_pivot.py (the socket with the carbon tube)</t>
+          <t>Cap face down, pin up</t>
         </is>
       </c>
     </row>
@@ -5893,7 +6027,7 @@
       </c>
       <c r="C19" s="27" t="inlineStr">
         <is>
-          <t>Base/stl/frame.stl</t>
+          <t>Base/stl/coupons/coupon_trunnion.stl, coupon_bearing_seat.stl, coupon_tube_socket.stl</t>
         </is>
       </c>
       <c r="D19" s="26" t="n">
@@ -5901,7 +6035,7 @@
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>Plate down</t>
+          <t>Fit-test coupons: print first and tune mk3_pivot.py (the socket with the carbon tube)</t>
         </is>
       </c>
     </row>
@@ -5916,7 +6050,7 @@
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>Base/stl/lever_lower.stl</t>
+          <t>Base/stl/frame.stl</t>
         </is>
       </c>
       <c r="D20" s="26" t="n">
@@ -5924,7 +6058,7 @@
       </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>On its joint face</t>
+          <t>Plate down</t>
         </is>
       </c>
     </row>
@@ -5939,7 +6073,7 @@
       </c>
       <c r="C21" s="27" t="inlineStr">
         <is>
-          <t>Base/stl/lever_upper.stl</t>
+          <t>Base/stl/lever_lower.stl</t>
         </is>
       </c>
       <c r="D21" s="26" t="n">
@@ -5962,7 +6096,7 @@
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>Base/stl/cap_left.stl, cap_right.stl</t>
+          <t>Base/stl/lever_upper.stl</t>
         </is>
       </c>
       <c r="D22" s="26" t="n">
@@ -5970,7 +6104,7 @@
       </c>
       <c r="E22" s="27" t="inlineStr">
         <is>
-          <t>One each</t>
+          <t>On its joint face</t>
         </is>
       </c>
     </row>
@@ -5985,7 +6119,7 @@
       </c>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>Base/stl/cover_cable.stl, cover_sensor.stl</t>
+          <t>Base/stl/cap_left.stl, cap_right.stl</t>
         </is>
       </c>
       <c r="D23" s="26" t="n">
@@ -6008,7 +6142,7 @@
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>Base/stl/cable_plug.stl</t>
+          <t>Base/stl/cover_cable.stl, cover_sensor.stl</t>
         </is>
       </c>
       <c r="D24" s="26" t="n">
@@ -6016,7 +6150,7 @@
       </c>
       <c r="E24" s="27" t="inlineStr">
         <is>
-          <t>On a long flat face. Fills the cable cover's slot once the USB cable is in</t>
+          <t>One each</t>
         </is>
       </c>
     </row>
@@ -6031,13 +6165,17 @@
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>Base/stl/sensor_carrier.stl</t>
+          <t>Base/stl/cable_plug.stl</t>
         </is>
       </c>
       <c r="D25" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="27" t="inlineStr"/>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>On a long flat face. Fills the cable cover's slot once the USB cable is in</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="26" t="n">
@@ -6050,7 +6188,7 @@
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>Base/stl/shoe.stl</t>
+          <t>Base/stl/sensor_carrier.stl</t>
         </is>
       </c>
       <c r="D26" s="26" t="n">
@@ -6069,17 +6207,13 @@
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>Base/stl/strut_collar.stl</t>
+          <t>Base/stl/shoe.stl</t>
         </is>
       </c>
       <c r="D27" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="27" t="inlineStr">
-        <is>
-          <t>Standing on one end</t>
-        </is>
-      </c>
+      <c r="E27" s="27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="26" t="n">
@@ -6092,13 +6226,36 @@
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
+          <t>Base/stl/strut_collar.stl</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>Standing on one end</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
           <t>Base/stl/friction_knob.stl</t>
         </is>
       </c>
-      <c r="D28" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="D29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>Top face down; glue the M5 x 20's head into it</t>
         </is>

--- a/BOM/Heli_Collective_Final_BOM.xlsx
+++ b/BOM/Heli_Collective_Final_BOM.xlsx
@@ -633,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="O38" s="22" t="inlineStr">
         <is>
-          <t>In the set screw kit. From the boss's front (lower panel off): tap the 4.2 mm pilot M5; the tip pins the tube through the front wall of its 5.2 mm cross hole, 10 mm below the tube's top. Replaces the M5 x 40 bolt and nut (the kit's M5s stop at 20 mm)</t>
+          <t>In the set screw kit. From the boss's front (lower panel off), into its printed M5 thread; the tip pins the tube through the front wall of its 5.2 mm cross hole, 10 mm below the tube's top. Replaces the M5 x 40 bolt and nut (the kit's M5s stop at 20 mm)</t>
         </is>
       </c>
       <c r="P38" s="22" t="inlineStr">
         <is>
-          <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+          <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="P39" s="22" t="inlineStr">
         <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>Head/Rev4/README.md and Head/Rev3/README.md, Bought; Amazon listing 2026-10-23</t>
+          <t>Head/Rev5/README.md and Head/Rev4/README.md, Bought; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -2638,12 +2638,12 @@
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>Ordered 2026-10-23. Uses the M3 x 25 (ISO 10642 / DIN 7991); the kits stop at 20 mm. Head in the countersink in the mount's left lug, through the trigger, then about 8 mm into the right lug's 2.5 mm pilot (tap it M3 all the way through); the tip stays about 0.9 mm inside the lug</t>
+          <t>Ordered 2026-10-23. Uses the M3 x 25 (ISO 10642 / DIN 7991); the kits stop at 20 mm. Head in the countersink in the mount's left lug, through the trigger, then about 8 mm into the right lug's printed M3 thread; the tip stays about 0.9 mm inside the lug</t>
         </is>
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>Head/Rev4/README.md and Head/Rev3/README.md, Bought; user's choice 2026-10-23; Amazon listing 2026-10-23</t>
+          <t>Head/Rev5/README.md and Head/Rev4/README.md, Bought; user's choice 2026-10-23; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -2703,12 +2703,12 @@
       </c>
       <c r="O42" s="22" t="inlineStr">
         <is>
-          <t>In the set screw kit. Through the trigger's arm (tap M3); its tip bears on the mount. Set it so the starter switch clicks before the stop</t>
+          <t>In the set screw kit. Through the trigger's arm (printed M3 thread); its tip bears on the mount. Set it so the starter switch clicks before the stop</t>
         </is>
       </c>
       <c r="P42" s="22" t="inlineStr">
         <is>
-          <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+          <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -2718,11 +2718,11 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>Search hat bezel</t>
+          <t>Trigger pull stop seat</t>
         </is>
       </c>
       <c r="C43" s="21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43" s="21" t="n">
         <v>1</v>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="O43" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. Through the hat's bezel into M2 threads tapped in the carrier (1.6 mm pilots)</t>
+          <t>In the screw kit. Flush in a countersunk, M2-tapped hole (1.6 mm pilot) in the mount's face under the spring pocket, so the pull stop's tip bears on steel and not on plastic</t>
         </is>
       </c>
       <c r="P43" s="22" t="inlineStr">
         <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -2783,11 +2783,11 @@
       </c>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>Search hat pivot</t>
+          <t>Search hat bezel</t>
         </is>
       </c>
       <c r="C44" s="21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44" s="21" t="n">
         <v>1</v>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H44" s="22" t="inlineStr">
         <is>
-          <t>M3 x 4 set screw</t>
+          <t>M2 x 8 countersunk screw</t>
         </is>
       </c>
       <c r="I44" s="22" t="inlineStr">
         <is>
-          <t>HIQTRADEBYJJ</t>
+          <t>AvrestYPT</t>
         </is>
       </c>
       <c r="J44" s="22" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="L44" s="24" t="inlineStr">
         <is>
-          <t>B0DG33R714</t>
+          <t>B0FMD5TMSH</t>
         </is>
       </c>
       <c r="M44" s="25" t="n">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O44" s="22" t="inlineStr">
         <is>
-          <t>In the set screw kit. Into the rocker plate's centre (tap M3), from behind; its tip is the pivot and sets the preload. Turn it with a 1.5 mm hex key through the carrier floor</t>
+          <t>In the screw kit. Through the hat's bezel into M2 threads tapped in the carrier (1.6 mm pilots)</t>
         </is>
       </c>
       <c r="P44" s="22" t="inlineStr">
         <is>
-          <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -2848,11 +2848,11 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>Panels</t>
+          <t>Search hat pivot</t>
         </is>
       </c>
       <c r="C45" s="21" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D45" s="21" t="n">
         <v>1</v>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="H45" s="22" t="inlineStr">
         <is>
-          <t>M3 x 12 countersunk screw (DIN 7991)</t>
+          <t>M3 x 4 set screw</t>
         </is>
       </c>
       <c r="I45" s="22" t="inlineStr">
         <is>
-          <t>AvrestYPT</t>
+          <t>HIQTRADEBYJJ</t>
         </is>
       </c>
       <c r="J45" s="22" t="inlineStr"/>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="L45" s="24" t="inlineStr">
         <is>
-          <t>B0FMD5TMSH</t>
+          <t>B0DG33R714</t>
         </is>
       </c>
       <c r="M45" s="25" t="n">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="O45" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. 4 per panel, into M3 threads tapped in the box's corner columns (the pilots run 50 mm deep, so the x 12 has room)</t>
+          <t>In the set screw kit. Into the rocker plate's centre (printed M3 thread), from behind; its tip is the pivot and sets the preload. Turn it with a 1.5 mm hex key through the carrier floor</t>
         </is>
       </c>
       <c r="P45" s="22" t="inlineStr">
         <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+          <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -2913,11 +2913,11 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>HeliSR board</t>
+          <t>Panels</t>
         </is>
       </c>
       <c r="C46" s="21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D46" s="21" t="n">
         <v>1</v>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="H46" s="22" t="inlineStr">
         <is>
-          <t>M3 x 12 countersunk screw (DIN 7991) + M3 hex nut</t>
+          <t>M3 x 16 countersunk screw (DIN 7991)</t>
         </is>
       </c>
       <c r="I46" s="22" t="inlineStr">
@@ -2963,146 +2963,146 @@
       </c>
       <c r="O46" s="22" t="inlineStr">
         <is>
+          <t>In the screw kit. 4 per panel, into the M3 threads printed 20 mm deep in the box's corner columns (a kit M3 x 20 fits too)</t>
+        </is>
+      </c>
+      <c r="P46" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>HeliSR board</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="21">
+        <f>ROUNDUP(C47*$C$3/D47,0)</f>
+        <v/>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="21">
+        <f>MAX(0,E47-F47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
+        <is>
+          <t>M3 x 12 countersunk screw (DIN 7991) + M3 hex nut</t>
+        </is>
+      </c>
+      <c r="I47" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT</t>
+        </is>
+      </c>
+      <c r="J47" s="22" t="inlineStr"/>
+      <c r="K47" s="22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L47" s="24" t="inlineStr">
+        <is>
+          <t>B0FMD5TMSH</t>
+        </is>
+      </c>
+      <c r="M47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="25">
+        <f>IF(M47="","",G47*M47)</f>
+        <v/>
+      </c>
+      <c r="O47" s="22" t="inlineStr">
+        <is>
           <t>In the screw kit. From outside the rear wall through a spacer and the board</t>
         </is>
       </c>
-      <c r="P46" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="P47" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>HeliSR board</t>
         </is>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C48" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D47" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="10">
-        <f>ROUNDUP(C47*$C$3/D47,0)</f>
-        <v/>
-      </c>
-      <c r="F47" s="12" t="n">
+      <c r="D48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="10">
+        <f>ROUNDUP(C48*$C$3/D48,0)</f>
+        <v/>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G47" s="10">
-        <f>MAX(0,E47-F47)</f>
-        <v/>
-      </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="G48" s="10">
+        <f>MAX(0,E48-F48)</f>
+        <v/>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>Round spacer, unthreaded, for M3, 4 mm long, 6.4 mm OD, PVC, self-retaining</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>Bivar</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr">
+      <c r="J48" s="11" t="inlineStr">
         <is>
           <t>SRS-4-4MM</t>
         </is>
       </c>
-      <c r="K47" s="11" t="inlineStr">
+      <c r="K48" s="11" t="inlineStr">
         <is>
           <t>Digi-Key</t>
         </is>
       </c>
-      <c r="L47" s="13" t="inlineStr">
+      <c r="L48" s="13" t="inlineStr">
         <is>
           <t>SRS-4-4MM-ND</t>
         </is>
       </c>
-      <c r="M47" s="14" t="n">
+      <c r="M48" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="N47" s="14">
-        <f>IF(M47="","",G47*M47)</f>
-        <v/>
-      </c>
-      <c r="O47" s="11" t="inlineStr">
+      <c r="N48" s="14">
+        <f>IF(M48="","",G48*M48)</f>
+        <v/>
+      </c>
+      <c r="O48" s="11" t="inlineStr">
         <is>
           <t>Between the rear wall and the board</t>
         </is>
       </c>
-      <c r="P47" s="11" t="inlineStr">
-        <is>
-          <t>Head/Rev4/README.md and Head/Rev3/README.md, Bought</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="B48" s="27" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
-      <c r="C48" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" s="26">
-        <f>ROUNDUP(C48*$C$3/D48,0)</f>
-        <v/>
-      </c>
-      <c r="F48" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="26">
-        <f>MAX(0,E48-F48)</f>
-        <v/>
-      </c>
-      <c r="H48" s="27" t="inlineStr">
-        <is>
-          <t>Pen spring, 4 mm OD x 50 mm, 0.4 mm wire, pack of 10</t>
-        </is>
-      </c>
-      <c r="I48" s="27" t="inlineStr">
-        <is>
-          <t>uxcell</t>
-        </is>
-      </c>
-      <c r="J48" s="27" t="inlineStr"/>
-      <c r="K48" s="27" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L48" s="29" t="inlineStr">
-        <is>
-          <t>B0GCZGNBYH</t>
-        </is>
-      </c>
-      <c r="M48" s="30" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="N48" s="30">
-        <f>IF(M48="","",G48*M48)</f>
-        <v/>
-      </c>
-      <c r="O48" s="27" t="inlineStr">
-        <is>
-          <t>Trigger return: cut to about 13 mm</t>
-        </is>
-      </c>
-      <c r="P48" s="27" t="inlineStr">
-        <is>
-          <t>Head/Rev4/README.md and Head/Rev3/README.md, Bought; Amazon listing 2026-10-23</t>
+      <c r="P48" s="11" t="inlineStr">
+        <is>
+          <t>Head/Rev5/README.md and Head/Rev4/README.md, Bought</t>
         </is>
       </c>
     </row>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Head box</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="C49" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E49" s="26">
         <f>ROUNDUP(C49*$C$3/D49,0)</f>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H49" s="27" t="inlineStr">
         <is>
-          <t>Ballast: lead split shot fishing weights, assorted, 120 pcs</t>
+          <t>Pen spring, 4 mm OD x 50 mm, 0.4 mm wire, pack of 10</t>
         </is>
       </c>
       <c r="I49" s="27" t="inlineStr">
         <is>
-          <t>SANWEAL</t>
+          <t>uxcell</t>
         </is>
       </c>
       <c r="J49" s="27" t="inlineStr"/>
@@ -3150,11 +3150,11 @@
       </c>
       <c r="L49" s="29" t="inlineStr">
         <is>
-          <t>B0H6J3X6GL</t>
+          <t>B0GCZGNBYH</t>
         </is>
       </c>
       <c r="M49" s="30" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="N49" s="30">
         <f>IF(M49="","",G49*M49)</f>
@@ -3162,116 +3162,112 @@
       </c>
       <c r="O49" s="27" t="inlineStr">
         <is>
+          <t>Trigger return: cut to about 13 mm</t>
+        </is>
+      </c>
+      <c r="P49" s="27" t="inlineStr">
+        <is>
+          <t>Head/Rev5/README.md and Head/Rev4/README.md, Bought; Amazon listing 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Head box</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="26">
+        <f>ROUNDUP(C50*$C$3/D50,0)</f>
+        <v/>
+      </c>
+      <c r="F50" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="26">
+        <f>MAX(0,E50-F50)</f>
+        <v/>
+      </c>
+      <c r="H50" s="27" t="inlineStr">
+        <is>
+          <t>Ballast: lead split shot fishing weights, assorted, 120 pcs</t>
+        </is>
+      </c>
+      <c r="I50" s="27" t="inlineStr">
+        <is>
+          <t>SANWEAL</t>
+        </is>
+      </c>
+      <c r="J50" s="27" t="inlineStr"/>
+      <c r="K50" s="27" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L50" s="29" t="inlineStr">
+        <is>
+          <t>B0H6J3X6GL</t>
+        </is>
+      </c>
+      <c r="M50" s="30" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="N50" s="30">
+        <f>IF(M50="","",G50*M50)</f>
+        <v/>
+      </c>
+      <c r="O50" s="27" t="inlineStr">
+        <is>
           <t>Only if the gas strut lifts too much: about 48 g for a 45 N strut. Close to the middle of the box. Weigh out what you need</t>
         </is>
       </c>
-      <c r="P49" s="27" t="inlineStr">
+      <c r="P50" s="27" t="inlineStr">
         <is>
           <t>Base/README.md, Bought parts; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="M50" s="3" t="inlineStr">
+    <row r="51">
+      <c r="M51" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N50" s="15">
-        <f>SUM(N38:N49)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="N51" s="15">
+        <f>SUM(N38:N50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>MkIII base Rev 3 (concept, not yet printed)</t>
         </is>
       </c>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
-      <c r="L51" s="8" t="n"/>
-      <c r="M51" s="8" t="n"/>
-      <c r="N51" s="8" t="n"/>
-      <c r="O51" s="8" t="n"/>
-      <c r="P51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>Pivot</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="10">
-        <f>ROUNDUP(C52*$C$3/D52,0)</f>
-        <v/>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="10">
-        <f>MAX(0,E52-F52)</f>
-        <v/>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>Deep-groove ball bearing 6006-2RS, 30 x 55 x 13 mm</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>BlueStars</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>6006-2RS</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L52" s="13" t="inlineStr">
-        <is>
-          <t>B09XTV8XYK</t>
-        </is>
-      </c>
-      <c r="M52" s="14" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="N52" s="14">
-        <f>IF(M52="","",G52*M52)</f>
-        <v/>
-      </c>
-      <c r="O52" s="11" t="inlineStr">
-        <is>
-          <t>Sold in pairs</t>
-        </is>
-      </c>
-      <c r="P52" s="11" t="inlineStr">
-        <is>
-          <t>Amazon listing on 2026-10-22 (link you sent); Base/mk3_pivot.py (the Rev 1 parts Rev 3 keeps)</t>
-        </is>
-      </c>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
+      <c r="M52" s="8" t="n"/>
+      <c r="N52" s="8" t="n"/>
+      <c r="O52" s="8" t="n"/>
+      <c r="P52" s="9" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n">
@@ -3279,11 +3275,11 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Tube</t>
+          <t>Pivot</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="10" t="n">
         <v>2</v>
@@ -3301,15 +3297,19 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Carbon fibre tube, 25 mm OD x 23 mm ID, 500 mm, 3K plain weave, wrapped</t>
+          <t>Deep-groove ball bearing 6006-2RS, 30 x 55 x 13 mm</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>MECCANIXITY</t>
-        </is>
-      </c>
-      <c r="J53" s="11" t="inlineStr"/>
+          <t>BlueStars</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>6006-2RS</t>
+        </is>
+      </c>
       <c r="K53" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
@@ -3317,11 +3317,11 @@
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>B0CFFT1B31</t>
+          <t>B09XTV8XYK</t>
         </is>
       </c>
       <c r="M53" s="14" t="n">
-        <v>27.49</v>
+        <v>8.99</v>
       </c>
       <c r="N53" s="14">
         <f>IF(M53="","",G53*M53)</f>
@@ -3329,207 +3329,207 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>Sold in pairs. Wrapped, as the base needs (not pultruded). Cut to 491 mm (470 + the head's extra 12.7 mm of bore + 8 mm for the base's deeper socket). Drill the M4 lock-screw hole 38.5 mm from the bottom end and the head's 5.2 mm cross hole 10 mm below the top end. Check the socket and head fits with it (coupons)</t>
+          <t>Sold in pairs</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
         <is>
+          <t>Amazon listing on 2026-10-22 (link you sent); Base/mk3_pivot.py (the Rev 1 parts Rev 3 keeps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Tube</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="10">
+        <f>ROUNDUP(C54*$C$3/D54,0)</f>
+        <v/>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="10">
+        <f>MAX(0,E54-F54)</f>
+        <v/>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Carbon fibre tube, 25 mm OD x 23 mm ID, 500 mm, 3K plain weave, wrapped</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>MECCANIXITY</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L54" s="13" t="inlineStr">
+        <is>
+          <t>B0CFFT1B31</t>
+        </is>
+      </c>
+      <c r="M54" s="14" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="N54" s="14">
+        <f>IF(M54="","",G54*M54)</f>
+        <v/>
+      </c>
+      <c r="O54" s="11" t="inlineStr">
+        <is>
+          <t>Sold in pairs. Wrapped, as the base needs (not pultruded). Used whole, 500 mm, uncut (470 + the head's extra 12.7 mm of bore + 17.3 mm down in the base's socket). Drill the head's 5.2 mm cross hole 10 mm below the top end and file a 13 mm wide notch, 4+ mm deep, in each side of the bottom end for the cables. Check the socket and head fits with it (coupons)</t>
+        </is>
+      </c>
+      <c r="P54" s="11" t="inlineStr">
+        <is>
           <t>Amazon listing on 2026-10-22 (link you sent); Base/README.md, Bought parts</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="21" t="n">
-        <v>36</v>
-      </c>
-      <c r="B54" s="22" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
         <is>
           <t>Lever halves</t>
         </is>
       </c>
-      <c r="C54" s="21" t="n">
+      <c r="C55" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D54" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="21">
-        <f>ROUNDUP(C54*$C$3/D54,0)</f>
-        <v/>
-      </c>
-      <c r="F54" s="23" t="n">
+      <c r="D55" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="21">
+        <f>ROUNDUP(C55*$C$3/D55,0)</f>
+        <v/>
+      </c>
+      <c r="F55" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="21">
-        <f>MAX(0,E54-F54)</f>
-        <v/>
-      </c>
-      <c r="H54" s="22" t="inlineStr">
+      <c r="G55" s="21">
+        <f>MAX(0,E55-F55)</f>
+        <v/>
+      </c>
+      <c r="H55" s="22" t="inlineStr">
         <is>
           <t>M4 x 20 countersunk screw + M4 hex nut</t>
         </is>
       </c>
-      <c r="I54" s="22" t="inlineStr">
+      <c r="I55" s="22" t="inlineStr">
         <is>
           <t>AvrestYPT</t>
         </is>
       </c>
-      <c r="J54" s="22" t="inlineStr"/>
-      <c r="K54" s="22" t="inlineStr">
+      <c r="J55" s="22" t="inlineStr"/>
+      <c r="K55" s="22" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L54" s="24" t="inlineStr">
+      <c r="L55" s="24" t="inlineStr">
         <is>
           <t>B0FMD5TMSH</t>
         </is>
       </c>
-      <c r="M54" s="25" t="n">
+      <c r="M55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="N54" s="25">
-        <f>IF(M54="","",G54*M54)</f>
-        <v/>
-      </c>
-      <c r="O54" s="22" t="inlineStr">
+      <c r="N55" s="25">
+        <f>IF(M55="","",G55*M55)</f>
+        <v/>
+      </c>
+      <c r="O55" s="22" t="inlineStr">
         <is>
           <t>In the screw kit. From the top, the heads 16 mm down their counterbores (a long 2.5 mm hex key helps); the nuts go in the lower half's pockets first</t>
         </is>
       </c>
-      <c r="P54" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="P55" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>Strut</t>
         </is>
       </c>
-      <c r="C55" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="10" t="n">
+      <c r="C56" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E55" s="10">
-        <f>ROUNDUP(C55*$C$3/D55,0)</f>
-        <v/>
-      </c>
-      <c r="F55" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="10">
-        <f>MAX(0,E55-F55)</f>
-        <v/>
-      </c>
-      <c r="H55" s="11" t="inlineStr">
+      <c r="E56" s="10">
+        <f>ROUNDUP(C56*$C$3/D56,0)</f>
+        <v/>
+      </c>
+      <c r="F56" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="10">
+        <f>MAX(0,E56-F56)</f>
+        <v/>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
         <is>
           <t>Gas strut, 6 in (152.4 mm eye to eye), 45 N (sold as 9-12 lb), flat eyelet tabs</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr">
+      <c r="I56" s="11" t="inlineStr">
         <is>
           <t>X AUTOHAUX</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr"/>
-      <c r="K55" s="11" t="inlineStr">
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L55" s="13" t="inlineStr">
+      <c r="L56" s="13" t="inlineStr">
         <is>
           <t>B0CY267GFY</t>
         </is>
       </c>
-      <c r="M55" s="14" t="n">
+      <c r="M56" s="14" t="n">
         <v>13.69</v>
       </c>
-      <c r="N55" s="14">
-        <f>IF(M55="","",G55*M55)</f>
-        <v/>
-      </c>
-      <c r="O55" s="11" t="inlineStr">
+      <c r="N56" s="14">
+        <f>IF(M56="","",G56*M56)</f>
+        <v/>
+      </c>
+      <c r="O56" s="11" t="inlineStr">
         <is>
           <t>Sold in pairs: the spare is the other half</t>
         </is>
       </c>
-      <c r="P55" s="11" t="inlineStr">
+      <c r="P56" s="11" t="inlineStr">
         <is>
           <t>Base/README.md, Bought parts</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="21" t="n">
-        <v>38</v>
-      </c>
-      <c r="B56" s="22" t="inlineStr">
-        <is>
-          <t>Strut eyes</t>
-        </is>
-      </c>
-      <c r="C56" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D56" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="21">
-        <f>ROUNDUP(C56*$C$3/D56,0)</f>
-        <v/>
-      </c>
-      <c r="F56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="21">
-        <f>MAX(0,E56-F56)</f>
-        <v/>
-      </c>
-      <c r="H56" s="22" t="inlineStr">
-        <is>
-          <t>M4 x 16 countersunk screw + M4 hex nut</t>
-        </is>
-      </c>
-      <c r="I56" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J56" s="22" t="inlineStr"/>
-      <c r="K56" s="22" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L56" s="24" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M56" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="25">
-        <f>IF(M56="","",G56*M56)</f>
-        <v/>
-      </c>
-      <c r="O56" s="22" t="inlineStr">
-        <is>
-          <t>In the screw kit. One per eye: head on +y, nut in the -y cheek's pocket. The listing gives the strut's eye holes as 4 mm. Snug, then thread-lock: the eye must still turn</t>
-        </is>
-      </c>
-      <c r="P56" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>Strut collar</t>
+          <t>Strut eyes</t>
         </is>
       </c>
       <c r="C57" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="21" t="n">
         <v>1</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H57" s="22" t="inlineStr">
         <is>
-          <t>M4 x 12 countersunk screw + M4 hex nut</t>
+          <t>M4 x 16 countersunk screw + M4 hex nut</t>
         </is>
       </c>
       <c r="I57" s="22" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="O57" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. Collar clamp: the head sits 2 mm into the -y ear, the nut in the +y ear's pocket</t>
+          <t>In the screw kit. One per eye: head on +y, nut in the -y cheek's pocket. The listing gives the strut's eye holes as 4 mm. Snug, then thread-lock: the eye must still turn</t>
         </is>
       </c>
       <c r="P57" s="22" t="inlineStr">
         <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -3604,11 +3604,11 @@
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>Down-stops</t>
+          <t>Strut collar</t>
         </is>
       </c>
       <c r="C58" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" s="21" t="n">
         <v>1</v>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H58" s="22" t="inlineStr">
         <is>
-          <t>M4 x 16 countersunk screw + 2 M4 hex nuts</t>
+          <t>M4 x 12 countersunk screw + M4 hex nut</t>
         </is>
       </c>
       <c r="I58" s="22" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="O58" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. Head up: its flat top is the stop. One nut pressed into the post's top pocket, the second on top of it locks the height that levels the tube</t>
+          <t>In the screw kit. Collar clamp: the head sits 2 mm into the -y ear, the nut in the +y ear's pocket</t>
         </is>
       </c>
       <c r="P58" s="22" t="inlineStr">
         <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -3669,11 +3669,11 @@
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>Pillow-block caps</t>
+          <t>Down-stops</t>
         </is>
       </c>
       <c r="C59" s="21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D59" s="21" t="n">
         <v>1</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="H59" s="22" t="inlineStr">
         <is>
-          <t>M4 x 20 countersunk screw + M4 hex nut</t>
+          <t>M4 x 16 countersunk screw + 2 M4 hex nuts</t>
         </is>
       </c>
       <c r="I59" s="22" t="inlineStr">
@@ -3719,144 +3719,144 @@
       </c>
       <c r="O59" s="22" t="inlineStr">
         <is>
+          <t>In the screw kit. Head up: its flat top is the stop. One nut pressed into the post's top pocket, the second on top of it locks the height that levels the tube</t>
+        </is>
+      </c>
+      <c r="P59" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Pillow-block caps</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="21">
+        <f>ROUNDUP(C60*$C$3/D60,0)</f>
+        <v/>
+      </c>
+      <c r="F60" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="21">
+        <f>MAX(0,E60-F60)</f>
+        <v/>
+      </c>
+      <c r="H60" s="22" t="inlineStr">
+        <is>
+          <t>M4 x 20 countersunk screw + M4 hex nut</t>
+        </is>
+      </c>
+      <c r="I60" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT</t>
+        </is>
+      </c>
+      <c r="J60" s="22" t="inlineStr"/>
+      <c r="K60" s="22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L60" s="24" t="inlineStr">
+        <is>
+          <t>B0FMD5TMSH</t>
+        </is>
+      </c>
+      <c r="M60" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="25">
+        <f>IF(M60="","",G60*M60)</f>
+        <v/>
+      </c>
+      <c r="O60" s="22" t="inlineStr">
+        <is>
           <t>In the screw kit. Two per cap, from the top; each nut slides into a slot in the block's front or back face. Length from the CAD</t>
         </is>
       </c>
-      <c r="P59" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="P60" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>Side covers</t>
         </is>
       </c>
-      <c r="C60" s="10" t="n">
+      <c r="C61" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D61" s="10" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="E60" s="10">
-        <f>IF($C$3&gt;0,C60,0)</f>
-        <v/>
-      </c>
-      <c r="F60" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="10">
-        <f>MAX(0,E60-F60)</f>
-        <v/>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
+      <c r="E61" s="10">
+        <f>IF($C$3&gt;0,C61,0)</f>
+        <v/>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="10">
+        <f>MAX(0,E61-F61)</f>
+        <v/>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
         <is>
           <t>M3 x 25 countersunk screw (from the M3 x 20-40 set, ASIN B0BYXS4BTF)</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr">
+      <c r="I61" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="J60" s="11" t="inlineStr"/>
-      <c r="K60" s="11" t="inlineStr">
+      <c r="J61" s="11" t="inlineStr"/>
+      <c r="K61" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L60" s="13" t="inlineStr">
+      <c r="L61" s="13" t="inlineStr">
         <is>
           <t>B0BYXS4BTF</t>
         </is>
       </c>
-      <c r="M60" s="14" t="n">
+      <c r="M61" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N60" s="14">
-        <f>IF(M60="","",G60*M60)</f>
-        <v/>
-      </c>
-      <c r="O60" s="11" t="inlineStr">
+      <c r="N61" s="14">
+        <f>IF(M61="","",G61*M61)</f>
+        <v/>
+      </c>
+      <c r="O61" s="11" t="inlineStr">
         <is>
           <t>From the same 100-piece set as the trigger pivot (20 of each length). Four per cover, from its outer face into M3 threads tapped 11 mm deep in the block and cap: 10 mm of thread, three times the 20 mm screw's. The kit's M3 x 20 would only reach 5</t>
         </is>
       </c>
-      <c r="P60" s="11" t="inlineStr">
+      <c r="P61" s="11" t="inlineStr">
         <is>
           <t>Base/README.md, Bought parts; user's M3 set 2026-10-24; Amazon listing 2026-10-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="21" t="n">
-        <v>43</v>
-      </c>
-      <c r="B61" s="22" t="inlineStr">
-        <is>
-          <t>Cable plug</t>
-        </is>
-      </c>
-      <c r="C61" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="21">
-        <f>ROUNDUP(C61*$C$3/D61,0)</f>
-        <v/>
-      </c>
-      <c r="F61" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="21">
-        <f>MAX(0,E61-F61)</f>
-        <v/>
-      </c>
-      <c r="H61" s="22" t="inlineStr">
-        <is>
-          <t>M2 x 12 countersunk screw</t>
-        </is>
-      </c>
-      <c r="I61" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J61" s="22" t="inlineStr"/>
-      <c r="K61" s="22" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L61" s="24" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M61" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="25">
-        <f>IF(M61="","",G61*M61)</f>
-        <v/>
-      </c>
-      <c r="O61" s="22" t="inlineStr">
-        <is>
-          <t>In the screw kit. Up from under the cable cover's rim, through a clearance hole, into an M2 thread tapped in the plug (1.6 mm pilot): pulls the plug that closes the cable's slot down onto the cover's shoulders. Length from the CAD</t>
-        </is>
-      </c>
-      <c r="P61" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>Tube lock</t>
+          <t>Cable plug</t>
         </is>
       </c>
       <c r="C62" s="21" t="n">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="H62" s="22" t="inlineStr">
         <is>
-          <t>M4 x 6 set screw</t>
+          <t>M2 x 12 countersunk screw</t>
         </is>
       </c>
       <c r="I62" s="22" t="inlineStr">
         <is>
-          <t>HIQTRADEBYJJ</t>
+          <t>AvrestYPT</t>
         </is>
       </c>
       <c r="J62" s="22" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L62" s="24" t="inlineStr">
         <is>
-          <t>B0DG33R714</t>
+          <t>B0FMD5TMSH</t>
         </is>
       </c>
       <c r="M62" s="25" t="n">
@@ -3916,77 +3916,67 @@
       </c>
       <c r="O62" s="22" t="inlineStr">
         <is>
-          <t>In the set screw kit. Tap the socket boss's 3.3 mm pilot M4; the tip goes into the tube's 4 mm lock hole, 38.5 mm from its bottom end</t>
+          <t>In the screw kit. Up from under the cable cover's rim, through a clearance hole, into an M2 thread tapped in the plug (1.6 mm pilot): pulls the plug that closes the cable's slot down onto the cover's shoulders. Length from the CAD</t>
         </is>
       </c>
       <c r="P62" s="22" t="inlineStr">
         <is>
-          <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="21" t="n">
+      <c r="A63" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="B63" s="22" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>Friction knob</t>
         </is>
       </c>
-      <c r="C63" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="21">
+      <c r="C63" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="16">
         <f>ROUNDUP(C63*$C$3/D63,0)</f>
         <v/>
       </c>
-      <c r="F63" s="23" t="n">
+      <c r="F63" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G63" s="21">
+      <c r="G63" s="16">
         <f>MAX(0,E63-F63)</f>
         <v/>
       </c>
-      <c r="H63" s="22" t="inlineStr">
-        <is>
-          <t>M5 x 20 countersunk screw + M5 hex nut</t>
-        </is>
-      </c>
-      <c r="I63" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J63" s="22" t="inlineStr"/>
-      <c r="K63" s="22" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L63" s="24" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" s="25">
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>M5 x 16 hex-head bolt (ISO 4017 / DIN 933), zinc or stainless</t>
+        </is>
+      </c>
+      <c r="I63" s="17" t="inlineStr"/>
+      <c r="J63" s="17" t="inlineStr"/>
+      <c r="K63" s="17" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="L63" s="17" t="inlineStr"/>
+      <c r="M63" s="20" t="n"/>
+      <c r="N63" s="20">
         <f>IF(M63="","",G63*M63)</f>
         <v/>
       </c>
-      <c r="O63" s="22" t="inlineStr">
-        <is>
-          <t>In the screw kit. Glue the head into the printed knob (Base/stl/friction_knob.stl); the screw goes through the spring and the shoe into the nut, slid into the knob tower's slot from the front. Length from the CAD</t>
-        </is>
-      </c>
-      <c r="P63" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+      <c r="O63" s="17" t="inlineStr">
+        <is>
+          <t>CHECK: Not in the screw kits (they have only countersunk heads): any hardware store. Its head presses into the hex pocket moulded into the printed knob (Base/stl/friction_knob.stl), so the knob turns it; it goes through the spring and the shoe into the M5 nut</t>
+        </is>
+      </c>
+      <c r="P63" s="17" t="inlineStr">
+        <is>
+          <t>Base/README.md, Friction knob</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3986,7 @@
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>Shoe hinge</t>
+          <t>Friction knob</t>
         </is>
       </c>
       <c r="C64" s="21" t="n">
@@ -4018,7 +4008,7 @@
       </c>
       <c r="H64" s="22" t="inlineStr">
         <is>
-          <t>M4 x 20 countersunk screw + M4 hex nut</t>
+          <t>M5 hex nut</t>
         </is>
       </c>
       <c r="I64" s="22" t="inlineStr">
@@ -4046,114 +4036,112 @@
       </c>
       <c r="O64" s="22" t="inlineStr">
         <is>
+          <t>In the screw kit. Slid into the knob tower's slot from the front; the friction bolt threads into it</t>
+        </is>
+      </c>
+      <c r="P64" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>Shoe hinge</t>
+        </is>
+      </c>
+      <c r="C65" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="21">
+        <f>ROUNDUP(C65*$C$3/D65,0)</f>
+        <v/>
+      </c>
+      <c r="F65" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="21">
+        <f>MAX(0,E65-F65)</f>
+        <v/>
+      </c>
+      <c r="H65" s="22" t="inlineStr">
+        <is>
+          <t>M4 x 20 countersunk screw + M4 hex nut</t>
+        </is>
+      </c>
+      <c r="I65" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT</t>
+        </is>
+      </c>
+      <c r="J65" s="22" t="inlineStr"/>
+      <c r="K65" s="22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L65" s="24" t="inlineStr">
+        <is>
+          <t>B0FMD5TMSH</t>
+        </is>
+      </c>
+      <c r="M65" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="25">
+        <f>IF(M65="","",G65*M65)</f>
+        <v/>
+      </c>
+      <c r="O65" s="22" t="inlineStr">
+        <is>
           <t>In the screw kit. Hinge pin through both frame lugs and the shoe's eye: head in the -y lug, nut in the +y lug's pocket (the lugs are 20 mm apart outside). Snug, then thread-lock: the shoe must still swing</t>
         </is>
       </c>
-      <c r="P64" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev4 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="M65" s="3" t="inlineStr">
+      <c r="P65" s="22" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="M66" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N65" s="15">
-        <f>SUM(N52:N64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="N66" s="15">
+        <f>SUM(N53:N65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>Kits, consumables and tools</t>
         </is>
       </c>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
-      <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="n"/>
-      <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
-      <c r="I66" s="8" t="n"/>
-      <c r="J66" s="8" t="n"/>
-      <c r="K66" s="8" t="n"/>
-      <c r="L66" s="8" t="n"/>
-      <c r="M66" s="8" t="n"/>
-      <c r="N66" s="8" t="n"/>
-      <c r="O66" s="8" t="n"/>
-      <c r="P66" s="9" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>once</t>
-        </is>
-      </c>
-      <c r="E67" s="10">
-        <f>IF($C$3&gt;0,C67,0)</f>
-        <v/>
-      </c>
-      <c r="F67" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="10">
-        <f>MAX(0,E67-F67)</f>
-        <v/>
-      </c>
-      <c r="H67" s="11" t="inlineStr">
-        <is>
-          <t>Screw kit, 1715 pieces: countersunk hex-socket screws M2-M4 x 8, 12, 16, 20 and M5 x 10, 12, 16, 20, with hex nuts and washers, hex keys</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr"/>
-      <c r="K67" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L67" s="13" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M67" s="14" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="N67" s="14">
-        <f>IF(M67="","",G67*M67)</f>
-        <v/>
-      </c>
-      <c r="O67" s="11" t="inlineStr">
-        <is>
-          <t>Every countersunk screw and nut in the head and base (the green lines). Used: M3 x 12 (12), M3 x 20 (8), M4 x 12 (2), M4 x 16 (4), M4 x 20 (9), M5 x 20 (1); nuts M3 (4), M4 (17), M5 (1). Your order (link 2026-10-23)</t>
-        </is>
-      </c>
-      <c r="P67" s="11" t="inlineStr">
-        <is>
-          <t>Amazon listing 2026-10-23 (your order)</t>
-        </is>
-      </c>
+      <c r="B67" s="8" t="n"/>
+      <c r="C67" s="8" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="8" t="n"/>
+      <c r="F67" s="8" t="n"/>
+      <c r="G67" s="8" t="n"/>
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+      <c r="L67" s="8" t="n"/>
+      <c r="M67" s="8" t="n"/>
+      <c r="N67" s="8" t="n"/>
+      <c r="O67" s="8" t="n"/>
+      <c r="P67" s="9" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="n">
@@ -4185,12 +4173,12 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>Set screw kit, 500 pieces, 304 stainless: M3 x 3, 4, 5, 6; M4 x 4, 5, 6; M5 x 5, 8; M6 x 6, 10; M8 x 8; hex keys</t>
+          <t>Screw kit, 1715 pieces: countersunk hex-socket screws M2-M4 x 8, 12, 16, 20 and M5 x 10, 12, 16, 20, with hex nuts and washers, hex keys</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>HIQTRADEBYJJ</t>
+          <t>AvrestYPT</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr"/>
@@ -4201,11 +4189,11 @@
       </c>
       <c r="L68" s="13" t="inlineStr">
         <is>
-          <t>B0DG33R714</t>
+          <t>B0FMD5TMSH</t>
         </is>
       </c>
       <c r="M68" s="14" t="n">
-        <v>8.960000000000001</v>
+        <v>17.99</v>
       </c>
       <c r="N68" s="14">
         <f>IF(M68="","",G68*M68)</f>
@@ -4213,7 +4201,7 @@
       </c>
       <c r="O68" s="11" t="inlineStr">
         <is>
-          <t>The set screws: M5 x 8 (tube, head), M3 x 4 (trigger pull stop), M4 x 6 (tube lock, base). Your order (link 2026-10-23)</t>
+          <t>Every countersunk screw and nut in the head and base (the green lines). Used: M3 x 12 (4), M3 x 16 (8), M3 x 20 (8), M4 x 12 (2), M4 x 16 (4), M4 x 20 (9); nuts M3 (4), M4 (17), M5 (1). Your order (link 2026-10-23)</t>
         </is>
       </c>
       <c r="P68" s="11" t="inlineStr">
@@ -4228,7 +4216,7 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
@@ -4252,12 +4240,12 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>White lithium grease, 1.5 oz tube</t>
+          <t>Set screw kit, 500 pieces, 304 stainless: M3 x 3, 4, 5, 6; M4 x 4, 5, 6; M5 x 5, 8; M6 x 6, 10; M8 x 8; hex keys</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>Permatex</t>
+          <t>HIQTRADEBYJJ</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr"/>
@@ -4268,11 +4256,11 @@
       </c>
       <c r="L69" s="13" t="inlineStr">
         <is>
-          <t>B000HBNV58</t>
+          <t>B0DG33R714</t>
         </is>
       </c>
       <c r="M69" s="14" t="n">
-        <v>3.99</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N69" s="14">
         <f>IF(M69="","",G69*M69)</f>
@@ -4280,12 +4268,12 @@
       </c>
       <c r="O69" s="11" t="inlineStr">
         <is>
-          <t>Bearing grease (not silicone paste)</t>
+          <t>The set screws: M5 x 8 (tube, head), M3 x 4 (trigger pull stop). Your order (link 2026-10-23)</t>
         </is>
       </c>
       <c r="P69" s="11" t="inlineStr">
         <is>
-          <t>Head/Rev4/README.md; Base/README.md; Amazon listing 2026-10-23</t>
+          <t>Amazon listing 2026-10-23 (your order)</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4307,12 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>Silicone faucet grease, waterproof, 0.5 oz</t>
+          <t>White lithium grease, 1.5 oz tube</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>Danco</t>
+          <t>Permatex</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr"/>
@@ -4335,11 +4323,11 @@
       </c>
       <c r="L70" s="13" t="inlineStr">
         <is>
-          <t>B000DZFUPC</t>
+          <t>B000HBNV58</t>
         </is>
       </c>
       <c r="M70" s="14" t="n">
-        <v>5.68</v>
+        <v>3.99</v>
       </c>
       <c r="N70" s="14">
         <f>IF(M70="","",G70*M70)</f>
@@ -4347,12 +4335,12 @@
       </c>
       <c r="O70" s="11" t="inlineStr">
         <is>
-          <t>For the head's four throttle O-rings (grease them lightly before fitting)</t>
+          <t>Bearing grease (not silicone paste)</t>
         </is>
       </c>
       <c r="P70" s="11" t="inlineStr">
         <is>
-          <t>Head/Rev4/README.md; Amazon listing 2026-10-23</t>
+          <t>Head/Rev4/README.md; Base/README.md; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -4386,31 +4374,27 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Solder paste, low-temperature (Sn42/Bi58, 138 C), syringe</t>
+          <t>Silicone faucet grease, waterproof, 0.5 oz</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>Chip Quik</t>
-        </is>
-      </c>
-      <c r="J71" s="11" t="inlineStr">
-        <is>
-          <t>NC191LT10</t>
-        </is>
-      </c>
+          <t>Danco</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr"/>
       <c r="K71" s="11" t="inlineStr">
         <is>
-          <t>Digi-Key</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="L71" s="13" t="inlineStr">
         <is>
-          <t>315-NC191LT10-ND</t>
+          <t>B000DZFUPC</t>
         </is>
       </c>
       <c r="M71" s="14" t="n">
-        <v>7.95</v>
+        <v>5.68</v>
       </c>
       <c r="N71" s="14">
         <f>IF(M71="","",G71*M71)</f>
@@ -4418,12 +4402,12 @@
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>For the SMD parts on the board (U1, U2, the 1206 caps, the JST headers, SW1-SW3). Needs a hot plate or hot air tool and flux. Optional: hand-soldering works too</t>
+          <t>For the head's four throttle O-rings (grease them lightly before fitting)</t>
         </is>
       </c>
       <c r="P71" s="11" t="inlineStr">
         <is>
-          <t>Digi-Key cart 2026-10-23</t>
+          <t>Head/Rev4/README.md; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -4457,17 +4441,17 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Tweezers, 1 mm tip (Olimex CHN-TWZ1MM), for placing the SMD parts</t>
+          <t>Solder paste, low-temperature (Sn42/Bi58, 138 C), syringe</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>Olimex</t>
+          <t>Chip Quik</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>CHN-TWZ1MM</t>
+          <t>NC191LT10</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr">
@@ -4477,11 +4461,11 @@
       </c>
       <c r="L72" s="13" t="inlineStr">
         <is>
-          <t>1188-CHN-TWZ1MM-ND</t>
+          <t>315-NC191LT10-ND</t>
         </is>
       </c>
       <c r="M72" s="14" t="n">
-        <v>0.82</v>
+        <v>7.95</v>
       </c>
       <c r="N72" s="14">
         <f>IF(M72="","",G72*M72)</f>
@@ -4489,61 +4473,132 @@
       </c>
       <c r="O72" s="11" t="inlineStr">
         <is>
+          <t>For the SMD parts on the board (U1, U2, the 1206 caps, the JST headers, SW1-SW3). Needs a hot plate or hot air tool and flux. Optional: hand-soldering works too</t>
+        </is>
+      </c>
+      <c r="P72" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key cart 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="E73" s="10">
+        <f>IF($C$3&gt;0,C73,0)</f>
+        <v/>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="10">
+        <f>MAX(0,E73-F73)</f>
+        <v/>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>Tweezers, 1 mm tip (Olimex CHN-TWZ1MM), for placing the SMD parts</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Olimex</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>CHN-TWZ1MM</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L73" s="13" t="inlineStr">
+        <is>
+          <t>1188-CHN-TWZ1MM-ND</t>
+        </is>
+      </c>
+      <c r="M73" s="14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N73" s="14">
+        <f>IF(M73="","",G73*M73)</f>
+        <v/>
+      </c>
+      <c r="O73" s="11" t="inlineStr">
+        <is>
           <t>Description from Olimex's sibling CHN-TWZ2MM listing: check the tip</t>
         </is>
       </c>
-      <c r="P72" s="11" t="inlineStr">
+      <c r="P73" s="11" t="inlineStr">
         <is>
           <t>Digi-Key order 102438510</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="M73" s="3" t="inlineStr">
+    <row r="74">
+      <c r="M74" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N73" s="15">
-        <f>SUM(N67:N72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="M75" s="3" t="inlineStr">
-        <is>
-          <t>Still to buy</t>
-        </is>
-      </c>
-      <c r="N75" s="15">
-        <f>N16+N20+N26+N29+N36+N50+N65+N73</f>
+      <c r="N74" s="15">
+        <f>SUM(N68:N73)</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>Whole build</t>
+          <t>Still to buy</t>
         </is>
       </c>
       <c r="N76" s="15">
-        <f>SUMPRODUCT(E6:E73,M6:M73)</f>
+        <f>N16+N20+N26+N29+N36+N51+N66+N74</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="M77" s="3" t="inlineStr">
         <is>
+          <t>Whole build</t>
+        </is>
+      </c>
+      <c r="N77" s="15">
+        <f>SUMPRODUCT(E6:E74,M6:M74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="M78" s="3" t="inlineStr">
+        <is>
           <t>Unpriced lines</t>
         </is>
       </c>
-      <c r="N77" s="3">
-        <f>COUNTIFS(A6:A73,"&gt;0",M6:M73,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="N78" s="3">
+        <f>COUNTIFS(A6:A74,"&gt;0",M6:M74,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Still to buy counts the packs to order; whole build counts every pack needed, bought or not. Both leave out the unpriced lines: generic hardware and wire.</t>
         </is>
@@ -4551,16 +4606,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A51:P51"/>
-    <mergeCell ref="A66:P66"/>
     <mergeCell ref="A17:P17"/>
     <mergeCell ref="A37:P37"/>
     <mergeCell ref="A27:P27"/>
+    <mergeCell ref="A67:P67"/>
+    <mergeCell ref="A79:P79"/>
     <mergeCell ref="A6:P6"/>
     <mergeCell ref="D3:P3"/>
     <mergeCell ref="A30:P30"/>
-    <mergeCell ref="A78:P78"/>
     <mergeCell ref="A21:P21"/>
+    <mergeCell ref="A52:P52"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
@@ -4598,7 +4653,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId37"/>
@@ -4609,14 +4664,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5470,7 +5525,7 @@
         </is>
       </c>
       <c r="C23" s="26">
-        <f>'Final BOM'!G47</f>
+        <f>'Final BOM'!G48</f>
         <v/>
       </c>
       <c r="D23" s="27" t="inlineStr">
@@ -5489,11 +5544,11 @@
         </is>
       </c>
       <c r="G23" s="30">
-        <f>'Final BOM'!M47</f>
+        <f>'Final BOM'!M48</f>
         <v/>
       </c>
       <c r="H23" s="30">
-        <f>IF('Final BOM'!M47="","",C23*G23)</f>
+        <f>IF('Final BOM'!M48="","",C23*G23)</f>
         <v/>
       </c>
       <c r="I23" s="27" t="inlineStr">
@@ -5512,7 +5567,7 @@
         </is>
       </c>
       <c r="C24" s="26">
-        <f>'Final BOM'!G71</f>
+        <f>'Final BOM'!G72</f>
         <v/>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -5531,11 +5586,11 @@
         </is>
       </c>
       <c r="G24" s="30">
-        <f>'Final BOM'!M71</f>
+        <f>'Final BOM'!M72</f>
         <v/>
       </c>
       <c r="H24" s="30">
-        <f>IF('Final BOM'!M71="","",C24*G24)</f>
+        <f>IF('Final BOM'!M72="","",C24*G24)</f>
         <v/>
       </c>
       <c r="I24" s="27" t="inlineStr">
@@ -5554,7 +5609,7 @@
         </is>
       </c>
       <c r="C25" s="26">
-        <f>'Final BOM'!G72</f>
+        <f>'Final BOM'!G73</f>
         <v/>
       </c>
       <c r="D25" s="27" t="inlineStr">
@@ -5573,11 +5628,11 @@
         </is>
       </c>
       <c r="G25" s="30">
-        <f>'Final BOM'!M72</f>
+        <f>'Final BOM'!M73</f>
         <v/>
       </c>
       <c r="H25" s="30">
-        <f>IF('Final BOM'!M72="","",C25*G25)</f>
+        <f>IF('Final BOM'!M73="","",C25*G25)</f>
         <v/>
       </c>
       <c r="I25" s="27" t="inlineStr">
@@ -5705,7 +5760,7 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-GripBearingCoupons.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-GripBearingCoupons.stl</t>
         </is>
       </c>
       <c r="D5" s="26" t="n">
@@ -5728,7 +5783,7 @@
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-ORingCoupon.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-ORingCoupon.stl</t>
         </is>
       </c>
       <c r="D6" s="26" t="n">
@@ -5751,7 +5806,7 @@
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-SensorSeatCoupon.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-SensorSeatCoupon.stl</t>
         </is>
       </c>
       <c r="D7" s="26" t="n">
@@ -5774,7 +5829,7 @@
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-Body.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-Body.stl</t>
         </is>
       </c>
       <c r="D8" s="26" t="n">
@@ -5797,7 +5852,7 @@
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-LowerPanel-Black.stl + -WhiteText.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-LowerPanel-Black.stl + -WhiteText.stl</t>
         </is>
       </c>
       <c r="D9" s="26" t="n">
@@ -5820,7 +5875,7 @@
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-UpperPanel-Black.stl + -WhiteText.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-UpperPanel-Black.stl + -WhiteText.stl</t>
         </is>
       </c>
       <c r="D10" s="26" t="n">
@@ -5843,7 +5898,7 @@
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-Trigger.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-Trigger.stl</t>
         </is>
       </c>
       <c r="D11" s="26" t="n">
@@ -5866,7 +5921,7 @@
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-Hat-Cap.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-Hat-Cap.stl</t>
         </is>
       </c>
       <c r="D12" s="26" t="n">
@@ -5889,7 +5944,7 @@
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-Hat-RockerPlate.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-Hat-RockerPlate.stl</t>
         </is>
       </c>
       <c r="D13" s="26" t="n">
@@ -5912,7 +5967,7 @@
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-Hat-Bezel.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-Hat-Bezel.stl</t>
         </is>
       </c>
       <c r="D14" s="26" t="n">
@@ -5935,7 +5990,7 @@
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-ThrottleGrip.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-ThrottleGrip.stl</t>
         </is>
       </c>
       <c r="D15" s="26" t="n">
@@ -5958,7 +6013,7 @@
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-FrictionCollar.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-FrictionCollar.stl</t>
         </is>
       </c>
       <c r="D16" s="26" t="n">
@@ -5981,7 +6036,7 @@
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-Pinion.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-Pinion.stl</t>
         </is>
       </c>
       <c r="D17" s="26" t="n">
@@ -6004,7 +6059,7 @@
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4/stl/HueyHeadR4-MagnetShaft.stl</t>
+          <t>Head/Rev5/stl/HueyHeadR5-MagnetShaft.stl</t>
         </is>
       </c>
       <c r="D18" s="26" t="n">
@@ -6257,7 +6312,7 @@
       </c>
       <c r="E29" s="27" t="inlineStr">
         <is>
-          <t>Top face down; glue the M5 x 20's head into it</t>
+          <t>Top face down; the M5 x 16 hex bolt's head presses into its hex pocket</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6438,7 @@
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>Took an M6 hex head; the base now prints its own knob for the M5 x 20</t>
+          <t>Took an M6 hex head; the base now prints its own knob for an M5 x 16 hex bolt</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
@@ -6921,12 +6976,12 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Head/Rev4</t>
+          <t>Head/Rev5</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>Current head design: Rev 4, one piece (Rev 3 with its neck block and trigger mount built back into the box). Rev 3 (Head/Rev3) is the same head in three parts, with no supports; Rev 2 (Head/) is superseded</t>
+          <t>Current head design: Rev 5, Rev 4 cut to the real UH-1 panels' dimensions, with printed threads. Rev 4 (Head/Rev4), the larger one-piece head it came from, is kept as a fallback</t>
         </is>
       </c>
     </row>

--- a/BOM/Heli_Collective_Final_BOM.xlsx
+++ b/BOM/Heli_Collective_Final_BOM.xlsx
@@ -3404,67 +3404,69 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="21" t="n">
+      <c r="A55" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="B55" s="22" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>Lever halves</t>
         </is>
       </c>
-      <c r="C55" s="21" t="n">
+      <c r="C55" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D55" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="21">
-        <f>ROUNDUP(C55*$C$3/D55,0)</f>
-        <v/>
-      </c>
-      <c r="F55" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="21">
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="E55" s="10">
+        <f>IF($C$3&gt;0,C55,0)</f>
+        <v/>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="10">
         <f>MAX(0,E55-F55)</f>
         <v/>
       </c>
-      <c r="H55" s="22" t="inlineStr">
-        <is>
-          <t>M4 x 20 countersunk screw + M4 hex nut</t>
-        </is>
-      </c>
-      <c r="I55" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J55" s="22" t="inlineStr"/>
-      <c r="K55" s="22" t="inlineStr">
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Socket head cap screws M4 x 30 / 35 / 40 / 45 / 50, 12.9 black oxide, 10 of each, with 50 M4 nuts, flat and lock washers and a hex key (200 pieces)</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>HELIFOUNER</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr"/>
+      <c r="K55" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L55" s="24" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M55" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="25">
+      <c r="L55" s="13" t="inlineStr">
+        <is>
+          <t>B0CDSKK7V1</t>
+        </is>
+      </c>
+      <c r="M55" s="14" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="N55" s="14">
         <f>IF(M55="","",G55*M55)</f>
         <v/>
       </c>
-      <c r="O55" s="22" t="inlineStr">
-        <is>
-          <t>In the screw kit. From the top, the heads 16 mm down their counterbores (a long 2.5 mm hex key helps); the nuts go in the lower half's pockets first</t>
-        </is>
-      </c>
-      <c r="P55" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+      <c r="O55" s="11" t="inlineStr">
+        <is>
+          <t>Uses 4 x M4 x 40, with 4 of its M4 nuts. The heads sit flush in 8 mm counterbores at the top and the nuts in hex pockets open to the underside, as far apart as the lever allows; no tip protrudes. The nuts go into the lower half's pockets first</t>
+        </is>
+      </c>
+      <c r="P55" s="11" t="inlineStr">
+        <is>
+          <t>Base/README.md, Bought parts; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3955,7 @@
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>M5 x 16 hex-head bolt (ISO 4017 / DIN 933), zinc or stainless</t>
+          <t>M5 x 25 hex-head bolt (ISO 4017 / DIN 933), zinc or stainless</t>
         </is>
       </c>
       <c r="I63" s="17" t="inlineStr"/>
@@ -4201,7 +4203,7 @@
       </c>
       <c r="O68" s="11" t="inlineStr">
         <is>
-          <t>Every countersunk screw and nut in the head and base (the green lines). Used: M3 x 12 (4), M3 x 16 (8), M3 x 20 (8), M4 x 12 (2), M4 x 16 (4), M4 x 20 (9); nuts M3 (4), M4 (17), M5 (1). Your order (link 2026-10-23)</t>
+          <t>Every countersunk screw and nut in the head and base (the green lines). Used: M3 x 12 (4), M3 x 16 (8), M3 x 20 (8), M4 x 12 (2), M4 x 16 (4), M4 x 20 (5); nuts M3 (4), M4 (13), M5 (1). Your order (link 2026-10-23)</t>
         </is>
       </c>
       <c r="P68" s="11" t="inlineStr">
@@ -6312,7 +6314,7 @@
       </c>
       <c r="E29" s="27" t="inlineStr">
         <is>
-          <t>Top face down; the M5 x 16 hex bolt's head presses into its hex pocket</t>
+          <t>Top face down; the M5 x 25 hex bolt's head presses into its hex pocket</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6440,7 @@
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>Took an M6 hex head; the base now prints its own knob for an M5 x 16 hex bolt</t>
+          <t>Took an M6 hex head; the base now prints its own knob for an M5 x 25 hex bolt</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">

--- a/BOM/Heli_Collective_Final_BOM.xlsx
+++ b/BOM/Heli_Collective_Final_BOM.xlsx
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="C58" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" s="21" t="n">
         <v>1</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O58" s="22" t="inlineStr">
         <is>
-          <t>In the screw kit. Collar clamp: the head sits 2 mm into the -y ear, the nut in the +y ear's pocket</t>
+          <t>In the screw kit. Collar clamp, two 20 mm apart: each head sits 2 mm into the -y ear, its nut in the +y ear's pocket</t>
         </is>
       </c>
       <c r="P58" s="22" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O68" s="11" t="inlineStr">
         <is>
-          <t>Every countersunk screw and nut in the head and base (the green lines). Used: M3 x 12 (4), M3 x 16 (8), M3 x 20 (8), M4 x 12 (2), M4 x 16 (4), M4 x 20 (5); nuts M3 (4), M4 (13), M5 (1). Your order (link 2026-10-23)</t>
+          <t>Every countersunk screw and nut in the head and base (the green lines). Used: M3 x 12 (4), M3 x 16 (8), M3 x 20 (8), M4 x 12 (3), M4 x 16 (4), M4 x 20 (5); nuts M3 (4), M4 (14), M5 (1). Your order (link 2026-10-23)</t>
         </is>
       </c>
       <c r="P68" s="11" t="inlineStr">

--- a/BOM/Heli_Collective_Final_BOM.xlsx
+++ b/BOM/Heli_Collective_Final_BOM.xlsx
@@ -106,17 +106,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -222,22 +222,22 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -253,19 +253,19 @@
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -633,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -664,7 +664,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything bought for one collective: the HeliSR Rev 3.0 board (the bare PCB is ordered from OSH Park; every part on it comes from Digi-Key), the Huey head and the MkIII base Rev 3 (a concept, not yet printed). Blue line: already ordered. Green: covered by a kit or pack priced on another line. Orange: size taken from the base's CAD, not from a parts list, so check before ordering. Prices are pack prices: Digi-Key cart (2026-10-23), Amazon listings (2026-10-22 and 2026-10-23) and the OSH Park order, before shipping and tariff. The Digi-Key order sheet lists the electronics to order from Digi-Key.</t>
+          <t>Everything bought for one collective: the HeliSR Rev 4.0 board (the bare PCB from OSH Park, every part on it from Digi-Key), the Huey head and the MkIII base Rev 3 (a concept, not yet printed). Packs bought counts what's already ordered, including the Digi-Key order placed for Rev 3.0: Rev 4.0 shares most of its parts. Blue line: already ordered. Green: covered by a kit or pack priced on another line. Orange: size taken from the base's CAD, not from a parts list, so check before ordering. Prices are pack prices: Digi-Key cart (2026-10-23), Amazon listings (2026-10-22 and 2026-10-23) and the OSH Park order, before shipping and tariff. The Digi-Key order sheet lists the electronics to order from Digi-Key.</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>HeliSR Rev 3.0: the parts you solder to the bare board (Digi-Key)</t>
+          <t>HeliSR Rev 4.0: the parts you solder to the bare board (Digi-Key)</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -847,12 +847,12 @@
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>Under the Pro Micro: fit before the sockets</t>
+          <t>Front, under the Pro Micro: fit before the sockets</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>PCB/HeliSR_Rev3.0 board BOM (checked against the ordered board)</t>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
         </is>
       </c>
     </row>
@@ -921,76 +921,76 @@
       </c>
       <c r="P8" s="11" t="inlineStr">
         <is>
-          <t>PCB/HeliSR_Rev3.0 board BOM (checked against the ordered board)</t>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>C1, C2</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="n">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>C1, C2, C4</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15">
+        <f>ROUNDUP(C9*$C$3/D9,0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10">
-        <f>ROUNDUP(C9*$C$3/D9,0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="10">
+      <c r="G9" s="15">
         <f>MAX(0,E9-F9)</f>
         <v/>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>Capacitor, 100 nF, 50 V, X7R, 1206</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>CL31B104KBCNNNC</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>Digi-Key</t>
         </is>
       </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>1276-1017-1-ND</t>
         </is>
       </c>
-      <c r="M9" s="14" t="n">
+      <c r="M9" s="19" t="n">
         <v>0.14</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="19">
         <f>IF(M9="","",G9*M9)</f>
         <v/>
       </c>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>Decoupling: C1 beside U1's VCC pin, C2 beside U2's</t>
-        </is>
-      </c>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0 board BOM (checked against the ordered board)</t>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>Decoupling: C1 beside U1's VCC pin, C2 beside U2's (front); C4 beside U3's (back)</t>
+        </is>
+      </c>
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
         </is>
       </c>
     </row>
@@ -1059,214 +1059,214 @@
       </c>
       <c r="P10" s="11" t="inlineStr">
         <is>
-          <t>PCB/HeliSR_Rev3.0 board BOM (checked against the ordered board)</t>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>R1, R2</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15">
         <f>ROUNDUP(C11*$C$3/D11,0)</f>
         <v/>
       </c>
-      <c r="F11" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="10">
+      <c r="F11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15">
         <f>MAX(0,E11-F11)</f>
         <v/>
       </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>Resistor, 1 kOhm, 1 %, 1/8 W, 0805</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>I2C switch, 4 channels, with reset, SOIC-16 (narrow, D package)</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>PCA9546ADR</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>296-21770-1-ND</t>
+        </is>
+      </c>
+      <c r="M11" s="19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="N11" s="19">
+        <f>IF(M11="","",G11*M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>Back. Gives each AS5600 port its own I2C channel (they all answer at 0x36). Not the wide DW package</t>
+        </is>
+      </c>
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>R1-R8</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15">
+        <f>ROUNDUP(C12*$C$3/D12,0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15">
+        <f>MAX(0,E12-F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>Resistor, 2.2 kOhm, 1 %, 1/4 W, 1206</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>YAGEO</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>RC0805FR-071KL</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>RC1206FR-072K2L</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>Digi-Key</t>
         </is>
       </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>311-1.00KCRCT-ND</t>
-        </is>
-      </c>
-      <c r="M11" s="14" t="n">
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>311-2.20KFRCT-ND</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="N11" s="14">
-        <f>IF(M11="","",G11*M11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="11" t="inlineStr">
-        <is>
-          <t>In series with PROG1 (R1) and PROG4 (R2)</t>
-        </is>
-      </c>
-      <c r="P11" s="11" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0 board BOM (checked against the ordered board)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>SW1-SW3</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
+      <c r="N12" s="19">
+        <f>IF(M12="","",G12*M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>Back: the ports' I2C pull-ups, a pair under each port (R1/R2 AX1, R3/R4 AX2, R5/R6 AX3, R7/R8 AX4; the odd one SDA, the even one SCL)</t>
+        </is>
+      </c>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>R9-R11</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10">
-        <f>ROUNDUP(C12*$C$3/D12,0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="10">
-        <f>MAX(0,E12-F12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Tactile switch, SMD, 3.9 x 2.9 mm, gull wing</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>E-Switch</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>TL1015AF160QG</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="D13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="15">
+        <f>ROUNDUP(C13*$C$3/D13,0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15">
+        <f>MAX(0,E13-F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kOhm, 1 %, 1/4 W, 1206</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>RC1206FR-0710KL</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t>Digi-Key</t>
         </is>
       </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>EG4344CT-ND</t>
-        </is>
-      </c>
-      <c r="M12" s="14" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="N12" s="14">
-        <f>IF(M12="","",G12*M12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="11" t="inlineStr">
-        <is>
-          <t>SW1 RST, SW2 PROG1 (AX1), SW3 PROG4 (AX4). The four ground tabs are left unsoldered</t>
-        </is>
-      </c>
-      <c r="P12" s="11" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0 board BOM (checked against the ordered board)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>J1, J2</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="10">
-        <f>ROUNDUP(C13*$C$3/D13,0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="10">
-        <f>MAX(0,E13-F13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>JST SR/SH header, 10-pin, 1.0 mm, SMD, top entry</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>JST</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>BM10B-SRSS-TBT</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>Digi-Key</t>
-        </is>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>455-BM10B-SRSS-TBTCT-ND</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="N13" s="14">
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>311-10.0KFRCT-ND</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N13" s="19">
         <f>IF(M13="","",G13*M13)</f>
         <v/>
       </c>
-      <c r="O13" s="11" t="inlineStr">
-        <is>
-          <t>Switch inputs: J1 IN1-IN8, J2 IN9-IN16. Digi-Key estimates $0.33 tariff each on top</t>
-        </is>
-      </c>
-      <c r="P13" s="11" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0 board BOM (checked against the ordered board)</t>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>Back: pull-ups on the Pro Micro's SDA (R9) and SCL (R10), and on U3's /RESET (R11). Any 1 % 1206 10 kOhm resistor will do if this one is out of stock</t>
+        </is>
+      </c>
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
         </is>
       </c>
     </row>
@@ -1276,11 +1276,11 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>J11-J14</t>
+          <t>SW1</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>1</v>
@@ -1290,7 +1290,7 @@
         <v/>
       </c>
       <c r="F14" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="10">
         <f>MAX(0,E14-F14)</f>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>JST SR/SH header, 3-pin, 1.0 mm, SMD, top entry</t>
+          <t>Tactile switch, SMD, 3.9 x 2.9 mm, gull wing</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>E-Switch</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>BM03B-SRSS-TBT</t>
+          <t>TL1015AF160QG</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr">
@@ -1318,11 +1318,11 @@
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>455-BM03B-SRSS-TBTCT-ND</t>
+          <t>EG4344CT-ND</t>
         </is>
       </c>
       <c r="M14" s="14" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="N14" s="14">
         <f>IF(M14="","",G14*M14)</f>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Analog inputs AX1-AX4 (J11-J14). Digi-Key estimates $0.26 tariff each on top. Fit all four, or only the inputs you use</t>
+          <t>RST, at the far end between AX4 and AX2. The four ground tabs are left unsoldered</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>PCB/HeliSR_Rev3.0 board BOM (checked against the ordered board)</t>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>J7, J8</t>
+          <t>J1, J2</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Socket header, female, 1x12, 2.54 mm, through hole</t>
+          <t>JST SR/SH header, 10-pin, 1.0 mm, SMD, top entry</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Sullins</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>PPTC121LFBN-RC</t>
+          <t>BM10B-SRSS-TBT</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
@@ -1387,11 +1387,11 @@
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>S6100-ND</t>
+          <t>455-BM10B-SRSS-TBTCT-ND</t>
         </is>
       </c>
       <c r="M15" s="14" t="n">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="N15" s="14">
         <f>IF(M15="","",G15*M15)</f>
@@ -1399,751 +1399,751 @@
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
+          <t>Switch inputs: J1 IN1-IN8, J2 IN9-IN16. Digi-Key estimates $0.33 tariff each on top</t>
+        </is>
+      </c>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>J11-J14</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <f>ROUNDUP(C16*$C$3/D16,0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="15">
+        <f>MAX(0,E16-F16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>JST SR/SH header, 4-pin, 1.0 mm, SMD, top entry</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>BM04B-SRSS-TBT</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>455-BM04B-SRSS-TBTCT-ND</t>
+        </is>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N16" s="19">
+        <f>IF(M16="","",G16*M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="16" t="inlineStr">
+        <is>
+          <t>AS5600 ports AX1-AX4 (J11-J14): 1 SDA, 2 GND, 3 VCC, 4 SCL. Fit all four, or only the ports you use</t>
+        </is>
+      </c>
+      <c r="P16" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>J7, J8</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10">
+        <f>ROUNDUP(C17*$C$3/D17,0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="10">
+        <f>MAX(0,E17-F17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Socket header, female, 1x12, 2.54 mm, through hole</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Sullins</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>PPTC121LFBN-RC</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>S6100-ND</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N17" s="14">
+        <f>IF(M17="","",G17*M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
           <t>Pro Micro sockets. Fit last</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0 board BOM (checked against the ordered board)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="M16" s="3" t="inlineStr">
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev4.0 board BOM (checked against the board file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N16" s="15">
-        <f>SUM(N7:N15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>HeliSR Rev 3.0: bare PCB and controller</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
-      <c r="P17" s="9" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="N18" s="20">
+        <f>SUM(N7:N17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>HeliSR Rev 4.0: bare PCB and controller</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="10" t="n">
+      <c r="C20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="10">
-        <f>ROUNDUP(C18*$C$3/D18,0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="10">
-        <f>MAX(0,E18-F18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>HeliSR Rev 3.0 bare PCB (no parts fitted), 2 layers, 1.6 mm FR4, 39.3 x 33.64 mm</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="E20" s="15">
+        <f>ROUNDUP(C20*$C$3/D20,0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="15">
+        <f>MAX(0,E20-F20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>HeliSR Rev 4.0 bare PCB (no parts fitted), 2 layers, 1.6 mm FR4, 39.3 x 33.64 mm</t>
+        </is>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>OSH Park</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr"/>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr"/>
+      <c r="K20" s="16" t="inlineStr">
         <is>
           <t>OSH Park</t>
         </is>
       </c>
-      <c r="L18" s="13" t="inlineStr"/>
-      <c r="M18" s="14" t="n">
+      <c r="L20" s="18" t="inlineStr"/>
+      <c r="M20" s="19" t="n">
         <v>10.2</v>
       </c>
-      <c r="N18" s="14">
-        <f>IF(M18="","",G18*M18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="11" t="inlineStr">
-        <is>
-          <t>Ordered 2026-10-21: $10.20 for three bare boards, free shipping, due back about 2026-10-29</t>
-        </is>
-      </c>
-      <c r="P18" s="11" t="inlineStr">
-        <is>
-          <t>OSH Park order confirmation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="N20" s="19">
+        <f>IF(M20="","",G20*M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>Not ordered yet: upload PCB/HeliSR_Rev4.0/HeliSR_Rev4.0_Gerbers.zip. Priced as Rev 3.0's order: $10.20 for three bare boards, free shipping</t>
+        </is>
+      </c>
+      <c r="P20" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev4.0/README.md; OSH Park order for Rev 3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>J7, J8</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10">
-        <f>ROUNDUP(C19*$C$3/D19,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="10">
-        <f>MAX(0,E19-F19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="C21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10">
+        <f>ROUNDUP(C21*$C$3/D21,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10">
+        <f>MAX(0,E21-F21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>Pro Micro 5V/16 MHz (ATmega32U4), USB-C, with header pins</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>OSOYOO</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr"/>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L19" s="13" t="inlineStr">
+      <c r="L21" s="13" t="inlineStr">
         <is>
           <t>B0B81FGBLY</t>
         </is>
       </c>
-      <c r="M19" s="14" t="n">
+      <c r="M21" s="14" t="n">
         <v>11.99</v>
       </c>
-      <c r="N19" s="14">
-        <f>IF(M19="","",G19*M19)</f>
-        <v/>
-      </c>
-      <c r="O19" s="11" t="inlineStr">
-        <is>
-          <t>Runs MMJoy2; plugs into the J7/J8 sockets. Comes with three rows of header pins, so no separate headers. Also sold as 3 for $21.99. Check that its 2 x 12 pins line up with J7/J8 (15.24 mm between rows)</t>
-        </is>
-      </c>
-      <c r="P19" s="11" t="inlineStr">
+      <c r="N21" s="14">
+        <f>IF(M21="","",G21*M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>Runs the HeliSR firmware (its Rev 4.0 build); plugs into the J7/J8 sockets. Comes with three rows of header pins, so no separate headers. Also sold as 3 for $21.99. Check that its 2 x 12 pins line up with J7/J8 (15.24 mm between rows)</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
         <is>
           <t>Amazon listing on 2026-10-22 (link you sent)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="M20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N20" s="15">
-        <f>SUM(N18:N19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="N22" s="20">
+        <f>SUM(N20:N21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Wiring</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
-      <c r="M21" s="8" t="n"/>
-      <c r="N21" s="8" t="n"/>
-      <c r="O21" s="8" t="n"/>
-      <c r="P21" s="9" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="8" t="n"/>
+      <c r="P23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>J1, J2</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="10">
-        <f>ROUNDUP(C22*$C$3/D22,0)</f>
-        <v/>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="10">
-        <f>MAX(0,E22-F22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="C24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="10">
+        <f>ROUNDUP(C24*$C$3/D24,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="10">
+        <f>MAX(0,E24-F24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>JST SR jumper, 10-pin, 10 in, 30 AWG, pin 1 to pin 1</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>JST</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>A10SR10SR30K254A</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>Digi-Key</t>
         </is>
       </c>
-      <c r="L22" s="13" t="inlineStr">
+      <c r="L24" s="13" t="inlineStr">
         <is>
           <t>455-3671-ND</t>
         </is>
       </c>
-      <c r="M22" s="14" t="n">
+      <c r="M24" s="14" t="n">
         <v>3.17</v>
       </c>
-      <c r="N22" s="14">
-        <f>IF(M22="","",G22*M22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="11" t="inlineStr">
+      <c r="N24" s="14">
+        <f>IF(M24="","",G24*M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
         <is>
           <t>Switch loom. The jumper has a connector at each end: cut it in half for the two board-end pigtails (J1 and J2). Price from Digi-Key, 2026-10-22</t>
         </is>
       </c>
-      <c r="P22" s="11" t="inlineStr">
+      <c r="P24" s="11" t="inlineStr">
         <is>
           <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>J11, J14</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C25" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="10">
-        <f>ROUNDUP(C23*$C$3/D23,0)</f>
-        <v/>
-      </c>
-      <c r="F23" s="12" t="n">
+      <c r="D25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15">
+        <f>ROUNDUP(C25*$C$3/D25,0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15">
+        <f>MAX(0,E25-F25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>JST SR jumper, 4 positions, socket to socket (reversed), 8 in (203 mm)</t>
+        </is>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>A04SR04SR30K203A</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L25" s="18" t="inlineStr">
+        <is>
+          <t>455-3633-ND</t>
+        </is>
+      </c>
+      <c r="M25" s="19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="N25" s="19">
+        <f>IF(M25="","",G25*M25)</f>
+        <v/>
+      </c>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>AX1 (collective sensor) and AX4 (throttle sensor); AX2 and AX3 are spare. Cut each in half for a board-end pigtail. The plug is keyed but the wires may all be one colour: find pin 1 (SDA) with a meter. Ports: 1 SDA, 2 GND, 3 VCC, 4 SCL</t>
+        </is>
+      </c>
+      <c r="P25" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key listing 2026-10-27; PCB/HeliSR_Rev4.0/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>AX1 lead</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="21">
+        <f>ROUNDUP(C26*$C$3/D26,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="21">
+        <f>MAX(0,E26-F26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>4-core cable, 28 AWG, one twisted pair, foil and braid shield, 3.61 mm OD, white, 1 m (Digi-Key cut length)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>Tensility</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>30-00099</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L26" s="24" t="inlineStr">
+        <is>
+          <t>839-30-00099-DS-ND</t>
+        </is>
+      </c>
+      <c r="M26" s="25" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N26" s="25">
+        <f>IF(M26="","",G26*M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="22" t="inlineStr">
+        <is>
+          <t>CHECK: Collective sensor lead: from the AS5600 in the base, through the lever's cable channels and up the 470 mm tube, spliced to an AX1 pigtail. SDA and GND on the twisted pair, VCC and SCL on the other two; the shield to GND at the board end only. Length is an estimate: measure your run; Digi-Key sells it by the metre (145 m in stock 2026-10-27; the black 30-00088 was out of stock)</t>
+        </is>
+      </c>
+      <c r="P26" s="22" t="inlineStr">
+        <is>
+          <t>Digi-Key listing 2026-10-27; Base/README.md (the 4-core sensor lead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>USB</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="10">
+        <f>ROUNDUP(C27*$C$3/D27,0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="10">
+        <f>MAX(0,E27-F27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>USB 2.0 cable, USB-A plug to USB-C plug, 2 m (6.56 ft)</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>Stewart Connector</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>SC-2CAK020M</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>380-SC-2CAK020M-ND</t>
+        </is>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="N27" s="14">
+        <f>IF(M27="","",G27*M27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>Cut it about 15 cm from the USB-C plug. Feed the long piece (USB-A end stays at the PC) through the device: laid in the lever's open channels, up the tube and in through the head. The cable cover's spout is a plain 7.5 mm bore. Splice the USB-C stub back on inside the head (red, black, green, white) and leave the shield wire unconnected. The cut costs about 15 cm of the 2 m: check the run still reaches. The head's clearances were checked with a micro-USB plug: check the C plug fits the same way</t>
+        </is>
+      </c>
+      <c r="P27" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key cart 2026-10-23; Head/Rev4/README.md; Base/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="N28" s="20">
+        <f>SUM(N24:N27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Angle sensors</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="8" t="n"/>
+      <c r="O29" s="8" t="n"/>
+      <c r="P29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>AX1, AX4</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="10">
-        <f>MAX(0,E23-F23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>JST SR jumper, 3-pin, 8 in, 30 AWG, pin 1 to pin 1</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>JST</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>A03SR03SR30K203A</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>Digi-Key</t>
-        </is>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>455-3627-ND</t>
-        </is>
-      </c>
-      <c r="M23" s="14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="N23" s="14">
-        <f>IF(M23="","",G23*M23)</f>
-        <v/>
-      </c>
-      <c r="O23" s="11" t="inlineStr">
-        <is>
-          <t>AX1 (collective sensor) and AX4 (throttle sensor); AX2 and AX3 are spare. Price from Digi-Key, 2026-10-22</t>
-        </is>
-      </c>
-      <c r="P23" s="11" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>AX1 lead</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="16">
-        <f>ROUNDUP(C24*$C$3/D24,0)</f>
-        <v/>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="16">
-        <f>MAX(0,E24-F24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>3-core cable, 28 AWG, black, 1 m (Digi-Key cut length)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>Tensility</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>30-01653</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>Digi-Key</t>
-        </is>
-      </c>
-      <c r="L24" s="19" t="inlineStr">
-        <is>
-          <t>839-30-01653-DS-ND</t>
-        </is>
-      </c>
-      <c r="M24" s="20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="N24" s="20">
-        <f>IF(M24="","",G24*M24)</f>
-        <v/>
-      </c>
-      <c r="O24" s="17" t="inlineStr">
-        <is>
-          <t>CHECK: Collective sensor lead: from the AS5600 in the base, through the lever's cable channels and up the 470 mm tube, spliced to an AX1 pigtail. Length is an estimate: measure your run; Digi-Key sells it by the metre</t>
-        </is>
-      </c>
-      <c r="P24" s="17" t="inlineStr">
-        <is>
-          <t>Digi-Key cart 2026-10-23; Base/README.md (the 3-core sensor lead)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>USB</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="10">
-        <f>ROUNDUP(C25*$C$3/D25,0)</f>
-        <v/>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="10">
-        <f>MAX(0,E25-F25)</f>
-        <v/>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>USB 2.0 cable, USB-A plug to USB-C plug, 2 m (6.56 ft)</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>Stewart Connector</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
-          <t>SC-2CAK020M</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>Digi-Key</t>
-        </is>
-      </c>
-      <c r="L25" s="13" t="inlineStr">
-        <is>
-          <t>380-SC-2CAK020M-ND</t>
-        </is>
-      </c>
-      <c r="M25" s="14" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="N25" s="14">
-        <f>IF(M25="","",G25*M25)</f>
-        <v/>
-      </c>
-      <c r="O25" s="11" t="inlineStr">
-        <is>
-          <t>Cut it about 15 cm from the USB-C plug. Feed the long piece (USB-A end stays at the PC) through the device: laid in the lever's open channels, up the tube and in through the head. The cable cover's spout is a plain 7.5 mm bore. Splice the USB-C stub back on inside the head (red, black, green, white) and leave the shield wire unconnected. The cut costs about 15 cm of the 2 m: check the run still reaches. The head's clearances were checked with a micro-USB plug: check the C plug fits the same way</t>
-        </is>
-      </c>
-      <c r="P25" s="11" t="inlineStr">
-        <is>
-          <t>Digi-Key cart 2026-10-23; Head/Rev4/README.md; Base/README.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="M26" s="3" t="inlineStr">
+      <c r="D30" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="10">
+        <f>ROUNDUP(C30*$C$3/D30,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="10">
+        <f>MAX(0,E30-F30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>AS5600 magnetic encoder module, 23 x 23 mm, with 5 x 2 mm diametric magnet</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>WWZMDiB</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr"/>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>B0CM3C8KFT</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="N30" s="14">
+        <f>IF(M30="","",G30*M30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="11" t="inlineStr">
+        <is>
+          <t>Sold in fours. AX1: the collective, in the base, DIR to VCC. AX4: the throttle, in the head, DIR to GND. Read over I2C; the firmware sets each range, nothing is burnt. On each: remove the 0 ohm R1 and R4 (1 kOhm, PGO to GND), check for about 1 uF from VDD3V3 to GND, and measure the pull-ups (see PCB/HeliSR_Rev4.0/README.md, AS5600 modules)</t>
+        </is>
+      </c>
+      <c r="P30" s="11" t="inlineStr">
+        <is>
+          <t>Amazon listing on 2026-10-22 (link you sent); PCB/HeliSR_Rev4.0/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N26" s="15">
-        <f>SUM(N22:N25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Angle sensors</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
-      <c r="L27" s="8" t="n"/>
-      <c r="M27" s="8" t="n"/>
-      <c r="N27" s="8" t="n"/>
-      <c r="O27" s="8" t="n"/>
-      <c r="P27" s="9" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>AX1, AX4</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" s="10">
-        <f>ROUNDUP(C28*$C$3/D28,0)</f>
-        <v/>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="10">
-        <f>MAX(0,E28-F28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>AS5600 magnetic encoder module, 23 x 23 mm, with 5 x 2 mm diametric magnet</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>WWZMDiB</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr"/>
-      <c r="K28" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L28" s="13" t="inlineStr">
-        <is>
-          <t>B0CM3C8KFT</t>
-        </is>
-      </c>
-      <c r="M28" s="14" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="N28" s="14">
-        <f>IF(M28="","",G28*M28)</f>
-        <v/>
-      </c>
-      <c r="O28" s="11" t="inlineStr">
-        <is>
-          <t>Sold in fours. AX1: the collective, in the base, programmed with PROG1, DIR to VCC. AX4: the throttle, in the head, programmed with PROG4, DIR to GND. On each: remove the 0 ohm R1, keep R4</t>
-        </is>
-      </c>
-      <c r="P28" s="11" t="inlineStr">
-        <is>
-          <t>Amazon listing on 2026-10-22 (link you sent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="N29" s="15">
-        <f>SUM(N28:N28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="N31" s="20">
+        <f>SUM(N30:N30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Huey head: switches</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
-      <c r="M30" s="8" t="n"/>
-      <c r="N30" s="8" t="n"/>
-      <c r="O30" s="8" t="n"/>
-      <c r="P30" s="9" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>IN3-IN6</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="10">
-        <f>ROUNDUP(C31*$C$3/D31,0)</f>
-        <v/>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="10">
-        <f>MAX(0,E31-F31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>Toggle switch, SPDT, ON-OFF-ON, M12 bushing, solder lug</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>APEM</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>639H/2</t>
-        </is>
-      </c>
-      <c r="K31" s="11" t="inlineStr">
-        <is>
-          <t>Digi-Key</t>
-        </is>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>679-1223-ND</t>
-        </is>
-      </c>
-      <c r="M31" s="14" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="N31" s="14">
-        <f>IF(M31="","",G31*M31)</f>
-        <v/>
-      </c>
-      <c r="O31" s="11" t="inlineStr">
-        <is>
-          <t>LDG LT EXT / RETR and SL ON / STOW. Common to GND. Price from Digi-Key, 2026-10-22</t>
-        </is>
-      </c>
-      <c r="P31" s="11" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>IN1, IN2</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="10">
-        <f>ROUNDUP(C32*$C$3/D32,0)</f>
-        <v/>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="10">
-        <f>MAX(0,E32-F32)</f>
-        <v/>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>Toggle switch, SPDT, (ON)-OFF-(ON), M12 bushing, solder lug</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>APEM</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>637H/2</t>
-        </is>
-      </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>Digi-Key</t>
-        </is>
-      </c>
-      <c r="L32" s="13" t="inlineStr">
-        <is>
-          <t>679-1219-ND</t>
-        </is>
-      </c>
-      <c r="M32" s="14" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="N32" s="14">
-        <f>IF(M32="","",G32*M32)</f>
-        <v/>
-      </c>
-      <c r="O32" s="11" t="inlineStr">
-        <is>
-          <t>GOV RPM INCR / DECR. Price from Digi-Key, 2026-10-22</t>
-        </is>
-      </c>
-      <c r="P32" s="11" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
-        </is>
-      </c>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="8" t="n"/>
+      <c r="P32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>IN7</t>
+          <t>IN3-IN6</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="10" t="n">
         <v>1</v>
@@ -2165,7 +2165,7 @@
         <v/>
       </c>
       <c r="F33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="10">
         <f>MAX(0,E33-F33)</f>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Toggle switch, SPDT, ON-ON, M12 bushing, solder lug</t>
+          <t>Toggle switch, SPDT, ON-OFF-ON, M12 bushing, solder lug</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>636H/2</t>
+          <t>639H/2</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
@@ -2193,11 +2193,11 @@
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>679-1217-ND</t>
+          <t>679-1223-ND</t>
         </is>
       </c>
       <c r="M33" s="14" t="n">
-        <v>7.55</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="N33" s="14">
         <f>IF(M33="","",G33*M33)</f>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>LDG LT ON (one side wired). Price from Digi-Key, 2026-10-22</t>
+          <t>LDG LT EXT / RETR and SL ON / STOW. Common to GND. Price from Digi-Key, 2026-10-22</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>IN13</t>
+          <t>IN1, IN2</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Push button, large, SPST-NO momentary, M12</t>
+          <t>Toggle switch, SPDT, (ON)-OFF-(ON), M12 bushing, solder lug</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>Same Sky</t>
+          <t>APEM</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>PB4-M-BK-D-67</t>
+          <t>637H/2</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
@@ -2262,11 +2262,11 @@
       </c>
       <c r="L34" s="13" t="inlineStr">
         <is>
-          <t>2223-PB4-M-BK-D-67-ND</t>
+          <t>679-1219-ND</t>
         </is>
       </c>
       <c r="M34" s="14" t="n">
-        <v>2.52</v>
+        <v>8.02</v>
       </c>
       <c r="N34" s="14">
         <f>IF(M34="","",G34*M34)</f>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>STOP REL</t>
+          <t>GOV RPM INCR / DECR. Price from Digi-Key, 2026-10-22</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr">
@@ -2289,11 +2289,11 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>IN9-IN12, IN14</t>
+          <t>IN7</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>1</v>
@@ -2303,7 +2303,7 @@
         <v/>
       </c>
       <c r="F35" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G35" s="10">
         <f>MAX(0,E35-F35)</f>
@@ -2311,17 +2311,17 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Tactile switch, 6 x 6 mm, 5 mm high, THT</t>
+          <t>Toggle switch, SPDT, ON-ON, M12 bushing, solder lug</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>APEM</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>1825910-6</t>
+          <t>636H/2</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr">
@@ -2331,11 +2331,11 @@
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>450-1650-ND</t>
+          <t>679-1217-ND</t>
         </is>
       </c>
       <c r="M35" s="14" t="n">
-        <v>0.13</v>
+        <v>7.55</v>
       </c>
       <c r="N35" s="14">
         <f>IF(M35="","",G35*M35)</f>
@@ -2343,766 +2343,770 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
+          <t>LDG LT ON (one side wired). Price from Digi-Key, 2026-10-22</t>
+        </is>
+      </c>
+      <c r="P35" s="11" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>IN13</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="10">
+        <f>ROUNDUP(C36*$C$3/D36,0)</f>
+        <v/>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="10">
+        <f>MAX(0,E36-F36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Push button, large, SPST-NO momentary, M12</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>Same Sky</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>PB4-M-BK-D-67</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L36" s="13" t="inlineStr">
+        <is>
+          <t>2223-PB4-M-BK-D-67-ND</t>
+        </is>
+      </c>
+      <c r="M36" s="14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N36" s="14">
+        <f>IF(M36="","",G36*M36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="11" t="inlineStr">
+        <is>
+          <t>STOP REL</t>
+        </is>
+      </c>
+      <c r="P36" s="11" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>IN9-IN12, IN14</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="10">
+        <f>ROUNDUP(C37*$C$3/D37,0)</f>
+        <v/>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="10">
+        <f>MAX(0,E37-F37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Tactile switch, 6 x 6 mm, 5 mm high, THT</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>1825910-6</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>450-1650-ND</t>
+        </is>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N37" s="14">
+        <f>IF(M37="","",G37*M37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="11" t="inlineStr">
+        <is>
           <t>SEARCH CONT hat (4, new rocker hat) and starter trigger (1). IN8, IN15, IN16 are spare</t>
         </is>
       </c>
-      <c r="P35" s="11" t="inlineStr">
+      <c r="P37" s="11" t="inlineStr">
         <is>
           <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="M36" s="3" t="inlineStr">
+    <row r="38">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N36" s="15">
-        <f>SUM(N31:N35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="N38" s="20">
+        <f>SUM(N33:N37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Huey head: hardware</t>
         </is>
       </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
-      <c r="L37" s="8" t="n"/>
-      <c r="M37" s="8" t="n"/>
-      <c r="N37" s="8" t="n"/>
-      <c r="O37" s="8" t="n"/>
-      <c r="P37" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="21" t="n">
-        <v>22</v>
-      </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="8" t="n"/>
+      <c r="M39" s="8" t="n"/>
+      <c r="N39" s="8" t="n"/>
+      <c r="O39" s="8" t="n"/>
+      <c r="P39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
         <is>
           <t>Tube boss</t>
         </is>
       </c>
-      <c r="C38" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="21">
-        <f>ROUNDUP(C38*$C$3/D38,0)</f>
-        <v/>
-      </c>
-      <c r="F38" s="23" t="n">
+      <c r="C40" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="26">
+        <f>ROUNDUP(C40*$C$3/D40,0)</f>
+        <v/>
+      </c>
+      <c r="F40" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="21">
-        <f>MAX(0,E38-F38)</f>
-        <v/>
-      </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="G40" s="26">
+        <f>MAX(0,E40-F40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="27" t="inlineStr">
         <is>
           <t>M5 x 8 set screw</t>
         </is>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>HIQTRADEBYJJ</t>
         </is>
       </c>
-      <c r="J38" s="22" t="inlineStr"/>
-      <c r="K38" s="22" t="inlineStr">
+      <c r="J40" s="27" t="inlineStr"/>
+      <c r="K40" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L38" s="24" t="inlineStr">
+      <c r="L40" s="29" t="inlineStr">
         <is>
           <t>B0DG33R714</t>
         </is>
       </c>
-      <c r="M38" s="25" t="n">
+      <c r="M40" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="25">
-        <f>IF(M38="","",G38*M38)</f>
-        <v/>
-      </c>
-      <c r="O38" s="22" t="inlineStr">
+      <c r="N40" s="30">
+        <f>IF(M40="","",G40*M40)</f>
+        <v/>
+      </c>
+      <c r="O40" s="27" t="inlineStr">
         <is>
           <t>In the set screw kit. From the boss's front (lower panel off), into its printed M5 thread; the tip pins the tube through the front wall of its 5.2 mm cross hole, 10 mm below the tube's top. Replaces the M5 x 40 bolt and nut (the kit's M5s stop at 20 mm)</t>
         </is>
       </c>
-      <c r="P38" s="22" t="inlineStr">
+      <c r="P40" s="27" t="inlineStr">
         <is>
           <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="21" t="n">
-        <v>23</v>
-      </c>
-      <c r="B39" s="22" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
         <is>
           <t>Friction collar</t>
         </is>
       </c>
-      <c r="C39" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="21">
-        <f>ROUNDUP(C39*$C$3/D39,0)</f>
-        <v/>
-      </c>
-      <c r="F39" s="23" t="n">
+      <c r="C41" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="26">
+        <f>ROUNDUP(C41*$C$3/D41,0)</f>
+        <v/>
+      </c>
+      <c r="F41" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="21">
-        <f>MAX(0,E39-F39)</f>
-        <v/>
-      </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="G41" s="26">
+        <f>MAX(0,E41-F41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="27" t="inlineStr">
         <is>
           <t>M4 x 12 countersunk screw + M4 hex nut</t>
         </is>
       </c>
-      <c r="I39" s="22" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT</t>
         </is>
       </c>
-      <c r="J39" s="22" t="inlineStr"/>
-      <c r="K39" s="22" t="inlineStr">
+      <c r="J41" s="27" t="inlineStr"/>
+      <c r="K41" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L39" s="24" t="inlineStr">
+      <c r="L41" s="29" t="inlineStr">
         <is>
           <t>B0FMD5TMSH</t>
         </is>
       </c>
-      <c r="M39" s="25" t="n">
+      <c r="M41" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N39" s="25">
-        <f>IF(M39="","",G39*M39)</f>
-        <v/>
-      </c>
-      <c r="O39" s="22" t="inlineStr">
+      <c r="N41" s="30">
+        <f>IF(M41="","",G41*M41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="27" t="inlineStr">
         <is>
           <t>In the screw kit. Pinch screw: the head sits 2 mm into the +y ear, the nut in the -y ear's pocket</t>
         </is>
       </c>
-      <c r="P39" s="22" t="inlineStr">
+      <c r="P41" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Throttle grip</t>
         </is>
       </c>
-      <c r="C40" s="10" t="n">
+      <c r="C42" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D42" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E40" s="10">
-        <f>ROUNDUP(C40*$C$3/D40,0)</f>
-        <v/>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="10">
-        <f>MAX(0,E40-F40)</f>
-        <v/>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="E42" s="10">
+        <f>ROUNDUP(C42*$C$3/D42,0)</f>
+        <v/>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="10">
+        <f>MAX(0,E42-F42)</f>
+        <v/>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>O-ring, 24 mm ID x 28 mm OD x 2 mm, nitrile (NBR 70A), pack of 50</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>FOCMKEAS</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-      <c r="K40" s="11" t="inlineStr">
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L40" s="13" t="inlineStr">
+      <c r="L42" s="13" t="inlineStr">
         <is>
           <t>B0BWWBTL4N</t>
         </is>
       </c>
-      <c r="M40" s="14" t="n">
+      <c r="M42" s="14" t="n">
         <v>6.89</v>
       </c>
-      <c r="N40" s="14">
-        <f>IF(M40="","",G40*M40)</f>
-        <v/>
-      </c>
-      <c r="O40" s="11" t="inlineStr">
+      <c r="N42" s="14">
+        <f>IF(M42="","",G42*M42)</f>
+        <v/>
+      </c>
+      <c r="O42" s="11" t="inlineStr">
         <is>
           <t>The grip floats on these: two in grooves in its bore (its bearings on the tube), one in the friction collar's groove and one in the ceiling's groove round the tube. Grease them lightly with silicone grease</t>
         </is>
       </c>
-      <c r="P40" s="11" t="inlineStr">
+      <c r="P42" s="11" t="inlineStr">
         <is>
           <t>Head/Rev5/README.md and Head/Rev4/README.md, Bought; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>Trigger pivot</t>
         </is>
       </c>
-      <c r="C41" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="C43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="E41" s="10">
-        <f>IF($C$3&gt;0,C41,0)</f>
-        <v/>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="10">
-        <f>MAX(0,E41-F41)</f>
-        <v/>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="E43" s="10">
+        <f>IF($C$3&gt;0,C43,0)</f>
+        <v/>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="10">
+        <f>MAX(0,E43-F43)</f>
+        <v/>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>M3 countersunk hex socket screws, 10.9 black oxide, M3 x 20 / 25 / 30 / 35 / 40, 100 pcs</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I43" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-      <c r="K41" s="11" t="inlineStr">
+      <c r="J43" s="11" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L41" s="13" t="inlineStr">
+      <c r="L43" s="13" t="inlineStr">
         <is>
           <t>B0BYXS4BTF</t>
         </is>
       </c>
-      <c r="M41" s="14" t="n">
+      <c r="M43" s="14" t="n">
         <v>9.99</v>
       </c>
-      <c r="N41" s="14">
-        <f>IF(M41="","",G41*M41)</f>
-        <v/>
-      </c>
-      <c r="O41" s="11" t="inlineStr">
+      <c r="N43" s="14">
+        <f>IF(M43="","",G43*M43)</f>
+        <v/>
+      </c>
+      <c r="O43" s="11" t="inlineStr">
         <is>
           <t>Ordered 2026-10-23. Uses the M3 x 25 (ISO 10642 / DIN 7991); the kits stop at 20 mm. Head in the countersink in the mount's left lug, through the trigger, then about 8 mm into the right lug's printed M3 thread; the tip stays about 0.9 mm inside the lug</t>
         </is>
       </c>
-      <c r="P41" s="11" t="inlineStr">
+      <c r="P43" s="11" t="inlineStr">
         <is>
           <t>Head/Rev5/README.md and Head/Rev4/README.md, Bought; user's choice 2026-10-23; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="21" t="n">
-        <v>26</v>
-      </c>
-      <c r="B42" s="22" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
         <is>
           <t>Trigger pull stop</t>
         </is>
       </c>
-      <c r="C42" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="21">
-        <f>ROUNDUP(C42*$C$3/D42,0)</f>
-        <v/>
-      </c>
-      <c r="F42" s="23" t="n">
+      <c r="C44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="26">
+        <f>ROUNDUP(C44*$C$3/D44,0)</f>
+        <v/>
+      </c>
+      <c r="F44" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="21">
-        <f>MAX(0,E42-F42)</f>
-        <v/>
-      </c>
-      <c r="H42" s="22" t="inlineStr">
+      <c r="G44" s="26">
+        <f>MAX(0,E44-F44)</f>
+        <v/>
+      </c>
+      <c r="H44" s="27" t="inlineStr">
         <is>
           <t>M3 x 4 set screw</t>
         </is>
       </c>
-      <c r="I42" s="22" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>HIQTRADEBYJJ</t>
         </is>
       </c>
-      <c r="J42" s="22" t="inlineStr"/>
-      <c r="K42" s="22" t="inlineStr">
+      <c r="J44" s="27" t="inlineStr"/>
+      <c r="K44" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L42" s="24" t="inlineStr">
+      <c r="L44" s="29" t="inlineStr">
         <is>
           <t>B0DG33R714</t>
         </is>
       </c>
-      <c r="M42" s="25" t="n">
+      <c r="M44" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N42" s="25">
-        <f>IF(M42="","",G42*M42)</f>
-        <v/>
-      </c>
-      <c r="O42" s="22" t="inlineStr">
+      <c r="N44" s="30">
+        <f>IF(M44="","",G44*M44)</f>
+        <v/>
+      </c>
+      <c r="O44" s="27" t="inlineStr">
         <is>
           <t>In the set screw kit. Through the trigger's arm (printed M3 thread); its tip bears on the mount. Set it so the starter switch clicks before the stop</t>
         </is>
       </c>
-      <c r="P42" s="22" t="inlineStr">
+      <c r="P44" s="27" t="inlineStr">
         <is>
           <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="21" t="n">
-        <v>27</v>
-      </c>
-      <c r="B43" s="22" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
         <is>
           <t>Trigger pull stop seat</t>
         </is>
       </c>
-      <c r="C43" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="21">
-        <f>ROUNDUP(C43*$C$3/D43,0)</f>
-        <v/>
-      </c>
-      <c r="F43" s="23" t="n">
+      <c r="C45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="26">
+        <f>ROUNDUP(C45*$C$3/D45,0)</f>
+        <v/>
+      </c>
+      <c r="F45" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="21">
-        <f>MAX(0,E43-F43)</f>
-        <v/>
-      </c>
-      <c r="H43" s="22" t="inlineStr">
+      <c r="G45" s="26">
+        <f>MAX(0,E45-F45)</f>
+        <v/>
+      </c>
+      <c r="H45" s="27" t="inlineStr">
         <is>
           <t>M2 x 8 countersunk screw</t>
         </is>
       </c>
-      <c r="I43" s="22" t="inlineStr">
+      <c r="I45" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT</t>
         </is>
       </c>
-      <c r="J43" s="22" t="inlineStr"/>
-      <c r="K43" s="22" t="inlineStr">
+      <c r="J45" s="27" t="inlineStr"/>
+      <c r="K45" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L43" s="24" t="inlineStr">
+      <c r="L45" s="29" t="inlineStr">
         <is>
           <t>B0FMD5TMSH</t>
         </is>
       </c>
-      <c r="M43" s="25" t="n">
+      <c r="M45" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N43" s="25">
-        <f>IF(M43="","",G43*M43)</f>
-        <v/>
-      </c>
-      <c r="O43" s="22" t="inlineStr">
+      <c r="N45" s="30">
+        <f>IF(M45="","",G45*M45)</f>
+        <v/>
+      </c>
+      <c r="O45" s="27" t="inlineStr">
         <is>
           <t>In the screw kit. Flush in a countersunk, M2-tapped hole (1.6 mm pilot) in the mount's face under the spring pocket, so the pull stop's tip bears on steel and not on plastic</t>
         </is>
       </c>
-      <c r="P43" s="22" t="inlineStr">
+      <c r="P45" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="21" t="n">
-        <v>28</v>
-      </c>
-      <c r="B44" s="22" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
         <is>
           <t>Search hat bezel</t>
         </is>
       </c>
-      <c r="C44" s="21" t="n">
+      <c r="C46" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="D44" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="21">
-        <f>ROUNDUP(C44*$C$3/D44,0)</f>
-        <v/>
-      </c>
-      <c r="F44" s="23" t="n">
+      <c r="D46" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="26">
+        <f>ROUNDUP(C46*$C$3/D46,0)</f>
+        <v/>
+      </c>
+      <c r="F46" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="21">
-        <f>MAX(0,E44-F44)</f>
-        <v/>
-      </c>
-      <c r="H44" s="22" t="inlineStr">
+      <c r="G46" s="26">
+        <f>MAX(0,E46-F46)</f>
+        <v/>
+      </c>
+      <c r="H46" s="27" t="inlineStr">
         <is>
           <t>M2 x 8 countersunk screw</t>
         </is>
       </c>
-      <c r="I44" s="22" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT</t>
         </is>
       </c>
-      <c r="J44" s="22" t="inlineStr"/>
-      <c r="K44" s="22" t="inlineStr">
+      <c r="J46" s="27" t="inlineStr"/>
+      <c r="K46" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L44" s="24" t="inlineStr">
+      <c r="L46" s="29" t="inlineStr">
         <is>
           <t>B0FMD5TMSH</t>
         </is>
       </c>
-      <c r="M44" s="25" t="n">
+      <c r="M46" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N44" s="25">
-        <f>IF(M44="","",G44*M44)</f>
-        <v/>
-      </c>
-      <c r="O44" s="22" t="inlineStr">
+      <c r="N46" s="30">
+        <f>IF(M46="","",G46*M46)</f>
+        <v/>
+      </c>
+      <c r="O46" s="27" t="inlineStr">
         <is>
           <t>In the screw kit. Through the hat's bezel into M2 threads tapped in the carrier (1.6 mm pilots)</t>
         </is>
       </c>
-      <c r="P44" s="22" t="inlineStr">
+      <c r="P46" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="21" t="n">
-        <v>29</v>
-      </c>
-      <c r="B45" s="22" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
         <is>
           <t>Search hat pivot</t>
         </is>
       </c>
-      <c r="C45" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="21">
-        <f>ROUNDUP(C45*$C$3/D45,0)</f>
-        <v/>
-      </c>
-      <c r="F45" s="23" t="n">
+      <c r="C47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="26">
+        <f>ROUNDUP(C47*$C$3/D47,0)</f>
+        <v/>
+      </c>
+      <c r="F47" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="21">
-        <f>MAX(0,E45-F45)</f>
-        <v/>
-      </c>
-      <c r="H45" s="22" t="inlineStr">
+      <c r="G47" s="26">
+        <f>MAX(0,E47-F47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="27" t="inlineStr">
         <is>
           <t>M3 x 4 set screw</t>
         </is>
       </c>
-      <c r="I45" s="22" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
         <is>
           <t>HIQTRADEBYJJ</t>
         </is>
       </c>
-      <c r="J45" s="22" t="inlineStr"/>
-      <c r="K45" s="22" t="inlineStr">
+      <c r="J47" s="27" t="inlineStr"/>
+      <c r="K47" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L45" s="24" t="inlineStr">
+      <c r="L47" s="29" t="inlineStr">
         <is>
           <t>B0DG33R714</t>
         </is>
       </c>
-      <c r="M45" s="25" t="n">
+      <c r="M47" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="25">
-        <f>IF(M45="","",G45*M45)</f>
-        <v/>
-      </c>
-      <c r="O45" s="22" t="inlineStr">
+      <c r="N47" s="30">
+        <f>IF(M47="","",G47*M47)</f>
+        <v/>
+      </c>
+      <c r="O47" s="27" t="inlineStr">
         <is>
           <t>In the set screw kit. Into the rocker plate's centre (printed M3 thread), from behind; its tip is the pivot and sets the preload. Turn it with a 1.5 mm hex key through the carrier floor</t>
         </is>
       </c>
-      <c r="P45" s="22" t="inlineStr">
+      <c r="P47" s="27" t="inlineStr">
         <is>
           <t>HIQTRADEBYJJ set screw kit (Amazon B0DG33R714); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="B46" s="22" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
         <is>
           <t>Panels</t>
         </is>
       </c>
-      <c r="C46" s="21" t="n">
+      <c r="C48" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="D46" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="21">
-        <f>ROUNDUP(C46*$C$3/D46,0)</f>
-        <v/>
-      </c>
-      <c r="F46" s="23" t="n">
+      <c r="D48" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="26">
+        <f>ROUNDUP(C48*$C$3/D48,0)</f>
+        <v/>
+      </c>
+      <c r="F48" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="21">
-        <f>MAX(0,E46-F46)</f>
-        <v/>
-      </c>
-      <c r="H46" s="22" t="inlineStr">
+      <c r="G48" s="26">
+        <f>MAX(0,E48-F48)</f>
+        <v/>
+      </c>
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>M3 x 16 countersunk screw (DIN 7991)</t>
         </is>
       </c>
-      <c r="I46" s="22" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT</t>
         </is>
       </c>
-      <c r="J46" s="22" t="inlineStr"/>
-      <c r="K46" s="22" t="inlineStr">
+      <c r="J48" s="27" t="inlineStr"/>
+      <c r="K48" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L46" s="24" t="inlineStr">
+      <c r="L48" s="29" t="inlineStr">
         <is>
           <t>B0FMD5TMSH</t>
         </is>
       </c>
-      <c r="M46" s="25" t="n">
+      <c r="M48" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N46" s="25">
-        <f>IF(M46="","",G46*M46)</f>
-        <v/>
-      </c>
-      <c r="O46" s="22" t="inlineStr">
+      <c r="N48" s="30">
+        <f>IF(M48="","",G48*M48)</f>
+        <v/>
+      </c>
+      <c r="O48" s="27" t="inlineStr">
         <is>
           <t>In the screw kit. 4 per panel, into the M3 threads printed 20 mm deep in the box's corner columns (a kit M3 x 20 fits too)</t>
         </is>
       </c>
-      <c r="P46" s="22" t="inlineStr">
+      <c r="P48" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="21" t="n">
-        <v>31</v>
-      </c>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>HeliSR board</t>
-        </is>
-      </c>
-      <c r="C47" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="21">
-        <f>ROUNDUP(C47*$C$3/D47,0)</f>
-        <v/>
-      </c>
-      <c r="F47" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="21">
-        <f>MAX(0,E47-F47)</f>
-        <v/>
-      </c>
-      <c r="H47" s="22" t="inlineStr">
-        <is>
-          <t>M3 x 12 countersunk screw (DIN 7991) + M3 hex nut</t>
-        </is>
-      </c>
-      <c r="I47" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J47" s="22" t="inlineStr"/>
-      <c r="K47" s="22" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L47" s="24" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="25">
-        <f>IF(M47="","",G47*M47)</f>
-        <v/>
-      </c>
-      <c r="O47" s="22" t="inlineStr">
-        <is>
-          <t>In the screw kit. From outside the rear wall through a spacer and the board</t>
-        </is>
-      </c>
-      <c r="P47" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>HeliSR board</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D48" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="10">
-        <f>ROUNDUP(C48*$C$3/D48,0)</f>
-        <v/>
-      </c>
-      <c r="F48" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G48" s="10">
-        <f>MAX(0,E48-F48)</f>
-        <v/>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>Round spacer, unthreaded, for M3, 4 mm long, 6.4 mm OD, PVC, self-retaining</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>Bivar</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>SRS-4-4MM</t>
-        </is>
-      </c>
-      <c r="K48" s="11" t="inlineStr">
-        <is>
-          <t>Digi-Key</t>
-        </is>
-      </c>
-      <c r="L48" s="13" t="inlineStr">
-        <is>
-          <t>SRS-4-4MM-ND</t>
-        </is>
-      </c>
-      <c r="M48" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N48" s="14">
-        <f>IF(M48="","",G48*M48)</f>
-        <v/>
-      </c>
-      <c r="O48" s="11" t="inlineStr">
-        <is>
-          <t>Between the rear wall and the board</t>
-        </is>
-      </c>
-      <c r="P48" s="11" t="inlineStr">
-        <is>
-          <t>Head/Rev5/README.md and Head/Rev4/README.md, Bought</t>
         </is>
       </c>
     </row>
@@ -3112,14 +3116,14 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>HeliSR board</t>
         </is>
       </c>
       <c r="C49" s="26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49" s="26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E49" s="26">
         <f>ROUNDUP(C49*$C$3/D49,0)</f>
@@ -3134,12 +3138,12 @@
       </c>
       <c r="H49" s="27" t="inlineStr">
         <is>
-          <t>Pen spring, 4 mm OD x 50 mm, 0.4 mm wire, pack of 10</t>
+          <t>M3 x 12 countersunk screw (DIN 7991) + M3 hex nut</t>
         </is>
       </c>
       <c r="I49" s="27" t="inlineStr">
         <is>
-          <t>uxcell</t>
+          <t>AvrestYPT</t>
         </is>
       </c>
       <c r="J49" s="27" t="inlineStr"/>
@@ -3150,11 +3154,11 @@
       </c>
       <c r="L49" s="29" t="inlineStr">
         <is>
-          <t>B0GCZGNBYH</t>
+          <t>B0FMD5TMSH</t>
         </is>
       </c>
       <c r="M49" s="30" t="n">
-        <v>6.99</v>
+        <v>0</v>
       </c>
       <c r="N49" s="30">
         <f>IF(M49="","",G49*M49)</f>
@@ -3162,246 +3166,246 @@
       </c>
       <c r="O49" s="27" t="inlineStr">
         <is>
+          <t>In the screw kit. From outside the rear wall through a spacer and the board</t>
+        </is>
+      </c>
+      <c r="P49" s="27" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>HeliSR board</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="10">
+        <f>ROUNDUP(C50*$C$3/D50,0)</f>
+        <v/>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" s="10">
+        <f>MAX(0,E50-F50)</f>
+        <v/>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Round spacer, unthreaded, for M3, 4 mm long, 6.4 mm OD, PVC, self-retaining</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Bivar</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>SRS-4-4MM</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L50" s="13" t="inlineStr">
+        <is>
+          <t>SRS-4-4MM-ND</t>
+        </is>
+      </c>
+      <c r="M50" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N50" s="14">
+        <f>IF(M50="","",G50*M50)</f>
+        <v/>
+      </c>
+      <c r="O50" s="11" t="inlineStr">
+        <is>
+          <t>Between the rear wall and the board</t>
+        </is>
+      </c>
+      <c r="P50" s="11" t="inlineStr">
+        <is>
+          <t>Head/Rev5/README.md and Head/Rev4/README.md, Bought</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" s="15">
+        <f>ROUNDUP(C51*$C$3/D51,0)</f>
+        <v/>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="15">
+        <f>MAX(0,E51-F51)</f>
+        <v/>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>Pen spring, 4 mm OD x 50 mm, 0.4 mm wire, pack of 10</t>
+        </is>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>uxcell</t>
+        </is>
+      </c>
+      <c r="J51" s="16" t="inlineStr"/>
+      <c r="K51" s="16" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L51" s="18" t="inlineStr">
+        <is>
+          <t>B0GCZGNBYH</t>
+        </is>
+      </c>
+      <c r="M51" s="19" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="N51" s="19">
+        <f>IF(M51="","",G51*M51)</f>
+        <v/>
+      </c>
+      <c r="O51" s="16" t="inlineStr">
+        <is>
           <t>Trigger return: cut to about 13 mm</t>
         </is>
       </c>
-      <c r="P49" s="27" t="inlineStr">
+      <c r="P51" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/README.md and Head/Rev4/README.md, Bought; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="26" t="n">
-        <v>34</v>
-      </c>
-      <c r="B50" s="27" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>Head box</t>
         </is>
       </c>
-      <c r="C50" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="26">
-        <f>ROUNDUP(C50*$C$3/D50,0)</f>
-        <v/>
-      </c>
-      <c r="F50" s="28" t="n">
+      <c r="C52" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15">
+        <f>ROUNDUP(C52*$C$3/D52,0)</f>
+        <v/>
+      </c>
+      <c r="F52" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="26">
-        <f>MAX(0,E50-F50)</f>
-        <v/>
-      </c>
-      <c r="H50" s="27" t="inlineStr">
+      <c r="G52" s="15">
+        <f>MAX(0,E52-F52)</f>
+        <v/>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
         <is>
           <t>Ballast: lead split shot fishing weights, assorted, 120 pcs</t>
         </is>
       </c>
-      <c r="I50" s="27" t="inlineStr">
+      <c r="I52" s="16" t="inlineStr">
         <is>
           <t>SANWEAL</t>
         </is>
       </c>
-      <c r="J50" s="27" t="inlineStr"/>
-      <c r="K50" s="27" t="inlineStr">
+      <c r="J52" s="16" t="inlineStr"/>
+      <c r="K52" s="16" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L50" s="29" t="inlineStr">
+      <c r="L52" s="18" t="inlineStr">
         <is>
           <t>B0H6J3X6GL</t>
         </is>
       </c>
-      <c r="M50" s="30" t="n">
+      <c r="M52" s="19" t="n">
         <v>5.99</v>
       </c>
-      <c r="N50" s="30">
-        <f>IF(M50="","",G50*M50)</f>
-        <v/>
-      </c>
-      <c r="O50" s="27" t="inlineStr">
+      <c r="N52" s="19">
+        <f>IF(M52="","",G52*M52)</f>
+        <v/>
+      </c>
+      <c r="O52" s="16" t="inlineStr">
         <is>
           <t>Only if the gas strut lifts too much: about 48 g for a 45 N strut. Close to the middle of the box. Weigh out what you need</t>
         </is>
       </c>
-      <c r="P50" s="27" t="inlineStr">
+      <c r="P52" s="16" t="inlineStr">
         <is>
           <t>Base/README.md, Bought parts; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="M51" s="3" t="inlineStr">
+    <row r="53">
+      <c r="M53" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N51" s="15">
-        <f>SUM(N38:N50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="N53" s="20">
+        <f>SUM(N40:N52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>MkIII base Rev 3 (concept, not yet printed)</t>
         </is>
       </c>
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="n"/>
-      <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="8" t="n"/>
-      <c r="J52" s="8" t="n"/>
-      <c r="K52" s="8" t="n"/>
-      <c r="L52" s="8" t="n"/>
-      <c r="M52" s="8" t="n"/>
-      <c r="N52" s="8" t="n"/>
-      <c r="O52" s="8" t="n"/>
-      <c r="P52" s="9" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>Pivot</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="10">
-        <f>ROUNDUP(C53*$C$3/D53,0)</f>
-        <v/>
-      </c>
-      <c r="F53" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="10">
-        <f>MAX(0,E53-F53)</f>
-        <v/>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
-        <is>
-          <t>Deep-groove ball bearing 6006-2RS, 30 x 55 x 13 mm</t>
-        </is>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>BlueStars</t>
-        </is>
-      </c>
-      <c r="J53" s="11" t="inlineStr">
-        <is>
-          <t>6006-2RS</t>
-        </is>
-      </c>
-      <c r="K53" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L53" s="13" t="inlineStr">
-        <is>
-          <t>B09XTV8XYK</t>
-        </is>
-      </c>
-      <c r="M53" s="14" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="N53" s="14">
-        <f>IF(M53="","",G53*M53)</f>
-        <v/>
-      </c>
-      <c r="O53" s="11" t="inlineStr">
-        <is>
-          <t>Sold in pairs</t>
-        </is>
-      </c>
-      <c r="P53" s="11" t="inlineStr">
-        <is>
-          <t>Amazon listing on 2026-10-22 (link you sent); Base/mk3_pivot.py (the Rev 1 parts Rev 3 keeps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>Tube</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" s="10">
-        <f>ROUNDUP(C54*$C$3/D54,0)</f>
-        <v/>
-      </c>
-      <c r="F54" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="10">
-        <f>MAX(0,E54-F54)</f>
-        <v/>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>Carbon fibre tube, 25 mm OD x 23 mm ID, 500 mm, 3K plain weave, wrapped</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>MECCANIXITY</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr"/>
-      <c r="K54" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L54" s="13" t="inlineStr">
-        <is>
-          <t>B0CFFT1B31</t>
-        </is>
-      </c>
-      <c r="M54" s="14" t="n">
-        <v>27.49</v>
-      </c>
-      <c r="N54" s="14">
-        <f>IF(M54="","",G54*M54)</f>
-        <v/>
-      </c>
-      <c r="O54" s="11" t="inlineStr">
-        <is>
-          <t>Sold in pairs. Wrapped, as the base needs (not pultruded). Used whole, 500 mm, uncut (470 + the head's extra 12.7 mm of bore + 17.3 mm down in the base's socket). Drill the head's 5.2 mm cross hole 10 mm below the top end and file a 13 mm wide notch, 4+ mm deep, in each side of the bottom end for the cables. Check the socket and head fits with it (coupons)</t>
-        </is>
-      </c>
-      <c r="P54" s="11" t="inlineStr">
-        <is>
-          <t>Amazon listing on 2026-10-22 (link you sent); Base/README.md, Bought parts</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="8" t="n"/>
+      <c r="N54" s="8" t="n"/>
+      <c r="O54" s="8" t="n"/>
+      <c r="P54" s="9" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n">
@@ -3409,19 +3413,17 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Lever halves</t>
+          <t>Pivot</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>once</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E55" s="10">
-        <f>IF($C$3&gt;0,C55,0)</f>
+        <f>ROUNDUP(C55*$C$3/D55,0)</f>
         <v/>
       </c>
       <c r="F55" s="12" t="n">
@@ -3433,15 +3435,19 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Socket head cap screws M4 x 30 / 35 / 40 / 45 / 50, 12.9 black oxide, 10 of each, with 50 M4 nuts, flat and lock washers and a hex key (200 pieces)</t>
+          <t>Deep-groove ball bearing 6006-2RS, 30 x 55 x 13 mm</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>HELIFOUNER</t>
-        </is>
-      </c>
-      <c r="J55" s="11" t="inlineStr"/>
+          <t>BlueStars</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>6006-2RS</t>
+        </is>
+      </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
@@ -3449,11 +3455,11 @@
       </c>
       <c r="L55" s="13" t="inlineStr">
         <is>
-          <t>B0CDSKK7V1</t>
+          <t>B09XTV8XYK</t>
         </is>
       </c>
       <c r="M55" s="14" t="n">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
       <c r="N55" s="14">
         <f>IF(M55="","",G55*M55)</f>
@@ -3461,12 +3467,12 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>Uses 4 x M4 x 40, with 4 of its M4 nuts. The heads sit flush in 8 mm counterbores at the top and the nuts in hex pockets open to the underside, as far apart as the lever allows; no tip protrudes. The nuts go into the lower half's pockets first</t>
+          <t>Sold in pairs</t>
         </is>
       </c>
       <c r="P55" s="11" t="inlineStr">
         <is>
-          <t>Base/README.md, Bought parts; Amazon listing 2026-10-23</t>
+          <t>Amazon listing on 2026-10-22 (link you sent); Base/mk3_pivot.py (the Rev 1 parts Rev 3 keeps)</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3482,7 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Strut</t>
+          <t>Tube</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
@@ -3498,12 +3504,12 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>Gas strut, 6 in (152.4 mm eye to eye), 45 N (sold as 9-12 lb), flat eyelet tabs</t>
+          <t>Carbon fibre tube, 25 mm OD x 23 mm ID, 500 mm, 3K plain weave, wrapped</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>X AUTOHAUX</t>
+          <t>MECCANIXITY</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr"/>
@@ -3514,11 +3520,11 @@
       </c>
       <c r="L56" s="13" t="inlineStr">
         <is>
-          <t>B0CY267GFY</t>
+          <t>B0CFFT1B31</t>
         </is>
       </c>
       <c r="M56" s="14" t="n">
-        <v>13.69</v>
+        <v>27.49</v>
       </c>
       <c r="N56" s="14">
         <f>IF(M56="","",G56*M56)</f>
@@ -3526,522 +3532,534 @@
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
+          <t>Sold in pairs. Wrapped, as the base needs (not pultruded). Used whole, 500 mm, uncut (470 + the head's extra 12.7 mm of bore + 17.3 mm down in the base's socket). Drill the head's 5.2 mm cross hole 10 mm below the top end and file a 13 mm wide notch, 4+ mm deep, in each side of the bottom end for the cables. Check the socket and head fits with it (coupons)</t>
+        </is>
+      </c>
+      <c r="P56" s="11" t="inlineStr">
+        <is>
+          <t>Amazon listing on 2026-10-22 (link you sent); Base/README.md, Bought parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Lever halves</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="E57" s="10">
+        <f>IF($C$3&gt;0,C57,0)</f>
+        <v/>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="10">
+        <f>MAX(0,E57-F57)</f>
+        <v/>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Socket head cap screws M4 x 30 / 35 / 40 / 45 / 50, 12.9 black oxide, 10 of each, with 50 M4 nuts, flat and lock washers and a hex key (200 pieces)</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>HELIFOUNER</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr"/>
+      <c r="K57" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L57" s="13" t="inlineStr">
+        <is>
+          <t>B0CDSKK7V1</t>
+        </is>
+      </c>
+      <c r="M57" s="14" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="N57" s="14">
+        <f>IF(M57="","",G57*M57)</f>
+        <v/>
+      </c>
+      <c r="O57" s="11" t="inlineStr">
+        <is>
+          <t>Uses 4 x M4 x 40, with 4 of its M4 nuts. The heads sit flush in 8 mm counterbores at the top and the nuts in hex pockets open to the underside, as far apart as the lever allows; no tip protrudes. The nuts go into the lower half's pockets first</t>
+        </is>
+      </c>
+      <c r="P57" s="11" t="inlineStr">
+        <is>
+          <t>Base/README.md, Bought parts; Amazon listing 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Strut</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="10">
+        <f>ROUNDUP(C58*$C$3/D58,0)</f>
+        <v/>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="10">
+        <f>MAX(0,E58-F58)</f>
+        <v/>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>Gas strut, 6 in (152.4 mm eye to eye), 45 N (sold as 9-12 lb), flat eyelet tabs</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>X AUTOHAUX</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr"/>
+      <c r="K58" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>B0CY267GFY</t>
+        </is>
+      </c>
+      <c r="M58" s="14" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="N58" s="14">
+        <f>IF(M58="","",G58*M58)</f>
+        <v/>
+      </c>
+      <c r="O58" s="11" t="inlineStr">
+        <is>
           <t>Sold in pairs: the spare is the other half</t>
         </is>
       </c>
-      <c r="P56" s="11" t="inlineStr">
+      <c r="P58" s="11" t="inlineStr">
         <is>
           <t>Base/README.md, Bought parts</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="21" t="n">
-        <v>39</v>
-      </c>
-      <c r="B57" s="22" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>Strut eyes</t>
         </is>
       </c>
-      <c r="C57" s="21" t="n">
+      <c r="C59" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D57" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="21">
-        <f>ROUNDUP(C57*$C$3/D57,0)</f>
-        <v/>
-      </c>
-      <c r="F57" s="23" t="n">
+      <c r="D59" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="26">
+        <f>ROUNDUP(C59*$C$3/D59,0)</f>
+        <v/>
+      </c>
+      <c r="F59" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="21">
-        <f>MAX(0,E57-F57)</f>
-        <v/>
-      </c>
-      <c r="H57" s="22" t="inlineStr">
+      <c r="G59" s="26">
+        <f>MAX(0,E59-F59)</f>
+        <v/>
+      </c>
+      <c r="H59" s="27" t="inlineStr">
         <is>
           <t>M4 x 16 countersunk screw + M4 hex nut</t>
         </is>
       </c>
-      <c r="I57" s="22" t="inlineStr">
+      <c r="I59" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT</t>
         </is>
       </c>
-      <c r="J57" s="22" t="inlineStr"/>
-      <c r="K57" s="22" t="inlineStr">
+      <c r="J59" s="27" t="inlineStr"/>
+      <c r="K59" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L57" s="24" t="inlineStr">
+      <c r="L59" s="29" t="inlineStr">
         <is>
           <t>B0FMD5TMSH</t>
         </is>
       </c>
-      <c r="M57" s="25" t="n">
+      <c r="M59" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N57" s="25">
-        <f>IF(M57="","",G57*M57)</f>
-        <v/>
-      </c>
-      <c r="O57" s="22" t="inlineStr">
+      <c r="N59" s="30">
+        <f>IF(M59="","",G59*M59)</f>
+        <v/>
+      </c>
+      <c r="O59" s="27" t="inlineStr">
         <is>
           <t>In the screw kit. One per eye: head on +y, nut in the -y cheek's pocket. The listing gives the strut's eye holes as 4 mm. Snug, then thread-lock: the eye must still turn</t>
         </is>
       </c>
-      <c r="P57" s="22" t="inlineStr">
+      <c r="P59" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="B58" s="22" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>Strut collar</t>
         </is>
       </c>
-      <c r="C58" s="21" t="n">
+      <c r="C60" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D58" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="21">
-        <f>ROUNDUP(C58*$C$3/D58,0)</f>
-        <v/>
-      </c>
-      <c r="F58" s="23" t="n">
+      <c r="D60" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="26">
+        <f>ROUNDUP(C60*$C$3/D60,0)</f>
+        <v/>
+      </c>
+      <c r="F60" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="21">
-        <f>MAX(0,E58-F58)</f>
-        <v/>
-      </c>
-      <c r="H58" s="22" t="inlineStr">
+      <c r="G60" s="26">
+        <f>MAX(0,E60-F60)</f>
+        <v/>
+      </c>
+      <c r="H60" s="27" t="inlineStr">
         <is>
           <t>M4 x 12 countersunk screw + M4 hex nut</t>
         </is>
       </c>
-      <c r="I58" s="22" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT</t>
         </is>
       </c>
-      <c r="J58" s="22" t="inlineStr"/>
-      <c r="K58" s="22" t="inlineStr">
+      <c r="J60" s="27" t="inlineStr"/>
+      <c r="K60" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L58" s="24" t="inlineStr">
+      <c r="L60" s="29" t="inlineStr">
         <is>
           <t>B0FMD5TMSH</t>
         </is>
       </c>
-      <c r="M58" s="25" t="n">
+      <c r="M60" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N58" s="25">
-        <f>IF(M58="","",G58*M58)</f>
-        <v/>
-      </c>
-      <c r="O58" s="22" t="inlineStr">
+      <c r="N60" s="30">
+        <f>IF(M60="","",G60*M60)</f>
+        <v/>
+      </c>
+      <c r="O60" s="27" t="inlineStr">
         <is>
           <t>In the screw kit. Collar clamp, two 20 mm apart: each head sits 2 mm into the -y ear, its nut in the +y ear's pocket</t>
         </is>
       </c>
-      <c r="P58" s="22" t="inlineStr">
+      <c r="P60" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="21" t="n">
-        <v>41</v>
-      </c>
-      <c r="B59" s="22" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>Down-stops</t>
         </is>
       </c>
-      <c r="C59" s="21" t="n">
+      <c r="C61" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D59" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="21">
-        <f>ROUNDUP(C59*$C$3/D59,0)</f>
-        <v/>
-      </c>
-      <c r="F59" s="23" t="n">
+      <c r="D61" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="26">
+        <f>ROUNDUP(C61*$C$3/D61,0)</f>
+        <v/>
+      </c>
+      <c r="F61" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G59" s="21">
-        <f>MAX(0,E59-F59)</f>
-        <v/>
-      </c>
-      <c r="H59" s="22" t="inlineStr">
+      <c r="G61" s="26">
+        <f>MAX(0,E61-F61)</f>
+        <v/>
+      </c>
+      <c r="H61" s="27" t="inlineStr">
         <is>
           <t>M4 x 16 countersunk screw + 2 M4 hex nuts</t>
         </is>
       </c>
-      <c r="I59" s="22" t="inlineStr">
+      <c r="I61" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT</t>
         </is>
       </c>
-      <c r="J59" s="22" t="inlineStr"/>
-      <c r="K59" s="22" t="inlineStr">
+      <c r="J61" s="27" t="inlineStr"/>
+      <c r="K61" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L59" s="24" t="inlineStr">
+      <c r="L61" s="29" t="inlineStr">
         <is>
           <t>B0FMD5TMSH</t>
         </is>
       </c>
-      <c r="M59" s="25" t="n">
+      <c r="M61" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N59" s="25">
-        <f>IF(M59="","",G59*M59)</f>
-        <v/>
-      </c>
-      <c r="O59" s="22" t="inlineStr">
+      <c r="N61" s="30">
+        <f>IF(M61="","",G61*M61)</f>
+        <v/>
+      </c>
+      <c r="O61" s="27" t="inlineStr">
         <is>
           <t>In the screw kit. Head up: its flat top is the stop. One nut pressed into the post's top pocket, the second on top of it locks the height that levels the tube</t>
         </is>
       </c>
-      <c r="P59" s="22" t="inlineStr">
+      <c r="P61" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="21" t="n">
-        <v>42</v>
-      </c>
-      <c r="B60" s="22" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>Pillow-block caps</t>
         </is>
       </c>
-      <c r="C60" s="21" t="n">
+      <c r="C62" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="D60" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="21">
-        <f>ROUNDUP(C60*$C$3/D60,0)</f>
-        <v/>
-      </c>
-      <c r="F60" s="23" t="n">
+      <c r="D62" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="26">
+        <f>ROUNDUP(C62*$C$3/D62,0)</f>
+        <v/>
+      </c>
+      <c r="F62" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="21">
-        <f>MAX(0,E60-F60)</f>
-        <v/>
-      </c>
-      <c r="H60" s="22" t="inlineStr">
+      <c r="G62" s="26">
+        <f>MAX(0,E62-F62)</f>
+        <v/>
+      </c>
+      <c r="H62" s="27" t="inlineStr">
         <is>
           <t>M4 x 20 countersunk screw + M4 hex nut</t>
         </is>
       </c>
-      <c r="I60" s="22" t="inlineStr">
+      <c r="I62" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT</t>
         </is>
       </c>
-      <c r="J60" s="22" t="inlineStr"/>
-      <c r="K60" s="22" t="inlineStr">
+      <c r="J62" s="27" t="inlineStr"/>
+      <c r="K62" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L60" s="24" t="inlineStr">
+      <c r="L62" s="29" t="inlineStr">
         <is>
           <t>B0FMD5TMSH</t>
         </is>
       </c>
-      <c r="M60" s="25" t="n">
+      <c r="M62" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N60" s="25">
-        <f>IF(M60="","",G60*M60)</f>
-        <v/>
-      </c>
-      <c r="O60" s="22" t="inlineStr">
+      <c r="N62" s="30">
+        <f>IF(M62="","",G62*M62)</f>
+        <v/>
+      </c>
+      <c r="O62" s="27" t="inlineStr">
         <is>
           <t>In the screw kit. Two per cap, from the top; each nut slides into a slot in the block's front or back face. Length from the CAD</t>
         </is>
       </c>
-      <c r="P60" s="22" t="inlineStr">
+      <c r="P62" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>Side covers</t>
         </is>
       </c>
-      <c r="C61" s="10" t="n">
+      <c r="C63" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="E61" s="10">
-        <f>IF($C$3&gt;0,C61,0)</f>
-        <v/>
-      </c>
-      <c r="F61" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="10">
-        <f>MAX(0,E61-F61)</f>
-        <v/>
-      </c>
-      <c r="H61" s="11" t="inlineStr">
+      <c r="E63" s="10">
+        <f>IF($C$3&gt;0,C63,0)</f>
+        <v/>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="10">
+        <f>MAX(0,E63-F63)</f>
+        <v/>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
         <is>
           <t>M3 x 25 countersunk screw (from the M3 x 20-40 set, ASIN B0BYXS4BTF)</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr">
+      <c r="I63" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="J61" s="11" t="inlineStr"/>
-      <c r="K61" s="11" t="inlineStr">
+      <c r="J63" s="11" t="inlineStr"/>
+      <c r="K63" s="11" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L61" s="13" t="inlineStr">
+      <c r="L63" s="13" t="inlineStr">
         <is>
           <t>B0BYXS4BTF</t>
         </is>
       </c>
-      <c r="M61" s="14" t="n">
+      <c r="M63" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N61" s="14">
-        <f>IF(M61="","",G61*M61)</f>
-        <v/>
-      </c>
-      <c r="O61" s="11" t="inlineStr">
+      <c r="N63" s="14">
+        <f>IF(M63="","",G63*M63)</f>
+        <v/>
+      </c>
+      <c r="O63" s="11" t="inlineStr">
         <is>
           <t>From the same 100-piece set as the trigger pivot (20 of each length). Four per cover, from its outer face into M3 threads tapped 11 mm deep in the block and cap: 10 mm of thread, three times the 20 mm screw's. The kit's M3 x 20 would only reach 5</t>
         </is>
       </c>
-      <c r="P61" s="11" t="inlineStr">
+      <c r="P63" s="11" t="inlineStr">
         <is>
           <t>Base/README.md, Bought parts; user's M3 set 2026-10-24; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="21" t="n">
-        <v>44</v>
-      </c>
-      <c r="B62" s="22" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
         <is>
           <t>Cable plug</t>
         </is>
       </c>
-      <c r="C62" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="21">
-        <f>ROUNDUP(C62*$C$3/D62,0)</f>
-        <v/>
-      </c>
-      <c r="F62" s="23" t="n">
+      <c r="C64" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="26">
+        <f>ROUNDUP(C64*$C$3/D64,0)</f>
+        <v/>
+      </c>
+      <c r="F64" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="21">
-        <f>MAX(0,E62-F62)</f>
-        <v/>
-      </c>
-      <c r="H62" s="22" t="inlineStr">
+      <c r="G64" s="26">
+        <f>MAX(0,E64-F64)</f>
+        <v/>
+      </c>
+      <c r="H64" s="27" t="inlineStr">
         <is>
           <t>M2 x 12 countersunk screw</t>
         </is>
       </c>
-      <c r="I62" s="22" t="inlineStr">
+      <c r="I64" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT</t>
         </is>
       </c>
-      <c r="J62" s="22" t="inlineStr"/>
-      <c r="K62" s="22" t="inlineStr">
+      <c r="J64" s="27" t="inlineStr"/>
+      <c r="K64" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="L62" s="24" t="inlineStr">
+      <c r="L64" s="29" t="inlineStr">
         <is>
           <t>B0FMD5TMSH</t>
         </is>
       </c>
-      <c r="M62" s="25" t="n">
+      <c r="M64" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N62" s="25">
-        <f>IF(M62="","",G62*M62)</f>
-        <v/>
-      </c>
-      <c r="O62" s="22" t="inlineStr">
+      <c r="N64" s="30">
+        <f>IF(M64="","",G64*M64)</f>
+        <v/>
+      </c>
+      <c r="O64" s="27" t="inlineStr">
         <is>
           <t>In the screw kit. Up from under the cable cover's rim, through a clearance hole, into an M2 thread tapped in the plug (1.6 mm pilot): pulls the plug that closes the cable's slot down onto the cover's shoulders. Length from the CAD</t>
         </is>
       </c>
-      <c r="P62" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>Friction knob</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="16">
-        <f>ROUNDUP(C63*$C$3/D63,0)</f>
-        <v/>
-      </c>
-      <c r="F63" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="16">
-        <f>MAX(0,E63-F63)</f>
-        <v/>
-      </c>
-      <c r="H63" s="17" t="inlineStr">
-        <is>
-          <t>M5 x 25 hex-head bolt (ISO 4017 / DIN 933), zinc or stainless</t>
-        </is>
-      </c>
-      <c r="I63" s="17" t="inlineStr"/>
-      <c r="J63" s="17" t="inlineStr"/>
-      <c r="K63" s="17" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="L63" s="17" t="inlineStr"/>
-      <c r="M63" s="20" t="n"/>
-      <c r="N63" s="20">
-        <f>IF(M63="","",G63*M63)</f>
-        <v/>
-      </c>
-      <c r="O63" s="17" t="inlineStr">
-        <is>
-          <t>CHECK: Not in the screw kits (they have only countersunk heads): any hardware store. Its head presses into the hex pocket moulded into the printed knob (Base/stl/friction_knob.stl), so the knob turns it; it goes through the spring and the shoe into the M5 nut</t>
-        </is>
-      </c>
-      <c r="P63" s="17" t="inlineStr">
-        <is>
-          <t>Base/README.md, Friction knob</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="21" t="n">
-        <v>46</v>
-      </c>
-      <c r="B64" s="22" t="inlineStr">
-        <is>
-          <t>Friction knob</t>
-        </is>
-      </c>
-      <c r="C64" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="21">
-        <f>ROUNDUP(C64*$C$3/D64,0)</f>
-        <v/>
-      </c>
-      <c r="F64" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="21">
-        <f>MAX(0,E64-F64)</f>
-        <v/>
-      </c>
-      <c r="H64" s="22" t="inlineStr">
-        <is>
-          <t>M5 hex nut</t>
-        </is>
-      </c>
-      <c r="I64" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J64" s="22" t="inlineStr"/>
-      <c r="K64" s="22" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L64" s="24" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M64" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="25">
-        <f>IF(M64="","",G64*M64)</f>
-        <v/>
-      </c>
-      <c r="O64" s="22" t="inlineStr">
-        <is>
-          <t>In the screw kit. Slid into the knob tower's slot from the front; the friction bolt threads into it</t>
-        </is>
-      </c>
-      <c r="P64" s="22" t="inlineStr">
+      <c r="P64" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
@@ -4053,7 +4071,7 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>Shoe hinge</t>
+          <t>Friction knob</t>
         </is>
       </c>
       <c r="C65" s="21" t="n">
@@ -4075,209 +4093,195 @@
       </c>
       <c r="H65" s="22" t="inlineStr">
         <is>
-          <t>M4 x 20 countersunk screw + M4 hex nut</t>
-        </is>
-      </c>
-      <c r="I65" s="22" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
+          <t>M5 x 25 hex-head bolt (ISO 4017 / DIN 933), zinc or stainless</t>
+        </is>
+      </c>
+      <c r="I65" s="22" t="inlineStr"/>
       <c r="J65" s="22" t="inlineStr"/>
       <c r="K65" s="22" t="inlineStr">
         <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L65" s="24" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M65" s="25" t="n">
-        <v>0</v>
-      </c>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="L65" s="22" t="inlineStr"/>
+      <c r="M65" s="25" t="n"/>
       <c r="N65" s="25">
         <f>IF(M65="","",G65*M65)</f>
         <v/>
       </c>
       <c r="O65" s="22" t="inlineStr">
         <is>
+          <t>CHECK: Not in the screw kits (they have only countersunk heads): any hardware store. Its head presses into the hex pocket moulded into the printed knob (Base/stl/friction_knob.stl), so the knob turns it; it goes through the spring and the shoe into the M5 nut</t>
+        </is>
+      </c>
+      <c r="P65" s="22" t="inlineStr">
+        <is>
+          <t>Base/README.md, Friction knob</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="B66" s="27" t="inlineStr">
+        <is>
+          <t>Friction knob</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="26">
+        <f>ROUNDUP(C66*$C$3/D66,0)</f>
+        <v/>
+      </c>
+      <c r="F66" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="26">
+        <f>MAX(0,E66-F66)</f>
+        <v/>
+      </c>
+      <c r="H66" s="27" t="inlineStr">
+        <is>
+          <t>M5 hex nut</t>
+        </is>
+      </c>
+      <c r="I66" s="27" t="inlineStr">
+        <is>
+          <t>AvrestYPT</t>
+        </is>
+      </c>
+      <c r="J66" s="27" t="inlineStr"/>
+      <c r="K66" s="27" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L66" s="29" t="inlineStr">
+        <is>
+          <t>B0FMD5TMSH</t>
+        </is>
+      </c>
+      <c r="M66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="30">
+        <f>IF(M66="","",G66*M66)</f>
+        <v/>
+      </c>
+      <c r="O66" s="27" t="inlineStr">
+        <is>
+          <t>In the screw kit. Slid into the knob tower's slot from the front; the friction bolt threads into it</t>
+        </is>
+      </c>
+      <c r="P66" s="27" t="inlineStr">
+        <is>
+          <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="B67" s="27" t="inlineStr">
+        <is>
+          <t>Shoe hinge</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="26">
+        <f>ROUNDUP(C67*$C$3/D67,0)</f>
+        <v/>
+      </c>
+      <c r="F67" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="26">
+        <f>MAX(0,E67-F67)</f>
+        <v/>
+      </c>
+      <c r="H67" s="27" t="inlineStr">
+        <is>
+          <t>M4 x 20 countersunk screw + M4 hex nut</t>
+        </is>
+      </c>
+      <c r="I67" s="27" t="inlineStr">
+        <is>
+          <t>AvrestYPT</t>
+        </is>
+      </c>
+      <c r="J67" s="27" t="inlineStr"/>
+      <c r="K67" s="27" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L67" s="29" t="inlineStr">
+        <is>
+          <t>B0FMD5TMSH</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="30">
+        <f>IF(M67="","",G67*M67)</f>
+        <v/>
+      </c>
+      <c r="O67" s="27" t="inlineStr">
+        <is>
           <t>In the screw kit. Hinge pin through both frame lugs and the shoe's eye: head in the -y lug, nut in the +y lug's pocket (the lugs are 20 mm apart outside). Snug, then thread-lock: the shoe must still swing</t>
         </is>
       </c>
-      <c r="P65" s="22" t="inlineStr">
+      <c r="P67" s="27" t="inlineStr">
         <is>
           <t>AvrestYPT screw kit (Amazon B0FMD5TMSH); Head/Rev5 and Base/mk3_rev3.py screw lists; renders/*Screws*.png</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="M66" s="3" t="inlineStr">
+    <row r="68">
+      <c r="M68" s="3" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="N66" s="15">
-        <f>SUM(N53:N65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="N68" s="20">
+        <f>SUM(N55:N67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>Kits, consumables and tools</t>
         </is>
       </c>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
-      <c r="E67" s="8" t="n"/>
-      <c r="F67" s="8" t="n"/>
-      <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="n"/>
-      <c r="I67" s="8" t="n"/>
-      <c r="J67" s="8" t="n"/>
-      <c r="K67" s="8" t="n"/>
-      <c r="L67" s="8" t="n"/>
-      <c r="M67" s="8" t="n"/>
-      <c r="N67" s="8" t="n"/>
-      <c r="O67" s="8" t="n"/>
-      <c r="P67" s="9" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>once</t>
-        </is>
-      </c>
-      <c r="E68" s="10">
-        <f>IF($C$3&gt;0,C68,0)</f>
-        <v/>
-      </c>
-      <c r="F68" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="10">
-        <f>MAX(0,E68-F68)</f>
-        <v/>
-      </c>
-      <c r="H68" s="11" t="inlineStr">
-        <is>
-          <t>Screw kit, 1715 pieces: countersunk hex-socket screws M2-M4 x 8, 12, 16, 20 and M5 x 10, 12, 16, 20, with hex nuts and washers, hex keys</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>AvrestYPT</t>
-        </is>
-      </c>
-      <c r="J68" s="11" t="inlineStr"/>
-      <c r="K68" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L68" s="13" t="inlineStr">
-        <is>
-          <t>B0FMD5TMSH</t>
-        </is>
-      </c>
-      <c r="M68" s="14" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="N68" s="14">
-        <f>IF(M68="","",G68*M68)</f>
-        <v/>
-      </c>
-      <c r="O68" s="11" t="inlineStr">
-        <is>
-          <t>Every countersunk screw and nut in the head and base (the green lines). Used: M3 x 12 (4), M3 x 16 (8), M3 x 20 (8), M4 x 12 (3), M4 x 16 (4), M4 x 20 (5); nuts M3 (4), M4 (14), M5 (1). Your order (link 2026-10-23)</t>
-        </is>
-      </c>
-      <c r="P68" s="11" t="inlineStr">
-        <is>
-          <t>Amazon listing 2026-10-23 (your order)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>once</t>
-        </is>
-      </c>
-      <c r="E69" s="10">
-        <f>IF($C$3&gt;0,C69,0)</f>
-        <v/>
-      </c>
-      <c r="F69" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="10">
-        <f>MAX(0,E69-F69)</f>
-        <v/>
-      </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>Set screw kit, 500 pieces, 304 stainless: M3 x 3, 4, 5, 6; M4 x 4, 5, 6; M5 x 5, 8; M6 x 6, 10; M8 x 8; hex keys</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>HIQTRADEBYJJ</t>
-        </is>
-      </c>
-      <c r="J69" s="11" t="inlineStr"/>
-      <c r="K69" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="L69" s="13" t="inlineStr">
-        <is>
-          <t>B0DG33R714</t>
-        </is>
-      </c>
-      <c r="M69" s="14" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="N69" s="14">
-        <f>IF(M69="","",G69*M69)</f>
-        <v/>
-      </c>
-      <c r="O69" s="11" t="inlineStr">
-        <is>
-          <t>The set screws: M5 x 8 (tube, head), M3 x 4 (trigger pull stop). Your order (link 2026-10-23)</t>
-        </is>
-      </c>
-      <c r="P69" s="11" t="inlineStr">
-        <is>
-          <t>Amazon listing 2026-10-23 (your order)</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
+      <c r="N69" s="8" t="n"/>
+      <c r="O69" s="8" t="n"/>
+      <c r="P69" s="9" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="n">
@@ -4285,7 +4289,7 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
@@ -4309,12 +4313,12 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>White lithium grease, 1.5 oz tube</t>
+          <t>Screw kit, 1715 pieces: countersunk hex-socket screws M2-M4 x 8, 12, 16, 20 and M5 x 10, 12, 16, 20, with hex nuts and washers, hex keys</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>Permatex</t>
+          <t>AvrestYPT</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr"/>
@@ -4325,11 +4329,11 @@
       </c>
       <c r="L70" s="13" t="inlineStr">
         <is>
-          <t>B000HBNV58</t>
+          <t>B0FMD5TMSH</t>
         </is>
       </c>
       <c r="M70" s="14" t="n">
-        <v>3.99</v>
+        <v>17.99</v>
       </c>
       <c r="N70" s="14">
         <f>IF(M70="","",G70*M70)</f>
@@ -4337,12 +4341,12 @@
       </c>
       <c r="O70" s="11" t="inlineStr">
         <is>
-          <t>Bearing grease (not silicone paste)</t>
+          <t>Every countersunk screw and nut in the head and base (the green lines). Used: M3 x 12 (4), M3 x 16 (8), M3 x 20 (8), M4 x 12 (3), M4 x 16 (4), M4 x 20 (5); nuts M3 (4), M4 (14), M5 (1). Your order (link 2026-10-23)</t>
         </is>
       </c>
       <c r="P70" s="11" t="inlineStr">
         <is>
-          <t>Head/Rev4/README.md; Base/README.md; Amazon listing 2026-10-23</t>
+          <t>Amazon listing 2026-10-23 (your order)</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4356,7 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
@@ -4376,12 +4380,12 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Silicone faucet grease, waterproof, 0.5 oz</t>
+          <t>Set screw kit, 500 pieces, 304 stainless: M3 x 3, 4, 5, 6; M4 x 4, 5, 6; M5 x 5, 8; M6 x 6, 10; M8 x 8; hex keys</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>Danco</t>
+          <t>HIQTRADEBYJJ</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr"/>
@@ -4392,11 +4396,11 @@
       </c>
       <c r="L71" s="13" t="inlineStr">
         <is>
-          <t>B000DZFUPC</t>
+          <t>B0DG33R714</t>
         </is>
       </c>
       <c r="M71" s="14" t="n">
-        <v>5.68</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N71" s="14">
         <f>IF(M71="","",G71*M71)</f>
@@ -4404,12 +4408,12 @@
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>For the head's four throttle O-rings (grease them lightly before fitting)</t>
+          <t>The set screws: M5 x 8 (tube, head), M3 x 4 (trigger pull stop). Your order (link 2026-10-23)</t>
         </is>
       </c>
       <c r="P71" s="11" t="inlineStr">
         <is>
-          <t>Head/Rev4/README.md; Amazon listing 2026-10-23</t>
+          <t>Amazon listing 2026-10-23 (your order)</t>
         </is>
       </c>
     </row>
@@ -4443,31 +4447,27 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Solder paste, low-temperature (Sn42/Bi58, 138 C), syringe</t>
+          <t>White lithium grease, 1.5 oz tube</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>Chip Quik</t>
-        </is>
-      </c>
-      <c r="J72" s="11" t="inlineStr">
-        <is>
-          <t>NC191LT10</t>
-        </is>
-      </c>
+          <t>Permatex</t>
+        </is>
+      </c>
+      <c r="J72" s="11" t="inlineStr"/>
       <c r="K72" s="11" t="inlineStr">
         <is>
-          <t>Digi-Key</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="L72" s="13" t="inlineStr">
         <is>
-          <t>315-NC191LT10-ND</t>
+          <t>B000HBNV58</t>
         </is>
       </c>
       <c r="M72" s="14" t="n">
-        <v>7.95</v>
+        <v>3.99</v>
       </c>
       <c r="N72" s="14">
         <f>IF(M72="","",G72*M72)</f>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="O72" s="11" t="inlineStr">
         <is>
-          <t>For the SMD parts on the board (U1, U2, the 1206 caps, the JST headers, SW1-SW3). Needs a hot plate or hot air tool and flux. Optional: hand-soldering works too</t>
+          <t>Bearing grease (not silicone paste)</t>
         </is>
       </c>
       <c r="P72" s="11" t="inlineStr">
         <is>
-          <t>Digi-Key cart 2026-10-23</t>
+          <t>Head/Rev4/README.md; Base/README.md; Amazon listing 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -4514,31 +4514,27 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Tweezers, 1 mm tip (Olimex CHN-TWZ1MM), for placing the SMD parts</t>
+          <t>Silicone faucet grease, waterproof, 0.5 oz</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>Olimex</t>
-        </is>
-      </c>
-      <c r="J73" s="11" t="inlineStr">
-        <is>
-          <t>CHN-TWZ1MM</t>
-        </is>
-      </c>
+          <t>Danco</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr"/>
       <c r="K73" s="11" t="inlineStr">
         <is>
-          <t>Digi-Key</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="L73" s="13" t="inlineStr">
         <is>
-          <t>1188-CHN-TWZ1MM-ND</t>
+          <t>B000DZFUPC</t>
         </is>
       </c>
       <c r="M73" s="14" t="n">
-        <v>0.82</v>
+        <v>5.68</v>
       </c>
       <c r="N73" s="14">
         <f>IF(M73="","",G73*M73)</f>
@@ -4546,61 +4542,203 @@
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
+          <t>For the head's four throttle O-rings (grease them lightly before fitting)</t>
+        </is>
+      </c>
+      <c r="P73" s="11" t="inlineStr">
+        <is>
+          <t>Head/Rev4/README.md; Amazon listing 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="E74" s="10">
+        <f>IF($C$3&gt;0,C74,0)</f>
+        <v/>
+      </c>
+      <c r="F74" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="10">
+        <f>MAX(0,E74-F74)</f>
+        <v/>
+      </c>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>Solder paste, low-temperature (Sn42/Bi58, 138 C), syringe</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Chip Quik</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>NC191LT10</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L74" s="13" t="inlineStr">
+        <is>
+          <t>315-NC191LT10-ND</t>
+        </is>
+      </c>
+      <c r="M74" s="14" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="N74" s="14">
+        <f>IF(M74="","",G74*M74)</f>
+        <v/>
+      </c>
+      <c r="O74" s="11" t="inlineStr">
+        <is>
+          <t>For the SMD parts on the board (U1-U3, the 1206 parts, the JST headers, SW1). Needs a hot plate or hot air tool and flux; with parts on both sides, do the back first. Optional: hand-soldering works too</t>
+        </is>
+      </c>
+      <c r="P74" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key cart 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="E75" s="10">
+        <f>IF($C$3&gt;0,C75,0)</f>
+        <v/>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="10">
+        <f>MAX(0,E75-F75)</f>
+        <v/>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>Tweezers, 1 mm tip (Olimex CHN-TWZ1MM), for placing the SMD parts</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Olimex</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>CHN-TWZ1MM</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr">
+        <is>
+          <t>Digi-Key</t>
+        </is>
+      </c>
+      <c r="L75" s="13" t="inlineStr">
+        <is>
+          <t>1188-CHN-TWZ1MM-ND</t>
+        </is>
+      </c>
+      <c r="M75" s="14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N75" s="14">
+        <f>IF(M75="","",G75*M75)</f>
+        <v/>
+      </c>
+      <c r="O75" s="11" t="inlineStr">
+        <is>
           <t>Description from Olimex's sibling CHN-TWZ2MM listing: check the tip</t>
         </is>
       </c>
-      <c r="P73" s="11" t="inlineStr">
+      <c r="P75" s="11" t="inlineStr">
         <is>
           <t>Digi-Key order 102438510</t>
         </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="N74" s="15">
-        <f>SUM(N68:N73)</f>
-        <v/>
       </c>
     </row>
     <row r="76">
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>Still to buy</t>
-        </is>
-      </c>
-      <c r="N76" s="15">
-        <f>N16+N20+N26+N29+N36+N51+N66+N74</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>Whole build</t>
-        </is>
-      </c>
-      <c r="N77" s="15">
-        <f>SUMPRODUCT(E6:E74,M6:M74)</f>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="N76" s="20">
+        <f>SUM(N70:N75)</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="M78" s="3" t="inlineStr">
         <is>
+          <t>Still to buy</t>
+        </is>
+      </c>
+      <c r="N78" s="20">
+        <f>N18+N22+N28+N31+N38+N53+N68+N76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>Whole build</t>
+        </is>
+      </c>
+      <c r="N79" s="20">
+        <f>SUMPRODUCT(E6:E76,M6:M76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="M80" s="3" t="inlineStr">
+        <is>
           <t>Unpriced lines</t>
         </is>
       </c>
-      <c r="N78" s="3">
-        <f>COUNTIFS(A6:A74,"&gt;0",M6:M74,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="N80" s="3">
+        <f>COUNTIFS(A6:A76,"&gt;0",M6:M76,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>Still to buy counts the packs to order; whole build counts every pack needed, bought or not. Both leave out the unpriced lines: generic hardware and wire.</t>
         </is>
@@ -4608,18 +4746,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A17:P17"/>
-    <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A27:P27"/>
-    <mergeCell ref="A67:P67"/>
-    <mergeCell ref="A79:P79"/>
+    <mergeCell ref="A32:P32"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A23:P23"/>
     <mergeCell ref="A6:P6"/>
     <mergeCell ref="D3:P3"/>
-    <mergeCell ref="A30:P30"/>
-    <mergeCell ref="A21:P21"/>
-    <mergeCell ref="A52:P52"/>
+    <mergeCell ref="A39:P39"/>
+    <mergeCell ref="A69:P69"/>
+    <mergeCell ref="A54:P54"/>
+    <mergeCell ref="A29:P29"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A81:P81"/>
+    <mergeCell ref="A19:P19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId1"/>
@@ -4631,20 +4769,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId26"/>
@@ -4656,8 +4794,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId39"/>
@@ -4666,14 +4804,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4686,7 +4826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4710,7 +4850,7 @@
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every line to buy from Digi-Key. Quantities come from the Final BOM's Packs to order, so they follow the collectives to build and anything marked as bought. Heli_Collective_DigiKey.csv holds the same order for one collective (part number, quantity, customer reference), for Digi-Key's cart or BOM upload.</t>
+          <t>Every line to buy from Digi-Key. Quantities come from the Final BOM's Packs to order, so they follow the collectives to build and anything marked as bought. Heli_Collective_DigiKey.csv holds what's still to order for one collective (part number, quantity, customer reference; lines already bought left out), for Digi-Key's cart or BOM upload.</t>
         </is>
       </c>
     </row>
@@ -4762,908 +4902,992 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="A5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>296-8250-1-ND</t>
         </is>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="15">
         <f>'Final BOM'!G7</f>
         <v/>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>SN74HC165DR</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Shift register, 74HC165, SOIC-16</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>U1, U2</t>
         </is>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="19">
         <f>'Final BOM'!M7</f>
         <v/>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="19">
         <f>IF('Final BOM'!M7="","",C5*G5)</f>
         <v/>
       </c>
-      <c r="I5" s="27" t="inlineStr">
-        <is>
-          <t>Under the Pro Micro: fit before the sockets</t>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Front, under the Pro Micro: fit before the sockets</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>4609X-101-103LF-ND</t>
         </is>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="15">
         <f>'Final BOM'!G8</f>
         <v/>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>4609X-101-103LF</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Resistor network, 8 x 10 kOhm bussed, SIP-9</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>RN1, RN2</t>
         </is>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="19">
         <f>'Final BOM'!M8</f>
         <v/>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="19">
         <f>IF('Final BOM'!M8="","",C6*G6)</f>
         <v/>
       </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>Pin 1 (dot) is the common pin: it goes in the square pad. Keep upright</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>1276-1017-1-ND</t>
         </is>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="15">
         <f>'Final BOM'!G9</f>
         <v/>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>CL31B104KBCNNNC</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Capacitor, 100 nF, 50 V, X7R, 1206</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
-        <is>
-          <t>C1, C2</t>
-        </is>
-      </c>
-      <c r="G7" s="30">
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>C1, C2, C4</t>
+        </is>
+      </c>
+      <c r="G7" s="19">
         <f>'Final BOM'!M9</f>
         <v/>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="19">
         <f>IF('Final BOM'!M9="","",C7*G7)</f>
         <v/>
       </c>
-      <c r="I7" s="27" t="inlineStr">
-        <is>
-          <t>Decoupling: C1 beside U1's VCC pin, C2 beside U2's</t>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Decoupling: C1 beside U1's VCC pin, C2 beside U2's (front); C4 beside U3's (back)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>1276-1287-1-ND</t>
         </is>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="15">
         <f>'Final BOM'!G10</f>
         <v/>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>CL31A226KPHNNNE</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Capacitor, 22 uF, 10 V, X5R, 1206</t>
         </is>
       </c>
-      <c r="F8" s="27" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="19">
         <f>'Final BOM'!M10</f>
         <v/>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="19">
         <f>IF('Final BOM'!M10="","",C8*G8)</f>
         <v/>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>Bulk supply capacitor, between U1 and U2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>311-1.00KCRCT-ND</t>
-        </is>
-      </c>
-      <c r="C9" s="26">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>296-21770-1-ND</t>
+        </is>
+      </c>
+      <c r="C9" s="15">
         <f>'Final BOM'!G11</f>
         <v/>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>RC0805FR-071KL</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>Resistor, 1 kOhm, 1 %, 1/8 W, 0805</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="inlineStr">
-        <is>
-          <t>R1, R2</t>
-        </is>
-      </c>
-      <c r="G9" s="30">
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>PCA9546ADR</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>I2C switch, 4 channels, with reset, SOIC-16 (narrow, D package)</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="G9" s="19">
         <f>'Final BOM'!M11</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="19">
         <f>IF('Final BOM'!M11="","",C9*G9)</f>
         <v/>
       </c>
-      <c r="I9" s="27" t="inlineStr">
-        <is>
-          <t>In series with PROG1 (R1) and PROG4 (R2)</t>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>Back. Gives each AS5600 port its own I2C channel (they all answer at 0x36). Not the wide DW package</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>311-2.20KFRCT-ND</t>
+        </is>
+      </c>
+      <c r="C10" s="15">
+        <f>'Final BOM'!G12</f>
+        <v/>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>RC1206FR-072K2L</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Resistor, 2.2 kOhm, 1 %, 1/4 W, 1206</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>R1-R8</t>
+        </is>
+      </c>
+      <c r="G10" s="19">
+        <f>'Final BOM'!M12</f>
+        <v/>
+      </c>
+      <c r="H10" s="19">
+        <f>IF('Final BOM'!M12="","",C10*G10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>Back: the ports' I2C pull-ups, a pair under each port (R1/R2 AX1, R3/R4 AX2, R5/R6 AX3, R7/R8 AX4; the odd one SDA, the even one SCL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>311-10.0KFRCT-ND</t>
+        </is>
+      </c>
+      <c r="C11" s="15">
+        <f>'Final BOM'!G13</f>
+        <v/>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>RC1206FR-0710KL</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kOhm, 1 %, 1/4 W, 1206</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>R9-R11</t>
+        </is>
+      </c>
+      <c r="G11" s="19">
+        <f>'Final BOM'!M13</f>
+        <v/>
+      </c>
+      <c r="H11" s="19">
+        <f>IF('Final BOM'!M13="","",C11*G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>Back: pull-ups on the Pro Micro's SDA (R9) and SCL (R10), and on U3's /RESET (R11). Any 1 % 1206 10 kOhm resistor will do if this one is out of stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>EG4344CT-ND</t>
         </is>
       </c>
-      <c r="C10" s="26">
-        <f>'Final BOM'!G12</f>
-        <v/>
-      </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="C12" s="15">
+        <f>'Final BOM'!G14</f>
+        <v/>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>TL1015AF160QG</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Tactile switch, SMD, 3.9 x 2.9 mm, gull wing</t>
         </is>
       </c>
-      <c r="F10" s="27" t="inlineStr">
-        <is>
-          <t>SW1-SW3</t>
-        </is>
-      </c>
-      <c r="G10" s="30">
-        <f>'Final BOM'!M12</f>
-        <v/>
-      </c>
-      <c r="H10" s="30">
-        <f>IF('Final BOM'!M12="","",C10*G10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="27" t="inlineStr">
-        <is>
-          <t>SW1 RST, SW2 PROG1 (AX1), SW3 PROG4 (AX4). The four ground tabs are left unsoldered</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>SW1</t>
+        </is>
+      </c>
+      <c r="G12" s="19">
+        <f>'Final BOM'!M14</f>
+        <v/>
+      </c>
+      <c r="H12" s="19">
+        <f>IF('Final BOM'!M14="","",C12*G12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>RST, at the far end between AX4 and AX2. The four ground tabs are left unsoldered</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>455-BM10B-SRSS-TBTCT-ND</t>
         </is>
       </c>
-      <c r="C11" s="26">
-        <f>'Final BOM'!G13</f>
-        <v/>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="C13" s="15">
+        <f>'Final BOM'!G15</f>
+        <v/>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>BM10B-SRSS-TBT</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>JST SR/SH header, 10-pin, 1.0 mm, SMD, top entry</t>
         </is>
       </c>
-      <c r="F11" s="27" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>J1, J2</t>
         </is>
       </c>
-      <c r="G11" s="30">
-        <f>'Final BOM'!M13</f>
-        <v/>
-      </c>
-      <c r="H11" s="30">
-        <f>IF('Final BOM'!M13="","",C11*G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="G13" s="19">
+        <f>'Final BOM'!M15</f>
+        <v/>
+      </c>
+      <c r="H13" s="19">
+        <f>IF('Final BOM'!M15="","",C13*G13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>Switch inputs: J1 IN1-IN8, J2 IN9-IN16. Digi-Key estimates $0.33 tariff each on top</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>455-BM03B-SRSS-TBTCT-ND</t>
-        </is>
-      </c>
-      <c r="C12" s="26">
-        <f>'Final BOM'!G14</f>
-        <v/>
-      </c>
-      <c r="D12" s="27" t="inlineStr">
-        <is>
-          <t>BM03B-SRSS-TBT</t>
-        </is>
-      </c>
-      <c r="E12" s="27" t="inlineStr">
-        <is>
-          <t>JST SR/SH header, 3-pin, 1.0 mm, SMD, top entry</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>455-BM04B-SRSS-TBTCT-ND</t>
+        </is>
+      </c>
+      <c r="C14" s="15">
+        <f>'Final BOM'!G16</f>
+        <v/>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>BM04B-SRSS-TBT</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>JST SR/SH header, 4-pin, 1.0 mm, SMD, top entry</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>J11-J14</t>
         </is>
       </c>
-      <c r="G12" s="30">
-        <f>'Final BOM'!M14</f>
-        <v/>
-      </c>
-      <c r="H12" s="30">
-        <f>IF('Final BOM'!M14="","",C12*G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="27" t="inlineStr">
-        <is>
-          <t>Analog inputs AX1-AX4 (J11-J14). Digi-Key estimates $0.26 tariff each on top. Fit all four, or only the inputs you use</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="G14" s="19">
+        <f>'Final BOM'!M16</f>
+        <v/>
+      </c>
+      <c r="H14" s="19">
+        <f>IF('Final BOM'!M16="","",C14*G14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>AS5600 ports AX1-AX4 (J11-J14): 1 SDA, 2 GND, 3 VCC, 4 SCL. Fit all four, or only the ports you use</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>S6100-ND</t>
         </is>
       </c>
-      <c r="C13" s="26">
-        <f>'Final BOM'!G15</f>
-        <v/>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="C15" s="15">
+        <f>'Final BOM'!G17</f>
+        <v/>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>PPTC121LFBN-RC</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>Socket header, female, 1x12, 2.54 mm, through hole</t>
         </is>
       </c>
-      <c r="F13" s="27" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>J7, J8</t>
         </is>
       </c>
-      <c r="G13" s="30">
-        <f>'Final BOM'!M15</f>
-        <v/>
-      </c>
-      <c r="H13" s="30">
-        <f>IF('Final BOM'!M15="","",C13*G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="G15" s="19">
+        <f>'Final BOM'!M17</f>
+        <v/>
+      </c>
+      <c r="H15" s="19">
+        <f>IF('Final BOM'!M17="","",C15*G15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>Pro Micro sockets. Fit last</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="29" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>455-3671-ND</t>
         </is>
       </c>
-      <c r="C14" s="26">
-        <f>'Final BOM'!G22</f>
-        <v/>
-      </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="C16" s="15">
+        <f>'Final BOM'!G24</f>
+        <v/>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>A10SR10SR30K254A</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>JST SR jumper, 10-pin, 10 in, 30 AWG, pin 1 to pin 1</t>
         </is>
       </c>
-      <c r="F14" s="27" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>J1, J2</t>
         </is>
       </c>
-      <c r="G14" s="30">
-        <f>'Final BOM'!M22</f>
-        <v/>
-      </c>
-      <c r="H14" s="30">
-        <f>IF('Final BOM'!M22="","",C14*G14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="G16" s="19">
+        <f>'Final BOM'!M24</f>
+        <v/>
+      </c>
+      <c r="H16" s="19">
+        <f>IF('Final BOM'!M24="","",C16*G16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>Switch loom. The jumper has a connector at each end: cut it in half for the two board-end pigtails (J1 and J2). Price from Digi-Key, 2026-10-22</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>455-3627-ND</t>
-        </is>
-      </c>
-      <c r="C15" s="26">
-        <f>'Final BOM'!G23</f>
-        <v/>
-      </c>
-      <c r="D15" s="27" t="inlineStr">
-        <is>
-          <t>A03SR03SR30K203A</t>
-        </is>
-      </c>
-      <c r="E15" s="27" t="inlineStr">
-        <is>
-          <t>JST SR jumper, 3-pin, 8 in, 30 AWG, pin 1 to pin 1</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>455-3633-ND</t>
+        </is>
+      </c>
+      <c r="C17" s="15">
+        <f>'Final BOM'!G25</f>
+        <v/>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>A04SR04SR30K203A</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>JST SR jumper, 4 positions, socket to socket (reversed), 8 in (203 mm)</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>J11, J14</t>
         </is>
       </c>
-      <c r="G15" s="30">
-        <f>'Final BOM'!M23</f>
-        <v/>
-      </c>
-      <c r="H15" s="30">
-        <f>IF('Final BOM'!M23="","",C15*G15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="27" t="inlineStr">
-        <is>
-          <t>AX1 (collective sensor) and AX4 (throttle sensor); AX2 and AX3 are spare. Price from Digi-Key, 2026-10-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>839-30-01653-DS-ND</t>
-        </is>
-      </c>
-      <c r="C16" s="26">
-        <f>'Final BOM'!G24</f>
-        <v/>
-      </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>30-01653</t>
-        </is>
-      </c>
-      <c r="E16" s="27" t="inlineStr">
-        <is>
-          <t>3-core cable, 28 AWG, black, 1 m (Digi-Key cut length)</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="inlineStr">
+      <c r="G17" s="19">
+        <f>'Final BOM'!M25</f>
+        <v/>
+      </c>
+      <c r="H17" s="19">
+        <f>IF('Final BOM'!M25="","",C17*G17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>AX1 (collective sensor) and AX4 (throttle sensor); AX2 and AX3 are spare. Cut each in half for a board-end pigtail. The plug is keyed but the wires may all be one colour: find pin 1 (SDA) with a meter. Ports: 1 SDA, 2 GND, 3 VCC, 4 SCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>839-30-00099-DS-ND</t>
+        </is>
+      </c>
+      <c r="C18" s="15">
+        <f>'Final BOM'!G26</f>
+        <v/>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>30-00099</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>4-core cable, 28 AWG, one twisted pair, foil and braid shield, 3.61 mm OD, white, 1 m (Digi-Key cut length)</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>AX1 lead</t>
         </is>
       </c>
-      <c r="G16" s="30">
-        <f>'Final BOM'!M24</f>
-        <v/>
-      </c>
-      <c r="H16" s="30">
-        <f>IF('Final BOM'!M24="","",C16*G16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="27" t="inlineStr">
-        <is>
-          <t>Collective sensor lead: from the AS5600 in the base, through the lever's cable channels and up the 470 mm tube, spliced to an AX1 pigtail. Length is an estimate: measure your run; Digi-Key sells it by the metre</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="G18" s="19">
+        <f>'Final BOM'!M26</f>
+        <v/>
+      </c>
+      <c r="H18" s="19">
+        <f>IF('Final BOM'!M26="","",C18*G18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>Collective sensor lead: from the AS5600 in the base, through the lever's cable channels and up the 470 mm tube, spliced to an AX1 pigtail. SDA and GND on the twisted pair, VCC and SCL on the other two; the shield to GND at the board end only. Length is an estimate: measure your run; Digi-Key sells it by the metre (145 m in stock 2026-10-27; the black 30-00088 was out of stock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>380-SC-2CAK020M-ND</t>
         </is>
       </c>
-      <c r="C17" s="26">
-        <f>'Final BOM'!G25</f>
-        <v/>
-      </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="C19" s="15">
+        <f>'Final BOM'!G27</f>
+        <v/>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>SC-2CAK020M</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>USB 2.0 cable, USB-A plug to USB-C plug, 2 m (6.56 ft)</t>
         </is>
       </c>
-      <c r="F17" s="27" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>USB</t>
         </is>
       </c>
-      <c r="G17" s="30">
-        <f>'Final BOM'!M25</f>
-        <v/>
-      </c>
-      <c r="H17" s="30">
-        <f>IF('Final BOM'!M25="","",C17*G17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="G19" s="19">
+        <f>'Final BOM'!M27</f>
+        <v/>
+      </c>
+      <c r="H19" s="19">
+        <f>IF('Final BOM'!M27="","",C19*G19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>Cut it about 15 cm from the USB-C plug. Feed the long piece (USB-A end stays at the PC) through the device: laid in the lever's open channels, up the tube and in through the head. The cable cover's spout is a plain 7.5 mm bore. Splice the USB-C stub back on inside the head (red, black, green, white) and leave the shield wire unconnected. The cut costs about 15 cm of the 2 m: check the run still reaches. The head's clearances were checked with a micro-USB plug: check the C plug fits the same way</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="29" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>679-1223-ND</t>
         </is>
       </c>
-      <c r="C18" s="26">
-        <f>'Final BOM'!G31</f>
-        <v/>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="C20" s="15">
+        <f>'Final BOM'!G33</f>
+        <v/>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>639H/2</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>Toggle switch, SPDT, ON-OFF-ON, M12 bushing, solder lug</t>
         </is>
       </c>
-      <c r="F18" s="27" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>IN3-IN6</t>
         </is>
       </c>
-      <c r="G18" s="30">
-        <f>'Final BOM'!M31</f>
-        <v/>
-      </c>
-      <c r="H18" s="30">
-        <f>IF('Final BOM'!M31="","",C18*G18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="27" t="inlineStr">
+      <c r="G20" s="19">
+        <f>'Final BOM'!M33</f>
+        <v/>
+      </c>
+      <c r="H20" s="19">
+        <f>IF('Final BOM'!M33="","",C20*G20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>LDG LT EXT / RETR and SL ON / STOW. Common to GND. Price from Digi-Key, 2026-10-22</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="29" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>679-1219-ND</t>
         </is>
       </c>
-      <c r="C19" s="26">
-        <f>'Final BOM'!G32</f>
-        <v/>
-      </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="C21" s="15">
+        <f>'Final BOM'!G34</f>
+        <v/>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>637H/2</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>Toggle switch, SPDT, (ON)-OFF-(ON), M12 bushing, solder lug</t>
         </is>
       </c>
-      <c r="F19" s="27" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>IN1, IN2</t>
         </is>
       </c>
-      <c r="G19" s="30">
-        <f>'Final BOM'!M32</f>
-        <v/>
-      </c>
-      <c r="H19" s="30">
-        <f>IF('Final BOM'!M32="","",C19*G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="27" t="inlineStr">
+      <c r="G21" s="19">
+        <f>'Final BOM'!M34</f>
+        <v/>
+      </c>
+      <c r="H21" s="19">
+        <f>IF('Final BOM'!M34="","",C21*G21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>GOV RPM INCR / DECR. Price from Digi-Key, 2026-10-22</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="29" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>679-1217-ND</t>
         </is>
       </c>
-      <c r="C20" s="26">
-        <f>'Final BOM'!G33</f>
-        <v/>
-      </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="C22" s="15">
+        <f>'Final BOM'!G35</f>
+        <v/>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>636H/2</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Toggle switch, SPDT, ON-ON, M12 bushing, solder lug</t>
         </is>
       </c>
-      <c r="F20" s="27" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>IN7</t>
         </is>
       </c>
-      <c r="G20" s="30">
-        <f>'Final BOM'!M33</f>
-        <v/>
-      </c>
-      <c r="H20" s="30">
-        <f>IF('Final BOM'!M33="","",C20*G20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="G22" s="19">
+        <f>'Final BOM'!M35</f>
+        <v/>
+      </c>
+      <c r="H22" s="19">
+        <f>IF('Final BOM'!M35="","",C22*G22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>LDG LT ON (one side wired). Price from Digi-Key, 2026-10-22</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="29" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>2223-PB4-M-BK-D-67-ND</t>
         </is>
       </c>
-      <c r="C21" s="26">
-        <f>'Final BOM'!G34</f>
-        <v/>
-      </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="C23" s="15">
+        <f>'Final BOM'!G36</f>
+        <v/>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>PB4-M-BK-D-67</t>
         </is>
       </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>Push button, large, SPST-NO momentary, M12</t>
         </is>
       </c>
-      <c r="F21" s="27" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>IN13</t>
         </is>
       </c>
-      <c r="G21" s="30">
-        <f>'Final BOM'!M34</f>
-        <v/>
-      </c>
-      <c r="H21" s="30">
-        <f>IF('Final BOM'!M34="","",C21*G21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="27" t="inlineStr">
+      <c r="G23" s="19">
+        <f>'Final BOM'!M36</f>
+        <v/>
+      </c>
+      <c r="H23" s="19">
+        <f>IF('Final BOM'!M36="","",C23*G23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>STOP REL</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="26" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="29" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>450-1650-ND</t>
         </is>
       </c>
-      <c r="C22" s="26">
-        <f>'Final BOM'!G35</f>
-        <v/>
-      </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="C24" s="15">
+        <f>'Final BOM'!G37</f>
+        <v/>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>1825910-6</t>
         </is>
       </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>Tactile switch, 6 x 6 mm, 5 mm high, THT</t>
         </is>
       </c>
-      <c r="F22" s="27" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>IN9-IN12, IN14</t>
         </is>
       </c>
-      <c r="G22" s="30">
-        <f>'Final BOM'!M35</f>
-        <v/>
-      </c>
-      <c r="H22" s="30">
-        <f>IF('Final BOM'!M35="","",C22*G22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="27" t="inlineStr">
+      <c r="G24" s="19">
+        <f>'Final BOM'!M37</f>
+        <v/>
+      </c>
+      <c r="H24" s="19">
+        <f>IF('Final BOM'!M37="","",C24*G24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>SEARCH CONT hat (4, new rocker hat) and starter trigger (1). IN8, IN15, IN16 are spare</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="26" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="29" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>SRS-4-4MM-ND</t>
         </is>
       </c>
-      <c r="C23" s="26">
-        <f>'Final BOM'!G48</f>
-        <v/>
-      </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="C25" s="15">
+        <f>'Final BOM'!G50</f>
+        <v/>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>SRS-4-4MM</t>
         </is>
       </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>Round spacer, unthreaded, for M3, 4 mm long, 6.4 mm OD, PVC, self-retaining</t>
         </is>
       </c>
-      <c r="F23" s="27" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>HeliSR board</t>
         </is>
       </c>
-      <c r="G23" s="30">
-        <f>'Final BOM'!M48</f>
-        <v/>
-      </c>
-      <c r="H23" s="30">
-        <f>IF('Final BOM'!M48="","",C23*G23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="27" t="inlineStr">
+      <c r="G25" s="19">
+        <f>'Final BOM'!M50</f>
+        <v/>
+      </c>
+      <c r="H25" s="19">
+        <f>IF('Final BOM'!M50="","",C25*G25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
         <is>
           <t>Between the rear wall and the board</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="26" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="29" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>315-NC191LT10-ND</t>
         </is>
       </c>
-      <c r="C24" s="26">
-        <f>'Final BOM'!G72</f>
-        <v/>
-      </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="C26" s="15">
+        <f>'Final BOM'!G74</f>
+        <v/>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>NC191LT10</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>Solder paste, low-temperature (Sn42/Bi58, 138 C), syringe</t>
         </is>
       </c>
-      <c r="F24" s="27" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Assembly</t>
         </is>
       </c>
-      <c r="G24" s="30">
-        <f>'Final BOM'!M72</f>
-        <v/>
-      </c>
-      <c r="H24" s="30">
-        <f>IF('Final BOM'!M72="","",C24*G24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="27" t="inlineStr">
-        <is>
-          <t>For the SMD parts on the board (U1, U2, the 1206 caps, the JST headers, SW1-SW3). Needs a hot plate or hot air tool and flux. Optional: hand-soldering works too</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="26" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="G26" s="19">
+        <f>'Final BOM'!M74</f>
+        <v/>
+      </c>
+      <c r="H26" s="19">
+        <f>IF('Final BOM'!M74="","",C26*G26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>For the SMD parts on the board (U1-U3, the 1206 parts, the JST headers, SW1). Needs a hot plate or hot air tool and flux; with parts on both sides, do the back first. Optional: hand-soldering works too</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>1188-CHN-TWZ1MM-ND</t>
         </is>
       </c>
-      <c r="C25" s="26">
-        <f>'Final BOM'!G73</f>
-        <v/>
-      </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="C27" s="15">
+        <f>'Final BOM'!G75</f>
+        <v/>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>CHN-TWZ1MM</t>
         </is>
       </c>
-      <c r="E25" s="27" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>Tweezers, 1 mm tip (Olimex CHN-TWZ1MM), for placing the SMD parts</t>
         </is>
       </c>
-      <c r="F25" s="27" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>Assembly</t>
         </is>
       </c>
-      <c r="G25" s="30">
-        <f>'Final BOM'!M73</f>
-        <v/>
-      </c>
-      <c r="H25" s="30">
-        <f>IF('Final BOM'!M73="","",C25*G25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="27" t="inlineStr">
+      <c r="G27" s="19">
+        <f>'Final BOM'!M75</f>
+        <v/>
+      </c>
+      <c r="H27" s="19">
+        <f>IF('Final BOM'!M75="","",C27*G27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>Description from Olimex's sibling CHN-TWZ2MM listing: check the tip</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="G26" s="3" t="inlineStr">
+    <row r="28">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H26" s="15">
-        <f>SUM(H5:H25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>All 21 Digi-Key lines are priced (checked 2026-10-23), before shipping and tariff.</t>
+      <c r="H28" s="20">
+        <f>SUM(H5:H27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>All 23 Digi-Key lines are priced (checked 2026-10-23; Rev 4.0's new parts 2026-10-27), before shipping and tariff.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <hyperlinks>
@@ -5688,6 +5912,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5752,567 +5978,567 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="A5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-GripBearingCoupons.stl</t>
         </is>
       </c>
-      <c r="D5" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="D5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Flat, labels up. Optional: checks the head's 25.2 mm tube bore on the carbon tube (the grip now rides on O-rings)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-ORingCoupon.stl</t>
         </is>
       </c>
-      <c r="D6" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="D6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Upright. A slice of the grip's bore with one O-ring groove: fit a greased 24 x 2 O-ring and slide it on the carbon tube before printing the grip (about 2 g)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-SensorSeatCoupon.stl</t>
         </is>
       </c>
-      <c r="D7" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="D7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>The same way round as in the head on its rear wall. Optional: slide the AS5600 module through it first</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-Body.stl</t>
         </is>
       </c>
-      <c r="D8" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="D8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>One piece: box, neck, faux friction knob, boss, sensor pod and trigger mount. On its rear wall, with tree supports under the neck, knob and tube bore; then ream the bore to a press fit on the tube</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-LowerPanel-Black.stl + -WhiteText.stl</t>
         </is>
       </c>
-      <c r="D9" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="D9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Front face down, two colours</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-UpperPanel-Black.stl + -WhiteText.stl</t>
         </is>
       </c>
-      <c r="D10" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="D10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Front face down, two colours</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-Trigger.stl</t>
         </is>
       </c>
-      <c r="D11" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="D11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>On either flat side</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-Hat-Cap.stl</t>
         </is>
       </c>
-      <c r="D12" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="D12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Base down. Glue it onto the rocker plate's four legs, last</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-Hat-RockerPlate.stl</t>
         </is>
       </c>
-      <c r="D13" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="D13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Legs down on the bed, boss up; the legs are part of it</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-Hat-Bezel.stl</t>
         </is>
       </c>
-      <c r="D14" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="D14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Front face down</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-ThrottleGrip.stl</t>
         </is>
       </c>
-      <c r="D15" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="D15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>Upright, bottom end down; no supports</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-FrictionCollar.stl</t>
         </is>
       </c>
-      <c r="D16" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="D16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Bottom face down, O-ring groove up</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-Pinion.stl</t>
         </is>
       </c>
-      <c r="D17" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="D17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>Flat; the magnet shaft presses into its hex</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5/stl/HueyHeadR5-MagnetShaft.stl</t>
         </is>
       </c>
-      <c r="D18" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="27" t="inlineStr">
+      <c r="D18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>Cap face down, pin up</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Base/stl/coupons/coupon_trunnion.stl, coupon_bearing_seat.stl, coupon_tube_socket.stl</t>
         </is>
       </c>
-      <c r="D19" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="D19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>Fit-test coupons: print first and tune mk3_pivot.py (the socket with the carbon tube)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Base/stl/frame.stl</t>
         </is>
       </c>
-      <c r="D20" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="D20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>Plate down</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="n">
+      <c r="A21" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C21" s="27" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Base/stl/lever_lower.stl</t>
         </is>
       </c>
-      <c r="D21" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="D21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>On its joint face</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="n">
+      <c r="A22" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C22" s="27" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Base/stl/lever_upper.stl</t>
         </is>
       </c>
-      <c r="D22" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="D22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>On its joint face</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="n">
+      <c r="A23" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C23" s="27" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Base/stl/cap_left.stl, cap_right.stl</t>
         </is>
       </c>
-      <c r="D23" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="D23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>One each</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="n">
+      <c r="A24" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C24" s="27" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Base/stl/cover_cable.stl, cover_sensor.stl</t>
         </is>
       </c>
-      <c r="D24" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="27" t="inlineStr">
+      <c r="D24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>One each</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="n">
+      <c r="A25" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C25" s="27" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>Base/stl/cable_plug.stl</t>
         </is>
       </c>
-      <c r="D25" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="27" t="inlineStr">
+      <c r="D25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>On a long flat face. Fills the cable cover's slot once the USB cable is in</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="n">
+      <c r="A26" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C26" s="27" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>Base/stl/sensor_carrier.stl</t>
         </is>
       </c>
-      <c r="D26" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="27" t="inlineStr"/>
+      <c r="D26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="16" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="n">
+      <c r="A27" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Base/stl/shoe.stl</t>
         </is>
       </c>
-      <c r="D27" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="27" t="inlineStr"/>
+      <c r="D27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="n">
+      <c r="A28" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Base/stl/strut_collar.stl</t>
         </is>
       </c>
-      <c r="D28" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="D28" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>Standing on one end</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="n">
+      <c r="A29" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C29" s="27" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Base/stl/friction_knob.stl</t>
         </is>
       </c>
-      <c r="D29" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
+      <c r="D29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Top face down; the M5 x 25 hex bolt's head presses into its hex pocket</t>
         </is>
@@ -6333,7 +6559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6353,7 +6579,7 @@
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lines in the Rev 3.0 board's full BOM, the Digi-Key cart or earlier head and base revisions that this build doesn't use. Take them out of the cart if they're still in it.</t>
+          <t>Lines in the Rev 3.0 board's full BOM, the Digi-Key cart or earlier head and base revisions that this build doesn't use, and the Rev 3.0 parts already bought that Rev 4.0 doesn't use. Take them out of the cart if they're still in it.</t>
         </is>
       </c>
     </row>
@@ -6385,515 +6611,632 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="A5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>HeliSR Rev 3.0 bare PCBs (OSH Park, 3 boards, $10.20)</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Bought 2026-10-21. Rev 4.0 replaces the board: it reads the AS5600s over I2C instead of their analog output</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>OSH Park order, 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>YAGEO RC0805FR-071KL 1 kOhm 0805 (311-1.00KCRCT-ND)</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Bought in order 102438510 for Rev 3.0's PROG buttons (R1, R2); Rev 4.0 has none</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key order 102438510</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>JST BM03B-SRSS-TBT 3-pin header (455-BM03B-SRSS-TBTCT-ND)</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Bought in order 102438510 for Rev 3.0's analog inputs; Rev 4.0's AX ports are 4-pin (BM04B-SRSS-TBT)</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key order 102438510</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>E-Switch TL1015AF160QG (EG4344CT-ND), 2 of the 3 bought</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Rev 4.0 has only RST (SW1): the other two are spares</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key order 102438510</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>JST A03SR03SR30K203A 3-pin jumpers (455-3627-ND)</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Bought in order 102438510; Rev 4.0's AX ports take the 4-pin A04SR04SR30K203A</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key order 102438510</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Tensility 30-01653 3-core lead, 1 m (839-30-01653-DS-ND)</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Bought in order 102438510 for the analog sensor; I2C needs four cores (Tensility 30-00099)</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key order 102438510</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Glue, thread-lock, taps, drill bit, felt tape, hose clamp, 10 mm spring, #10 desk screws</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr"/>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr"/>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>You supply these yourself</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>User, 2026-10-23</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="26" t="n">
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Fgruh M3 and M4 socket-cap screw kits, M3 x 10 / M4 x 30 / M5 x 40 countersunk packs, M6 x 25 and M6 x 30 bolts, M6 and M4 nyloc nuts, uxcell M5 x 5 set screws, heat-set inserts and insert tips</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr"/>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Every screw and nut now comes from the AvrestYPT and set screw kits (2026-10-23): the CAD was changed to suit them</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>User, 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>MkII-AdjustKnob.stl (friction knob)</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Took an M6 hex head; the base now prints its own knob for an M5 x 25 hex bolt</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>Base/mk3_pivot.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>SparkFun Pro Micro 12640 (Digi-Key 1568-12640-ND)</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Replaced by the OSOYOO USB-C Pro Micro from Amazon</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Sullins PRPC012SAAN-RC male headers (Digi-Key 35-PRPC012SAAN-RC-ND)</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>Fgruh M3 and M4 socket-cap screw kits, M3 x 10 / M4 x 30 / M5 x 40 countersunk packs, M6 x 25 and M6 x 30 bolts, M6 and M4 nyloc nuts, uxcell M5 x 5 set screws, heat-set inserts and insert tips</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="inlineStr"/>
-      <c r="D6" s="27" t="inlineStr">
-        <is>
-          <t>Every screw and nut now comes from the AvrestYPT and set screw kits (2026-10-23): the CAD was changed to suit them</t>
-        </is>
-      </c>
-      <c r="E6" s="27" t="inlineStr">
-        <is>
-          <t>User, 2026-10-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>The OSOYOO Pro Micro comes with header pins</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Assmann AK67421-2 USB A to micro-B cable</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>The OSOYOO Pro Micro is USB-C</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>E-Switch PS1024ABLK push button (EG2011-ND)</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>The head removed the two lower-panel push buttons</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>TT P0915N-QC20BR5K 5 k pot (987-1278-ND)</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>No head-knob pot any more; the throttle is read by an AS5600</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Knob for a 6 mm knurled shaft (Cliff FC7257)</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Went with the head-knob pot</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>TI DRV5055A4 / A2 Hall sensors, KEMET axial 100 nF</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>MkII-AdjustKnob.stl (friction knob)</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="27" t="inlineStr">
-        <is>
-          <t>Took an M6 hex head; the base now prints its own knob for an M5 x 25 hex bolt</t>
-        </is>
-      </c>
-      <c r="E7" s="27" t="inlineStr">
-        <is>
-          <t>Base/mk3_pivot.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>SparkFun Pro Micro 12640 (Digi-Key 1568-12640-ND)</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>Replaced by the OSOYOO USB-C Pro Micro from Amazon</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>MkII base only; the MkIII base uses an AS5600</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>Sullins PRPC012SAAN-RC male headers (Digi-Key 35-PRPC012SAAN-RC-ND)</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="n">
+    <row r="21">
+      <c r="A21" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>APEM MJTP1230A / G / F tactile switches (Digi-Key 679-2429-ND, 679-2435-ND, 679-2434-ND)</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>The TE 1825910-6 covers all five tactile inputs</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key cart, 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Keystone 941 micro-B plug (Digi-Key 36-941-ND)</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>The Pro Micro is USB-C</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key cart, 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Samsung CL10B104KB8WPNC 0.1 uF 0603 cap (Digi-Key 1276-6854-1-ND)</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>The board uses 1206 caps</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key cart, 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Qualtek 3021017-10 USB-A to open-end cable, 10 ft (Digi-Key Q369-ND)</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>The Stewart A-to-C cable, cut and spliced, replaces it</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key cart, 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>USB-C male plug (loose) and hookup wire</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>The plug comes on the Stewart cable; you already have hookup wire, heat-shrink and solder</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>Earlier BOM draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>TE 2495152-1 USB-C plug</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Board-edge part with no solder cups: needs its own PCB</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>User question, 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>JST SR 3-pin jumpers beyond 2</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>The OSOYOO Pro Micro comes with header pins</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>The full BOM had 4 (one per AX connector); only AX1 and AX4 are wired now</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>Assmann AK67421-2 USB A to micro-B cable</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="27" t="inlineStr">
-        <is>
-          <t>The OSOYOO Pro Micro is USB-C</t>
-        </is>
-      </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>E-Switch PS1024ABLK push button (EG2011-ND)</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>The head removed the two lower-panel push buttons</t>
-        </is>
-      </c>
-      <c r="E11" s="27" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>TT P0915N-QC20BR5K 5 k pot (987-1278-ND)</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="27" t="inlineStr">
-        <is>
-          <t>No head-knob pot any more; the throttle is read by an AS5600</t>
-        </is>
-      </c>
-      <c r="E12" s="27" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>Knob for a 6 mm knurled shaft (Cliff FC7257)</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>Went with the head-knob pot</t>
-        </is>
-      </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>TI DRV5055A4 / A2 Hall sensors, KEMET axial 100 nF</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="27" t="inlineStr">
-        <is>
-          <t>MkII base only; the MkIII base uses an AS5600</t>
-        </is>
-      </c>
-      <c r="E14" s="27" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>APEM MJTP1230A / G / F tactile switches (Digi-Key 679-2429-ND, 679-2435-ND, 679-2434-ND)</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="27" t="inlineStr">
-        <is>
-          <t>The TE 1825910-6 covers all five tactile inputs</t>
-        </is>
-      </c>
-      <c r="E15" s="27" t="inlineStr">
-        <is>
-          <t>Digi-Key cart, 2026-10-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>Keystone 941 micro-B plug (Digi-Key 36-941-ND)</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>The Pro Micro is USB-C</t>
-        </is>
-      </c>
-      <c r="E16" s="27" t="inlineStr">
-        <is>
-          <t>Digi-Key cart, 2026-10-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>Samsung CL10B104KB8WPNC 0.1 uF 0603 cap (Digi-Key 1276-6854-1-ND)</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="27" t="inlineStr">
-        <is>
-          <t>The board uses 1206 caps</t>
-        </is>
-      </c>
-      <c r="E17" s="27" t="inlineStr">
-        <is>
-          <t>Digi-Key cart, 2026-10-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>Qualtek 3021017-10 USB-A to open-end cable, 10 ft (Digi-Key Q369-ND)</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>The Stewart A-to-C cable, cut and spliced, replaces it</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>Digi-Key cart, 2026-10-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>USB-C male plug (loose) and hookup wire</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>The plug comes on the Stewart cable; you already have hookup wire, heat-shrink and solder</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="inlineStr">
-        <is>
-          <t>Earlier BOM draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>TE 2495152-1 USB-C plug</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t>Board-edge part with no solder cups: needs its own PCB</t>
-        </is>
-      </c>
-      <c r="E20" s="27" t="inlineStr">
-        <is>
-          <t>User question, 2026-10-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>JST SR 3-pin jumpers beyond 2</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="27" t="inlineStr">
-        <is>
-          <t>The full BOM had 4 (one per AX connector); only AX1 and AX4 are wired now</t>
-        </is>
-      </c>
-      <c r="E21" s="27" t="inlineStr">
-        <is>
-          <t>PCB/HeliSR_Rev3.0/HeliSR_Rev3.0_BOM.xlsx (Digi-Key cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="26" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>JST BM03B-SRSS-TBT: the cart has 3</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr"/>
-      <c r="D22" s="27" t="inlineStr">
-        <is>
-          <t>A note, not dropped: the board has 4 footprints (J11-J14); this BOM orders 4</t>
-        </is>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>Digi-Key cart, 2026-10-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="26" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="27" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>MkII collective hardware (base, head bolts, springs, magnets)</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr"/>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr"/>
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>The MkII base is replaced by the MkIII Rev 3</t>
         </is>
       </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>HeliSR_Rev3.0_BOM.xlsx, sheet 2</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="26" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="27" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>25 x 1 mm aluminium tube, 358 mm</t>
         </is>
       </c>
-      <c r="C24" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="C29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Replaced by the base's 470 mm carbon tube</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Head/README.md (before)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="26" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="27" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Ballast bucket, lid, ~0.95 kg ballast, 4 x M4 bucket bolts + inserts, lid M3 screws + inserts</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr"/>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr"/>
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Base Rev 3 balances with the gas strut</t>
         </is>
       </c>
-      <c r="E25" s="27" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>Base/README.md, Bought parts</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="26" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="27" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>Quadrant stop block, thumb knob, M5 x 16 stop bolt + nut, M6 striker + insert</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr"/>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr"/>
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>Base Rev 3 has a fixed 32 deg stop</t>
         </is>
       </c>
-      <c r="E26" s="27" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>Base/README.md, Bought parts</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="27" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Rev 1 centre down-stop screw, nut and insert</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr"/>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr"/>
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Base Rev 3 uses two down-stop posts beside the strut</t>
         </is>
       </c>
-      <c r="E27" s="27" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>Base/mk3_rev3.py</t>
         </is>
@@ -6914,7 +7257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6954,68 +7297,85 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>HeliSR Rev 4.0 board</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>PCB/HeliSR_Rev4.0 (tools/make_board_bom_v4.py, checked against HeliSR_Rev4.0.kicad_pcb)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Designed and checked, not ordered yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>HeliSR Rev 3.0 board</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>PCB/HeliSR_Rev3.0</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>Bare PCB ordered from OSH Park on 2026-10-21; folder frozen and read-only</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Replaced by Rev 4.0. Bare PCB ordered from OSH Park on 2026-10-21, and its parts in Digi-Key order 102438510; folder frozen and read-only. Its full BOM still supplies the cables and head switches</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Huey head</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Head/Rev5</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Current head design: Rev 5, Rev 4 cut to the real UH-1 panels' dimensions, with printed threads. Rev 4 (Head/Rev4), the larger one-piece head it came from, is kept as a fallback</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>MkIII base Rev 3</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Base (Base/mk3_rev3.py imports Base/mk3_pivot.py)</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Concept, nothing printed yet: check the orange lines</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Prices</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Digi-Key cart 2026-10-19 (JST headers 2026-10-22); Amazon listings 2026-10-22; OSH Park order 2026-10-21</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Digi-Key cart 2026-10-19 (JST headers 2026-10-22; Rev 4.0's new parts and cables 2026-10-27); Amazon listings 2026-10-22; OSH Park order 2026-10-21</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Pack prices, before shipping and tariff</t>
         </is>
